--- a/STW programs/STW_sitefile_and_mapping.xlsx
+++ b/STW programs/STW_sitefile_and_mapping.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\finnf\Desktop\LEI-SRML-Intern-Project\STW programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3080AC-D5D8-451A-B2B7-F26348DDCB39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8290B3-06D5-444F-A12F-B9162221781A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="STW site" sheetId="2" r:id="rId1"/>
-    <sheet name="Master" sheetId="3" r:id="rId2"/>
+    <sheet name="All" sheetId="3" r:id="rId2"/>
     <sheet name="GHI" sheetId="5" r:id="rId3"/>
     <sheet name="DNI" sheetId="6" r:id="rId4"/>
     <sheet name="DHI" sheetId="7" r:id="rId5"/>
@@ -22,6 +22,7 @@
     <sheet name="PIR" sheetId="9" r:id="rId7"/>
     <sheet name="SZA" sheetId="10" r:id="rId8"/>
     <sheet name="AZM" sheetId="11" r:id="rId9"/>
+    <sheet name="Column Mapping" sheetId="12" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2578" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2667" uniqueCount="272">
   <si>
     <t>M = 1000/R</t>
   </si>
@@ -809,6 +810,54 @@
   </si>
   <si>
     <t>5218</t>
+  </si>
+  <si>
+    <t>Datetime</t>
+  </si>
+  <si>
+    <t>09/30/2015 23:00</t>
+  </si>
+  <si>
+    <t>01/01/2016 00:01</t>
+  </si>
+  <si>
+    <t>01/01/2017 00:01</t>
+  </si>
+  <si>
+    <t>08/01/2017 11:40</t>
+  </si>
+  <si>
+    <t>01/01/2018 00:01</t>
+  </si>
+  <si>
+    <t>01/01/2019 00:01</t>
+  </si>
+  <si>
+    <t>01/01/2020 00:01</t>
+  </si>
+  <si>
+    <t>08/01/2020 00:01</t>
+  </si>
+  <si>
+    <t>01/01/2021 00:01</t>
+  </si>
+  <si>
+    <t>07/01/2021 00:01</t>
+  </si>
+  <si>
+    <t>07/19/2022 12:46</t>
+  </si>
+  <si>
+    <t>02/01/2024 00:01</t>
+  </si>
+  <si>
+    <t>08/01/2024 00:01</t>
+  </si>
+  <si>
+    <t>08/01/2025 00:01</t>
+  </si>
+  <si>
+    <t>151960</t>
   </si>
 </sst>
 </file>
@@ -1269,7 +1318,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -1553,6 +1602,54 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF95B3D7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF95B3D7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF95B3D7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF95B3D7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF95B3D7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF95B3D7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF95B3D7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF95B3D7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF95B3D7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF95B3D7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1599,7 +1696,7 @@
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1682,6 +1779,21 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="13" fillId="44" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="45" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="45" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="44" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="44" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="46" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="47" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="48" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="22" fillId="47" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="22" fillId="48" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="48" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="22" fillId="48" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="47" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="22" fillId="47" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1694,21 +1806,13 @@
     <xf numFmtId="0" fontId="16" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="45" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="45" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="45" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="44" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="44" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="46" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="47" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="48" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="22" fillId="47" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="22" fillId="48" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="48" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="22" fillId="48" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="47" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="22" fillId="47" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="48" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="47" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="48" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="47" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="47" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="47" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1757,40 +1861,10 @@
   </cellStyles>
   <dxfs count="98">
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF4F81BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <border outline="0">
         <top style="thin">
           <color rgb="FF95B3D7"/>
         </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF95B3D7"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1804,6 +1878,13 @@
         <top style="thin">
           <color rgb="FF95B3D7"/>
         </top>
+        <bottom style="thin">
+          <color rgb="FF95B3D7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color rgb="FF95B3D7"/>
         </bottom>
@@ -1841,13 +1922,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF95B3D7"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color rgb="FF95B3D7"/>
         </left>
@@ -1857,6 +1931,13 @@
         <top style="thin">
           <color rgb="FF95B3D7"/>
         </top>
+        <bottom style="thin">
+          <color rgb="FF95B3D7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color rgb="FF95B3D7"/>
         </bottom>
@@ -1882,29 +1963,6 @@
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FF4F81BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2443,13 +2501,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF95B3D7"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color rgb="FF95B3D7"/>
         </left>
@@ -2459,6 +2510,36 @@
         <top style="thin">
           <color rgb="FF95B3D7"/>
         </top>
+        <bottom style="thin">
+          <color rgb="FF95B3D7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color rgb="FF95B3D7"/>
         </bottom>
@@ -2484,29 +2565,6 @@
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FF4F81BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3045,13 +3103,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF95B3D7"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color rgb="FF95B3D7"/>
         </left>
@@ -3061,6 +3112,36 @@
         <top style="thin">
           <color rgb="FF95B3D7"/>
         </top>
+        <bottom style="thin">
+          <color rgb="FF95B3D7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color rgb="FF95B3D7"/>
         </bottom>
@@ -3086,29 +3167,6 @@
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FF4F81BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDCE6F1"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3647,13 +3705,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF95B3D7"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color rgb="FF95B3D7"/>
         </left>
@@ -3663,6 +3714,36 @@
         <top style="thin">
           <color rgb="FF95B3D7"/>
         </top>
+        <bottom style="thin">
+          <color rgb="FF95B3D7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color rgb="FF95B3D7"/>
         </bottom>
@@ -3688,29 +3769,6 @@
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor rgb="FF4F81BD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4249,13 +4307,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF95B3D7"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color rgb="FF95B3D7"/>
         </left>
@@ -4265,6 +4316,36 @@
         <top style="thin">
           <color rgb="FF95B3D7"/>
         </top>
+        <bottom style="thin">
+          <color rgb="FF95B3D7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color rgb="FF95B3D7"/>
         </bottom>
@@ -4282,15 +4363,14 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color theme="0"/>
+        <color rgb="FFFFFFFF"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF4F81BD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4483,13 +4563,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <right style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </right>
@@ -4500,6 +4573,37 @@
           <color theme="4" tint="0.39997558519241921"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4572,15 +4676,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E2971E8D-EC9F-4E58-B2D2-0AE0519F728F}" name="Table2" displayName="Table2" ref="A1:O19" totalsRowShown="0" headerRowDxfId="88" headerRowBorderDxfId="95" tableBorderDxfId="96" totalsRowBorderDxfId="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E2971E8D-EC9F-4E58-B2D2-0AE0519F728F}" name="Table2" displayName="Table2" ref="A1:O19" totalsRowShown="0" headerRowDxfId="96" headerRowBorderDxfId="95" tableBorderDxfId="94" totalsRowBorderDxfId="93">
   <autoFilter ref="A1:O19" xr:uid="{E2971E8D-EC9F-4E58-B2D2-0AE0519F728F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O19">
     <sortCondition ref="A1:A19"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{9EF617D4-F72F-428C-8C02-BFC8CEB705E4}" name="Year" dataDxfId="93"/>
-    <tableColumn id="2" xr3:uid="{064DEE78-908D-410D-869D-0A1DF96C0A12}" name="Month" dataDxfId="92"/>
-    <tableColumn id="3" xr3:uid="{AF4CC9CF-855F-4E8B-94D6-AEE3181E6DBE}" name="Day" dataDxfId="91"/>
+    <tableColumn id="1" xr3:uid="{9EF617D4-F72F-428C-8C02-BFC8CEB705E4}" name="Year" dataDxfId="92"/>
+    <tableColumn id="2" xr3:uid="{064DEE78-908D-410D-869D-0A1DF96C0A12}" name="Month" dataDxfId="91"/>
+    <tableColumn id="3" xr3:uid="{AF4CC9CF-855F-4E8B-94D6-AEE3181E6DBE}" name="Day" dataDxfId="90"/>
     <tableColumn id="4" xr3:uid="{4B827B0B-D329-42C4-B0BD-FE4E4FBBB514}" name="Hour"/>
     <tableColumn id="5" xr3:uid="{C7210130-12DB-4F95-BDD2-F898E2C3ABB0}" name="Minute"/>
     <tableColumn id="6" xr3:uid="{EA66C9AC-EDE4-4974-B174-B283289B3FBF}" name="Column"/>
@@ -4590,8 +4694,8 @@
     <tableColumn id="10" xr3:uid="{F4DDA843-9006-4C5B-8BD2-4FFBC8DCF5AF}" name="Metric"/>
     <tableColumn id="11" xr3:uid="{B14ADA59-B0A3-4645-AC40-1127D298BAFD}" name="R_program"/>
     <tableColumn id="12" xr3:uid="{2D3CC04A-39C8-4DEF-BE60-9E9FFA02ADDA}" name="R_should_be"/>
-    <tableColumn id="13" xr3:uid="{814478A7-F655-4BA3-A8A1-4D9F76038C5E}" name="M_program" dataDxfId="90"/>
-    <tableColumn id="14" xr3:uid="{BDB10B69-13DA-474E-8D6E-C57C7C1D5FA8}" name="M_should_be" dataDxfId="89"/>
+    <tableColumn id="13" xr3:uid="{814478A7-F655-4BA3-A8A1-4D9F76038C5E}" name="M_program" dataDxfId="89"/>
+    <tableColumn id="14" xr3:uid="{BDB10B69-13DA-474E-8D6E-C57C7C1D5FA8}" name="M_should_be" dataDxfId="88"/>
     <tableColumn id="15" xr3:uid="{0E15DDED-6FD9-4BDF-8854-BF0CBED9919E}" name="Uncertainty"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4599,103 +4703,103 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9FE5D8B3-8BD3-4ECC-BD36-0871F9AB381A}" name="Table4" displayName="Table4" ref="A1:O10" totalsRowShown="0" headerRowDxfId="68" dataDxfId="69" headerRowBorderDxfId="86" tableBorderDxfId="87" totalsRowBorderDxfId="85">
-  <autoFilter ref="A1:O10" xr:uid="{9FE5D8B3-8BD3-4ECC-BD36-0871F9AB381A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9FE5D8B3-8BD3-4ECC-BD36-0871F9AB381A}" name="Table4" displayName="Table4" ref="A1:O20" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86" tableBorderDxfId="84" totalsRowBorderDxfId="83">
+  <autoFilter ref="A1:O20" xr:uid="{9FE5D8B3-8BD3-4ECC-BD36-0871F9AB381A}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{C5318B82-0C9B-4280-8F18-2386624D75D4}" name="Year" dataDxfId="84"/>
-    <tableColumn id="2" xr3:uid="{AB7BB480-881B-4705-BBE6-30CA6A8F0319}" name="Month" dataDxfId="83"/>
-    <tableColumn id="3" xr3:uid="{85B8F4C2-75CA-40D4-B600-78CD6F769E13}" name="Day" dataDxfId="82"/>
-    <tableColumn id="4" xr3:uid="{00C26572-13A6-45D1-A188-AFC4D9AE6807}" name="Hour" dataDxfId="81"/>
-    <tableColumn id="5" xr3:uid="{9A6943E8-358E-4EF8-9950-56E21A50000B}" name="Minute" dataDxfId="80"/>
-    <tableColumn id="6" xr3:uid="{377D20C0-C78F-4393-9884-28D8755B5097}" name="Column" dataDxfId="79"/>
-    <tableColumn id="7" xr3:uid="{FD2CEB93-5687-4039-BDBD-3F1E2E61C93D}" name="Measurment" dataDxfId="78"/>
-    <tableColumn id="8" xr3:uid="{EF83013D-9385-490C-8065-D95DCD4B83ED}" name="Sensor" dataDxfId="77"/>
-    <tableColumn id="9" xr3:uid="{C596A226-17F4-41FA-99AC-6F2D9320F7C7}" name="Serial Number" dataDxfId="76"/>
-    <tableColumn id="10" xr3:uid="{2C356D69-3FCF-46A0-8F23-203C9D72E028}" name="Metric" dataDxfId="75"/>
-    <tableColumn id="11" xr3:uid="{50941B6E-35F6-4429-854D-BB770F4CEA43}" name="R_program" dataDxfId="74"/>
-    <tableColumn id="12" xr3:uid="{49B1BCE1-89AA-4239-BFC9-8E8685857FA7}" name="R_should_be" dataDxfId="73"/>
-    <tableColumn id="13" xr3:uid="{B4255115-AD8D-4225-905D-EAFDF953EB71}" name="M_program" dataDxfId="72"/>
-    <tableColumn id="14" xr3:uid="{4B740645-9E88-410B-BEBB-EAF87799D2DE}" name="M_should_be" dataDxfId="71"/>
-    <tableColumn id="15" xr3:uid="{25F2B51D-3DCA-443F-972B-D56D448385E5}" name="Uncertainty" dataDxfId="70"/>
+    <tableColumn id="1" xr3:uid="{C5318B82-0C9B-4280-8F18-2386624D75D4}" name="Year" dataDxfId="82"/>
+    <tableColumn id="2" xr3:uid="{AB7BB480-881B-4705-BBE6-30CA6A8F0319}" name="Month" dataDxfId="81"/>
+    <tableColumn id="3" xr3:uid="{85B8F4C2-75CA-40D4-B600-78CD6F769E13}" name="Day" dataDxfId="80"/>
+    <tableColumn id="4" xr3:uid="{00C26572-13A6-45D1-A188-AFC4D9AE6807}" name="Hour" dataDxfId="79"/>
+    <tableColumn id="5" xr3:uid="{9A6943E8-358E-4EF8-9950-56E21A50000B}" name="Minute" dataDxfId="78"/>
+    <tableColumn id="6" xr3:uid="{377D20C0-C78F-4393-9884-28D8755B5097}" name="Column" dataDxfId="77"/>
+    <tableColumn id="7" xr3:uid="{FD2CEB93-5687-4039-BDBD-3F1E2E61C93D}" name="Measurment" dataDxfId="76"/>
+    <tableColumn id="8" xr3:uid="{EF83013D-9385-490C-8065-D95DCD4B83ED}" name="Sensor" dataDxfId="75"/>
+    <tableColumn id="9" xr3:uid="{C596A226-17F4-41FA-99AC-6F2D9320F7C7}" name="Serial Number" dataDxfId="74"/>
+    <tableColumn id="10" xr3:uid="{2C356D69-3FCF-46A0-8F23-203C9D72E028}" name="Metric" dataDxfId="73"/>
+    <tableColumn id="11" xr3:uid="{50941B6E-35F6-4429-854D-BB770F4CEA43}" name="R_program" dataDxfId="72"/>
+    <tableColumn id="12" xr3:uid="{49B1BCE1-89AA-4239-BFC9-8E8685857FA7}" name="R_should_be" dataDxfId="71"/>
+    <tableColumn id="13" xr3:uid="{B4255115-AD8D-4225-905D-EAFDF953EB71}" name="M_program" dataDxfId="70"/>
+    <tableColumn id="14" xr3:uid="{4B740645-9E88-410B-BEBB-EAF87799D2DE}" name="M_should_be" dataDxfId="69"/>
+    <tableColumn id="15" xr3:uid="{25F2B51D-3DCA-443F-972B-D56D448385E5}" name="Uncertainty" dataDxfId="68"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4CE50CCA-E98C-47E5-9B6A-5036206E6077}" name="Table5" displayName="Table5" ref="A1:O11" totalsRowShown="0" headerRowDxfId="48" dataDxfId="49" headerRowBorderDxfId="66" tableBorderDxfId="67" totalsRowBorderDxfId="65">
-  <autoFilter ref="A1:O11" xr:uid="{4CE50CCA-E98C-47E5-9B6A-5036206E6077}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4CE50CCA-E98C-47E5-9B6A-5036206E6077}" name="Table5" displayName="Table5" ref="A1:O14" totalsRowShown="0" headerRowDxfId="67" dataDxfId="65" headerRowBorderDxfId="66" tableBorderDxfId="64" totalsRowBorderDxfId="63">
+  <autoFilter ref="A1:O14" xr:uid="{4CE50CCA-E98C-47E5-9B6A-5036206E6077}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{40739C4F-7926-4D30-85E5-B1C70F07CC58}" name="Year" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{B9C436A4-C86A-4176-A748-A2EB263F2366}" name="Month" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{A23B2393-E795-4522-B348-48FA029168BF}" name="Day" dataDxfId="62"/>
-    <tableColumn id="4" xr3:uid="{12BC92B3-8400-4788-87F1-C45E3B3C0FF7}" name="Hour" dataDxfId="61"/>
-    <tableColumn id="5" xr3:uid="{5C484A21-4EB7-4A52-BDA8-9C8F6B385A2E}" name="Minute" dataDxfId="60"/>
-    <tableColumn id="6" xr3:uid="{43B4D4A3-BD23-4372-85F8-D1DC673B257B}" name="Column" dataDxfId="59"/>
-    <tableColumn id="7" xr3:uid="{13F1C5B1-12D8-497A-995C-A3C1C8F4EBBD}" name="Measurment" dataDxfId="58"/>
-    <tableColumn id="8" xr3:uid="{EEDF6678-0BA1-494A-B56E-3F4EE6168405}" name="Sensor" dataDxfId="57"/>
-    <tableColumn id="9" xr3:uid="{901111A6-DC2D-4708-9245-52416AA6A1AD}" name="Serial Number" dataDxfId="56"/>
-    <tableColumn id="10" xr3:uid="{ADA0E13A-487E-4D6B-9E5A-1B9264AF29CF}" name="Metric" dataDxfId="55"/>
-    <tableColumn id="11" xr3:uid="{AB1994B9-EB06-4647-987F-1CB1F7987349}" name="R_program" dataDxfId="54"/>
-    <tableColumn id="12" xr3:uid="{7FDD4AF8-12C8-413E-9CC7-BF250EE0F961}" name="R_should_be" dataDxfId="53"/>
-    <tableColumn id="13" xr3:uid="{29D5B8D2-9715-4A57-B62E-A9C204755268}" name="M_program" dataDxfId="52"/>
-    <tableColumn id="14" xr3:uid="{F9951DCF-AEF5-4B93-8D8B-B1E0768DD0D7}" name="M_should_be" dataDxfId="51"/>
-    <tableColumn id="15" xr3:uid="{6E3B4665-570E-4C16-91E2-C0362452FCB0}" name="Uncertainty" dataDxfId="50"/>
+    <tableColumn id="1" xr3:uid="{40739C4F-7926-4D30-85E5-B1C70F07CC58}" name="Year" dataDxfId="62"/>
+    <tableColumn id="2" xr3:uid="{B9C436A4-C86A-4176-A748-A2EB263F2366}" name="Month" dataDxfId="61"/>
+    <tableColumn id="3" xr3:uid="{A23B2393-E795-4522-B348-48FA029168BF}" name="Day" dataDxfId="60"/>
+    <tableColumn id="4" xr3:uid="{12BC92B3-8400-4788-87F1-C45E3B3C0FF7}" name="Hour" dataDxfId="59"/>
+    <tableColumn id="5" xr3:uid="{5C484A21-4EB7-4A52-BDA8-9C8F6B385A2E}" name="Minute" dataDxfId="58"/>
+    <tableColumn id="6" xr3:uid="{43B4D4A3-BD23-4372-85F8-D1DC673B257B}" name="Column" dataDxfId="57"/>
+    <tableColumn id="7" xr3:uid="{13F1C5B1-12D8-497A-995C-A3C1C8F4EBBD}" name="Measurment" dataDxfId="56"/>
+    <tableColumn id="8" xr3:uid="{EEDF6678-0BA1-494A-B56E-3F4EE6168405}" name="Sensor" dataDxfId="55"/>
+    <tableColumn id="9" xr3:uid="{901111A6-DC2D-4708-9245-52416AA6A1AD}" name="Serial Number" dataDxfId="54"/>
+    <tableColumn id="10" xr3:uid="{ADA0E13A-487E-4D6B-9E5A-1B9264AF29CF}" name="Metric" dataDxfId="53"/>
+    <tableColumn id="11" xr3:uid="{AB1994B9-EB06-4647-987F-1CB1F7987349}" name="R_program" dataDxfId="52"/>
+    <tableColumn id="12" xr3:uid="{7FDD4AF8-12C8-413E-9CC7-BF250EE0F961}" name="R_should_be" dataDxfId="51"/>
+    <tableColumn id="13" xr3:uid="{29D5B8D2-9715-4A57-B62E-A9C204755268}" name="M_program" dataDxfId="50"/>
+    <tableColumn id="14" xr3:uid="{F9951DCF-AEF5-4B93-8D8B-B1E0768DD0D7}" name="M_should_be" dataDxfId="49"/>
+    <tableColumn id="15" xr3:uid="{6E3B4665-570E-4C16-91E2-C0362452FCB0}" name="Uncertainty" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E12E6B68-D4AA-4DCB-952B-825D37B874DE}" name="Table6" displayName="Table6" ref="A1:O7" totalsRowShown="0" headerRowDxfId="28" dataDxfId="29" headerRowBorderDxfId="46" tableBorderDxfId="47" totalsRowBorderDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E12E6B68-D4AA-4DCB-952B-825D37B874DE}" name="Table6" displayName="Table6" ref="A1:O7" totalsRowShown="0" headerRowDxfId="47" dataDxfId="45" headerRowBorderDxfId="46" tableBorderDxfId="44" totalsRowBorderDxfId="43">
   <autoFilter ref="A1:O7" xr:uid="{E12E6B68-D4AA-4DCB-952B-825D37B874DE}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{0F1A7524-DA72-4FD5-A73D-940828E75147}" name="Year" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{C16CE2B4-47CD-4ADA-93DF-677A69E7F1AC}" name="Month" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{738038BF-BC5C-42F1-B28F-2484A4655B98}" name="Day" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{E2847807-43F5-4623-812F-144C1EB6142B}" name="Hour" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{02D4F4F5-DB5C-4D67-932D-3D9A31A69D79}" name="Minute" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{3AEEC5D7-D4FE-4911-B65C-EEAB293DE665}" name="Column" dataDxfId="39"/>
-    <tableColumn id="7" xr3:uid="{C37A3973-F165-499C-91EF-AC400D75F0FF}" name="Measurment" dataDxfId="38"/>
-    <tableColumn id="8" xr3:uid="{3D6C50E0-E4FE-4AD0-B098-0B427D60F012}" name="Sensor" dataDxfId="37"/>
-    <tableColumn id="9" xr3:uid="{060CB63C-FAFA-43C3-9B22-D6390526F437}" name="Serial Number" dataDxfId="36"/>
-    <tableColumn id="10" xr3:uid="{621438F1-C1FC-44E0-85D9-DD61AFD019DC}" name="Metric" dataDxfId="35"/>
-    <tableColumn id="11" xr3:uid="{4ABC7FD1-2D78-4B75-9B92-BB7CE33A0C28}" name="R_program" dataDxfId="34"/>
-    <tableColumn id="12" xr3:uid="{CBDC9302-E79D-44E0-BF54-08BA95A67F07}" name="R_should_be" dataDxfId="33"/>
-    <tableColumn id="13" xr3:uid="{35CBBAD8-9C3F-4D3C-B8C1-74F02A935C2E}" name="M_program" dataDxfId="32"/>
-    <tableColumn id="14" xr3:uid="{75DDF4A8-32B5-42A6-8B09-5F7D14ADA471}" name="M_should_be" dataDxfId="31"/>
-    <tableColumn id="15" xr3:uid="{C7D1FB57-AD31-4730-9364-B08F0DDF93E5}" name="Uncertainty" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{0F1A7524-DA72-4FD5-A73D-940828E75147}" name="Year" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{C16CE2B4-47CD-4ADA-93DF-677A69E7F1AC}" name="Month" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{738038BF-BC5C-42F1-B28F-2484A4655B98}" name="Day" dataDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{E2847807-43F5-4623-812F-144C1EB6142B}" name="Hour" dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{02D4F4F5-DB5C-4D67-932D-3D9A31A69D79}" name="Minute" dataDxfId="38"/>
+    <tableColumn id="6" xr3:uid="{3AEEC5D7-D4FE-4911-B65C-EEAB293DE665}" name="Column" dataDxfId="37"/>
+    <tableColumn id="7" xr3:uid="{C37A3973-F165-499C-91EF-AC400D75F0FF}" name="Measurment" dataDxfId="36"/>
+    <tableColumn id="8" xr3:uid="{3D6C50E0-E4FE-4AD0-B098-0B427D60F012}" name="Sensor" dataDxfId="35"/>
+    <tableColumn id="9" xr3:uid="{060CB63C-FAFA-43C3-9B22-D6390526F437}" name="Serial Number" dataDxfId="34"/>
+    <tableColumn id="10" xr3:uid="{621438F1-C1FC-44E0-85D9-DD61AFD019DC}" name="Metric" dataDxfId="33"/>
+    <tableColumn id="11" xr3:uid="{4ABC7FD1-2D78-4B75-9B92-BB7CE33A0C28}" name="R_program" dataDxfId="32"/>
+    <tableColumn id="12" xr3:uid="{CBDC9302-E79D-44E0-BF54-08BA95A67F07}" name="R_should_be" dataDxfId="31"/>
+    <tableColumn id="13" xr3:uid="{35CBBAD8-9C3F-4D3C-B8C1-74F02A935C2E}" name="M_program" dataDxfId="30"/>
+    <tableColumn id="14" xr3:uid="{75DDF4A8-32B5-42A6-8B09-5F7D14ADA471}" name="M_should_be" dataDxfId="29"/>
+    <tableColumn id="15" xr3:uid="{C7D1FB57-AD31-4730-9364-B08F0DDF93E5}" name="Uncertainty" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{711D5B68-1238-449A-8645-2AC9ACAF458A}" name="Table7" displayName="Table7" ref="A1:O15" totalsRowShown="0" headerRowDxfId="8" dataDxfId="9" headerRowBorderDxfId="26" tableBorderDxfId="27" totalsRowBorderDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{711D5B68-1238-449A-8645-2AC9ACAF458A}" name="Table7" displayName="Table7" ref="A1:O15" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <autoFilter ref="A1:O15" xr:uid="{711D5B68-1238-449A-8645-2AC9ACAF458A}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{7FBAA725-EAC4-4982-9B93-C956A7A3E634}" name="Year" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{52CC427C-2BEF-4A6D-BF35-3CDD7313B8AC}" name="Month" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{3437A29F-CE8B-494F-9D7E-71E71F9D0676}" name="Day" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{ACEDF893-F34D-40C7-B4DB-AF1A3CA637F2}" name="Hour" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{2FC8642F-733E-4967-B15E-E77396073039}" name="Minute" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{C972ABA6-682B-48E5-AA31-BA5AF7A3E232}" name="Column" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{B6D9E56D-99EA-4E3B-9F1A-A9972A90D9EC}" name="Measurment" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{9D781722-4C1D-4249-9704-F163D9CFD39A}" name="Sensor" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{A632F4D8-D2C4-49F6-B745-371EB460F23B}" name="Serial Number" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{D4A950AC-F2C9-43B3-B532-A804EA572E6A}" name="Metric" dataDxfId="15"/>
-    <tableColumn id="11" xr3:uid="{9C21F125-C9DF-41EB-BA48-74D164FB3CC7}" name="R_program" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{96C0D3D8-FCA6-4590-915F-0FA20D30EBAA}" name="R_should_be" dataDxfId="13"/>
-    <tableColumn id="13" xr3:uid="{C457721C-3D7C-45B3-985B-D3C41AA11179}" name="M_program" dataDxfId="12"/>
-    <tableColumn id="14" xr3:uid="{1E8D3234-A498-4357-A64F-1F44B07D10A9}" name="M_should_be" dataDxfId="11"/>
-    <tableColumn id="15" xr3:uid="{429A4912-DA0F-4AE4-B07D-0546AA3A41D9}" name="Uncertainty" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{7FBAA725-EAC4-4982-9B93-C956A7A3E634}" name="Year" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{52CC427C-2BEF-4A6D-BF35-3CDD7313B8AC}" name="Month" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{3437A29F-CE8B-494F-9D7E-71E71F9D0676}" name="Day" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{ACEDF893-F34D-40C7-B4DB-AF1A3CA637F2}" name="Hour" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{2FC8642F-733E-4967-B15E-E77396073039}" name="Minute" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{C972ABA6-682B-48E5-AA31-BA5AF7A3E232}" name="Column" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{B6D9E56D-99EA-4E3B-9F1A-A9972A90D9EC}" name="Measurment" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{9D781722-4C1D-4249-9704-F163D9CFD39A}" name="Sensor" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{A632F4D8-D2C4-49F6-B745-371EB460F23B}" name="Serial Number" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{D4A950AC-F2C9-43B3-B532-A804EA572E6A}" name="Metric" dataDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{9C21F125-C9DF-41EB-BA48-74D164FB3CC7}" name="R_program" dataDxfId="12"/>
+    <tableColumn id="12" xr3:uid="{96C0D3D8-FCA6-4590-915F-0FA20D30EBAA}" name="R_should_be" dataDxfId="11"/>
+    <tableColumn id="13" xr3:uid="{C457721C-3D7C-45B3-985B-D3C41AA11179}" name="M_program" dataDxfId="10"/>
+    <tableColumn id="14" xr3:uid="{1E8D3234-A498-4357-A64F-1F44B07D10A9}" name="M_should_be" dataDxfId="9"/>
+    <tableColumn id="15" xr3:uid="{429A4912-DA0F-4AE4-B07D-0546AA3A41D9}" name="Uncertainty" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C7E29289-7DBE-4911-BB05-F5A795234529}" name="Table8" displayName="Table8" ref="A1:O4" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C7E29289-7DBE-4911-BB05-F5A795234529}" name="Table8" displayName="Table8" ref="A1:O4" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5" totalsRowBorderDxfId="4">
   <autoFilter ref="A1:O4" xr:uid="{C7E29289-7DBE-4911-BB05-F5A795234529}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{E8E5A895-2227-412A-84E3-D47A395B3551}" name="Year"/>
@@ -4719,7 +4823,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{82F79206-9F29-4A8C-B33F-D953AB903B1F}" name="Table9" displayName="Table9" ref="A1:O4" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="2" tableBorderDxfId="3" totalsRowBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{82F79206-9F29-4A8C-B33F-D953AB903B1F}" name="Table9" displayName="Table9" ref="A1:O4" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2" tableBorderDxfId="1" totalsRowBorderDxfId="0">
   <autoFilter ref="A1:O4" xr:uid="{82F79206-9F29-4A8C-B33F-D953AB903B1F}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{E8D883CD-EE32-4CCE-B047-9F700CE99109}" name="Year"/>
@@ -5076,18 +5180,18 @@
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="56" t="s">
+      <c r="D1" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="58" t="s">
+      <c r="E1" s="71"/>
+      <c r="F1" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="59"/>
-      <c r="H1" s="57" t="s">
+      <c r="G1" s="74"/>
+      <c r="H1" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="57"/>
+      <c r="I1" s="72"/>
       <c r="J1" s="46"/>
       <c r="K1" s="13"/>
       <c r="L1" s="5" t="s">
@@ -13729,6 +13833,262 @@
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA7BD733-D02F-4818-9D6A-E6E21FE780ED}">
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="75" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1" s="75" t="s">
+        <v>213</v>
+      </c>
+      <c r="C1" s="75" t="s">
+        <v>225</v>
+      </c>
+      <c r="D1" s="75" t="s">
+        <v>226</v>
+      </c>
+      <c r="E1" s="75" t="s">
+        <v>228</v>
+      </c>
+      <c r="F1" s="75" t="s">
+        <v>230</v>
+      </c>
+      <c r="G1" s="75" t="s">
+        <v>222</v>
+      </c>
+      <c r="H1" s="75" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="54" t="s">
+        <v>257</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="54" t="s">
+        <v>258</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="54" t="s">
+        <v>260</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="54" t="s">
+        <v>261</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="54" t="s">
+        <v>262</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="54" t="s">
+        <v>263</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="54" t="s">
+        <v>265</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>14</v>
+      </c>
+      <c r="F10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="54" t="s">
+        <v>266</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="54" t="s">
+        <v>267</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+      <c r="D13">
+        <v>11</v>
+      </c>
+      <c r="E13">
+        <v>16</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="54" t="s">
+        <v>269</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+      <c r="D14">
+        <v>11</v>
+      </c>
+      <c r="E14">
+        <v>16</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="54" t="s">
+        <v>270</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>7</v>
+      </c>
+      <c r="D15">
+        <v>11</v>
+      </c>
+      <c r="E15">
+        <v>16</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -15696,6 +16056,9 @@
       <c r="G54">
         <v>7</v>
       </c>
+      <c r="H54" t="s">
+        <v>225</v>
+      </c>
       <c r="I54" t="s">
         <v>247</v>
       </c>
@@ -15740,6 +16103,9 @@
       <c r="G55">
         <v>8</v>
       </c>
+      <c r="H55" t="s">
+        <v>225</v>
+      </c>
       <c r="I55" t="s">
         <v>247</v>
       </c>
@@ -15772,6 +16138,9 @@
       <c r="G56">
         <v>9</v>
       </c>
+      <c r="H56" t="s">
+        <v>225</v>
+      </c>
       <c r="I56" t="s">
         <v>247</v>
       </c>
@@ -15819,6 +16188,9 @@
       <c r="G57">
         <v>10</v>
       </c>
+      <c r="H57" t="s">
+        <v>225</v>
+      </c>
       <c r="I57" t="s">
         <v>247</v>
       </c>
@@ -15851,6 +16223,9 @@
       <c r="G58">
         <v>11</v>
       </c>
+      <c r="H58" t="s">
+        <v>226</v>
+      </c>
       <c r="I58" t="s">
         <v>214</v>
       </c>
@@ -15895,6 +16270,9 @@
       <c r="G59">
         <v>12</v>
       </c>
+      <c r="H59" t="s">
+        <v>226</v>
+      </c>
       <c r="I59" t="s">
         <v>214</v>
       </c>
@@ -15927,6 +16305,9 @@
       <c r="G60">
         <v>13</v>
       </c>
+      <c r="H60" t="s">
+        <v>226</v>
+      </c>
       <c r="I60" t="s">
         <v>214</v>
       </c>
@@ -15974,6 +16355,9 @@
       <c r="G61">
         <v>14</v>
       </c>
+      <c r="H61" t="s">
+        <v>226</v>
+      </c>
       <c r="I61" t="s">
         <v>214</v>
       </c>
@@ -18051,6 +18435,9 @@
       <c r="G111">
         <v>2</v>
       </c>
+      <c r="H111" t="s">
+        <v>225</v>
+      </c>
       <c r="I111" t="s">
         <v>37</v>
       </c>
@@ -18212,6 +18599,9 @@
       <c r="G115">
         <v>2</v>
       </c>
+      <c r="H115" t="s">
+        <v>225</v>
+      </c>
       <c r="I115" t="s">
         <v>37</v>
       </c>
@@ -18256,6 +18646,9 @@
       <c r="G116">
         <v>3</v>
       </c>
+      <c r="H116" t="s">
+        <v>226</v>
+      </c>
       <c r="I116" t="s">
         <v>86</v>
       </c>
@@ -18889,6 +19282,9 @@
       <c r="G131">
         <v>2</v>
       </c>
+      <c r="H131" t="s">
+        <v>225</v>
+      </c>
       <c r="I131" t="s">
         <v>37</v>
       </c>
@@ -19024,6 +19420,9 @@
       <c r="G134">
         <v>2</v>
       </c>
+      <c r="H134" t="s">
+        <v>225</v>
+      </c>
       <c r="I134" t="s">
         <v>37</v>
       </c>
@@ -19159,6 +19558,9 @@
       <c r="G137">
         <v>2</v>
       </c>
+      <c r="H137" t="s">
+        <v>225</v>
+      </c>
       <c r="I137" t="s">
         <v>37</v>
       </c>
@@ -19294,6 +19696,9 @@
       <c r="G140">
         <v>2</v>
       </c>
+      <c r="H140" t="s">
+        <v>225</v>
+      </c>
       <c r="I140" t="s">
         <v>37</v>
       </c>
@@ -19429,6 +19834,9 @@
       <c r="G143">
         <v>2</v>
       </c>
+      <c r="H143" t="s">
+        <v>225</v>
+      </c>
       <c r="I143" t="s">
         <v>37</v>
       </c>
@@ -19564,6 +19972,9 @@
       </c>
       <c r="G146">
         <v>2</v>
+      </c>
+      <c r="H146" t="s">
+        <v>225</v>
       </c>
       <c r="I146" t="s">
         <v>37</v>
@@ -19656,819 +20067,837 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="60" t="s">
         <v>201</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="61" t="s">
         <v>202</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="C1" s="61" t="s">
         <v>203</v>
       </c>
-      <c r="D1" s="65" t="s">
+      <c r="D1" s="61" t="s">
         <v>204</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="61" t="s">
         <v>205</v>
       </c>
-      <c r="F1" s="65" t="s">
+      <c r="F1" s="61" t="s">
         <v>206</v>
       </c>
-      <c r="G1" s="65" t="s">
+      <c r="G1" s="61" t="s">
         <v>207</v>
       </c>
-      <c r="H1" s="65" t="s">
+      <c r="H1" s="61" t="s">
         <v>208</v>
       </c>
-      <c r="I1" s="65" t="s">
+      <c r="I1" s="61" t="s">
         <v>209</v>
       </c>
-      <c r="J1" s="65" t="s">
+      <c r="J1" s="61" t="s">
         <v>239</v>
       </c>
-      <c r="K1" s="65" t="s">
+      <c r="K1" s="61" t="s">
         <v>210</v>
       </c>
-      <c r="L1" s="65" t="s">
+      <c r="L1" s="61" t="s">
         <v>211</v>
       </c>
-      <c r="M1" s="65" t="s">
+      <c r="M1" s="61" t="s">
         <v>245</v>
       </c>
-      <c r="N1" s="65" t="s">
+      <c r="N1" s="61" t="s">
         <v>246</v>
       </c>
-      <c r="O1" s="65" t="s">
+      <c r="O1" s="61" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="61">
+      <c r="A2" s="57">
         <v>2015</v>
       </c>
-      <c r="B2" s="61">
+      <c r="B2" s="57">
         <v>9</v>
       </c>
-      <c r="C2" s="61">
+      <c r="C2" s="57">
         <v>30</v>
       </c>
-      <c r="D2" s="62">
+      <c r="D2" s="58">
         <v>23</v>
       </c>
-      <c r="E2" s="62">
-        <v>0</v>
-      </c>
-      <c r="F2" s="62">
-        <v>1</v>
-      </c>
-      <c r="G2" s="63" t="s">
+      <c r="E2" s="58">
+        <v>0</v>
+      </c>
+      <c r="F2" s="58">
+        <v>1</v>
+      </c>
+      <c r="G2" s="59" t="s">
         <v>213</v>
       </c>
-      <c r="H2" s="63" t="s">
+      <c r="H2" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="62" t="s">
+      <c r="I2" s="58" t="s">
         <v>216</v>
       </c>
-      <c r="J2" s="63"/>
-      <c r="K2" s="63">
+      <c r="J2" s="59" t="s">
+        <v>242</v>
+      </c>
+      <c r="K2" s="59">
         <v>8.3229989429791296</v>
       </c>
-      <c r="L2" s="63">
+      <c r="L2" s="59">
         <v>8.3055000000000003</v>
       </c>
-      <c r="M2" s="61">
+      <c r="M2" s="57">
         <v>120.149</v>
       </c>
-      <c r="N2" s="61">
+      <c r="N2" s="57">
         <v>120.40214315814799</v>
       </c>
-      <c r="O2" s="63">
+      <c r="O2" s="59">
         <v>1.6168725409881399</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="60">
+      <c r="A3" s="56">
         <v>2016</v>
       </c>
-      <c r="B3" s="60">
-        <v>1</v>
-      </c>
-      <c r="C3" s="60">
-        <v>1</v>
-      </c>
-      <c r="D3" s="60">
-        <v>0</v>
-      </c>
-      <c r="E3" s="60">
-        <v>1</v>
-      </c>
-      <c r="F3" s="60">
-        <v>1</v>
-      </c>
-      <c r="G3" s="60" t="s">
+      <c r="B3" s="56">
+        <v>1</v>
+      </c>
+      <c r="C3" s="56">
+        <v>1</v>
+      </c>
+      <c r="D3" s="56">
+        <v>0</v>
+      </c>
+      <c r="E3" s="56">
+        <v>1</v>
+      </c>
+      <c r="F3" s="56">
+        <v>1</v>
+      </c>
+      <c r="G3" s="56" t="s">
         <v>213</v>
       </c>
-      <c r="H3" s="60" t="s">
+      <c r="H3" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="60" t="s">
+      <c r="I3" s="56" t="s">
         <v>216</v>
       </c>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60">
+      <c r="J3" s="59" t="s">
+        <v>242</v>
+      </c>
+      <c r="K3" s="56">
         <v>8.3229989429791296</v>
       </c>
-      <c r="L3" s="60">
+      <c r="L3" s="56">
         <v>8.2956000000000003</v>
       </c>
-      <c r="M3" s="60">
+      <c r="M3" s="56">
         <v>120.149</v>
       </c>
-      <c r="N3" s="60">
+      <c r="N3" s="56">
         <v>120.545831525146</v>
       </c>
-      <c r="O3" s="60">
+      <c r="O3" s="56">
         <v>1.6188010157323101</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="60">
+      <c r="A4" s="56">
         <v>2017</v>
       </c>
-      <c r="B4" s="60">
-        <v>1</v>
-      </c>
-      <c r="C4" s="60">
-        <v>1</v>
-      </c>
-      <c r="D4" s="60">
-        <v>0</v>
-      </c>
-      <c r="E4" s="60">
-        <v>1</v>
-      </c>
-      <c r="F4" s="60">
-        <v>1</v>
-      </c>
-      <c r="G4" s="60" t="s">
+      <c r="B4" s="56">
+        <v>1</v>
+      </c>
+      <c r="C4" s="56">
+        <v>1</v>
+      </c>
+      <c r="D4" s="56">
+        <v>0</v>
+      </c>
+      <c r="E4" s="56">
+        <v>1</v>
+      </c>
+      <c r="F4" s="56">
+        <v>1</v>
+      </c>
+      <c r="G4" s="56" t="s">
         <v>213</v>
       </c>
-      <c r="H4" s="60" t="s">
+      <c r="H4" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="60" t="s">
+      <c r="I4" s="56" t="s">
         <v>216</v>
       </c>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60">
+      <c r="J4" s="59" t="s">
+        <v>242</v>
+      </c>
+      <c r="K4" s="56">
         <v>8.3229989429791296</v>
       </c>
-      <c r="L4" s="60">
+      <c r="L4" s="56">
         <v>8.2759</v>
       </c>
-      <c r="M4" s="60">
+      <c r="M4" s="56">
         <v>120.149</v>
       </c>
-      <c r="N4" s="60">
+      <c r="N4" s="56">
         <v>120.832779516427</v>
       </c>
-      <c r="O4" s="60">
+      <c r="O4" s="56">
         <v>1.6226717989921</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="61">
+      <c r="A5" s="57">
         <v>2017</v>
       </c>
-      <c r="B5" s="61">
+      <c r="B5" s="57">
         <v>8</v>
       </c>
-      <c r="C5" s="61">
-        <v>1</v>
-      </c>
-      <c r="D5" s="61">
+      <c r="C5" s="57">
+        <v>1</v>
+      </c>
+      <c r="D5" s="57">
         <v>11</v>
       </c>
-      <c r="E5" s="61">
+      <c r="E5" s="57">
         <v>40</v>
       </c>
-      <c r="F5" s="61">
-        <v>1</v>
-      </c>
-      <c r="G5" s="61" t="s">
+      <c r="F5" s="57">
+        <v>1</v>
+      </c>
+      <c r="G5" s="57" t="s">
         <v>213</v>
       </c>
-      <c r="H5" s="61" t="s">
+      <c r="H5" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="61" t="s">
+      <c r="I5" s="57" t="s">
         <v>217</v>
       </c>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61">
+      <c r="J5" s="59" t="s">
+        <v>242</v>
+      </c>
+      <c r="K5" s="57">
         <v>7.0324971694198899</v>
       </c>
-      <c r="L5" s="61">
+      <c r="L5" s="57">
         <v>7.0361000000000002</v>
       </c>
-      <c r="M5" s="61">
+      <c r="M5" s="57">
         <v>142.197</v>
       </c>
-      <c r="N5" s="61">
+      <c r="N5" s="57">
         <v>142.12418811557501</v>
       </c>
-      <c r="O5" s="61">
+      <c r="O5" s="57">
         <v>1.66982297226244</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="61">
+      <c r="A6" s="57">
         <v>2018</v>
       </c>
-      <c r="B6" s="61">
-        <v>1</v>
-      </c>
-      <c r="C6" s="61">
-        <v>1</v>
-      </c>
-      <c r="D6" s="61">
-        <v>0</v>
-      </c>
-      <c r="E6" s="61">
-        <v>1</v>
-      </c>
-      <c r="F6" s="61">
-        <v>1</v>
-      </c>
-      <c r="G6" s="61" t="s">
+      <c r="B6" s="57">
+        <v>1</v>
+      </c>
+      <c r="C6" s="57">
+        <v>1</v>
+      </c>
+      <c r="D6" s="57">
+        <v>0</v>
+      </c>
+      <c r="E6" s="57">
+        <v>1</v>
+      </c>
+      <c r="F6" s="57">
+        <v>1</v>
+      </c>
+      <c r="G6" s="57" t="s">
         <v>213</v>
       </c>
-      <c r="H6" s="61" t="s">
+      <c r="H6" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="61" t="s">
+      <c r="I6" s="57" t="s">
         <v>217</v>
       </c>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61">
+      <c r="J6" s="59" t="s">
+        <v>242</v>
+      </c>
+      <c r="K6" s="57">
         <v>7.0324971694198899</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="57">
         <v>7.0320999999999998</v>
       </c>
-      <c r="M6" s="61">
+      <c r="M6" s="57">
         <v>142.197</v>
       </c>
-      <c r="N6" s="61">
+      <c r="N6" s="57">
         <v>142.20503121400401</v>
       </c>
-      <c r="O6" s="61">
+      <c r="O6" s="57">
         <v>1.67075591548251</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="60">
+      <c r="A7" s="56">
         <v>2019</v>
       </c>
-      <c r="B7" s="60">
-        <v>1</v>
-      </c>
-      <c r="C7" s="60">
-        <v>1</v>
-      </c>
-      <c r="D7" s="60">
-        <v>0</v>
-      </c>
-      <c r="E7" s="60">
-        <v>1</v>
-      </c>
-      <c r="F7" s="60">
-        <v>1</v>
-      </c>
-      <c r="G7" s="60" t="s">
+      <c r="B7" s="56">
+        <v>1</v>
+      </c>
+      <c r="C7" s="56">
+        <v>1</v>
+      </c>
+      <c r="D7" s="56">
+        <v>0</v>
+      </c>
+      <c r="E7" s="56">
+        <v>1</v>
+      </c>
+      <c r="F7" s="56">
+        <v>1</v>
+      </c>
+      <c r="G7" s="56" t="s">
         <v>213</v>
       </c>
-      <c r="H7" s="60" t="s">
+      <c r="H7" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="I7" s="60" t="s">
+      <c r="I7" s="56" t="s">
         <v>217</v>
       </c>
-      <c r="J7" s="60"/>
-      <c r="K7" s="60">
+      <c r="J7" s="59" t="s">
+        <v>242</v>
+      </c>
+      <c r="K7" s="56">
         <v>7.0324971694198899</v>
       </c>
-      <c r="L7" s="60">
+      <c r="L7" s="56">
         <v>7.0243000000000002</v>
       </c>
-      <c r="M7" s="60">
+      <c r="M7" s="56">
         <v>142.197</v>
       </c>
-      <c r="N7" s="60">
+      <c r="N7" s="56">
         <v>142.362940079439</v>
       </c>
-      <c r="O7" s="60">
+      <c r="O7" s="56">
         <v>1.67262493287749</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="60">
+      <c r="A8" s="56">
         <v>2020</v>
       </c>
-      <c r="B8" s="60">
-        <v>1</v>
-      </c>
-      <c r="C8" s="60">
-        <v>1</v>
-      </c>
-      <c r="D8" s="60">
-        <v>0</v>
-      </c>
-      <c r="E8" s="60">
-        <v>1</v>
-      </c>
-      <c r="F8" s="60">
-        <v>1</v>
-      </c>
-      <c r="G8" s="60" t="s">
+      <c r="B8" s="56">
+        <v>1</v>
+      </c>
+      <c r="C8" s="56">
+        <v>1</v>
+      </c>
+      <c r="D8" s="56">
+        <v>0</v>
+      </c>
+      <c r="E8" s="56">
+        <v>1</v>
+      </c>
+      <c r="F8" s="56">
+        <v>1</v>
+      </c>
+      <c r="G8" s="56" t="s">
         <v>213</v>
       </c>
-      <c r="H8" s="60" t="s">
+      <c r="H8" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="60" t="s">
+      <c r="I8" s="56" t="s">
         <v>217</v>
       </c>
-      <c r="J8" s="60"/>
-      <c r="K8" s="60">
+      <c r="J8" s="59" t="s">
+        <v>242</v>
+      </c>
+      <c r="K8" s="56">
         <v>7.0324971694198899</v>
       </c>
-      <c r="L8" s="60">
+      <c r="L8" s="56">
         <v>7.0164</v>
       </c>
-      <c r="M8" s="60">
+      <c r="M8" s="56">
         <v>142.197</v>
       </c>
-      <c r="N8" s="60">
+      <c r="N8" s="56">
         <v>142.5232312867</v>
       </c>
-      <c r="O8" s="60">
+      <c r="O8" s="56">
         <v>1.67449813656697</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="61">
+      <c r="A9" s="57">
         <v>2020</v>
       </c>
-      <c r="B9" s="61">
+      <c r="B9" s="57">
         <v>8</v>
       </c>
-      <c r="C9" s="61">
-        <v>1</v>
-      </c>
-      <c r="D9" s="61">
-        <v>0</v>
-      </c>
-      <c r="E9" s="61">
-        <v>1</v>
-      </c>
-      <c r="F9" s="61">
-        <v>1</v>
-      </c>
-      <c r="G9" s="61" t="s">
+      <c r="C9" s="57">
+        <v>1</v>
+      </c>
+      <c r="D9" s="57">
+        <v>0</v>
+      </c>
+      <c r="E9" s="57">
+        <v>1</v>
+      </c>
+      <c r="F9" s="57">
+        <v>1</v>
+      </c>
+      <c r="G9" s="57" t="s">
         <v>213</v>
       </c>
-      <c r="H9" s="61" t="s">
+      <c r="H9" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="I9" s="61" t="s">
+      <c r="I9" s="57" t="s">
         <v>217</v>
       </c>
-      <c r="J9" s="61"/>
-      <c r="K9" s="61">
-        <v>1000</v>
-      </c>
-      <c r="L9" s="61">
+      <c r="J9" s="59" t="s">
+        <v>242</v>
+      </c>
+      <c r="K9" s="57">
+        <v>1000</v>
+      </c>
+      <c r="L9" s="57">
         <v>7.0164</v>
       </c>
-      <c r="M9" s="61">
-        <v>1</v>
-      </c>
-      <c r="N9" s="61">
+      <c r="M9" s="57">
+        <v>1</v>
+      </c>
+      <c r="N9" s="57">
         <v>142.5232312867</v>
       </c>
-      <c r="O9" s="61">
+      <c r="O9" s="57">
         <v>1.67449813656697</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="60">
+      <c r="A10" s="56">
         <v>2021</v>
       </c>
-      <c r="B10" s="60">
-        <v>1</v>
-      </c>
-      <c r="C10" s="60">
-        <v>1</v>
-      </c>
-      <c r="D10" s="60">
-        <v>0</v>
-      </c>
-      <c r="E10" s="60">
-        <v>1</v>
-      </c>
-      <c r="F10" s="60">
-        <v>1</v>
-      </c>
-      <c r="G10" s="60" t="s">
+      <c r="B10" s="56">
+        <v>1</v>
+      </c>
+      <c r="C10" s="56">
+        <v>1</v>
+      </c>
+      <c r="D10" s="56">
+        <v>0</v>
+      </c>
+      <c r="E10" s="56">
+        <v>1</v>
+      </c>
+      <c r="F10" s="56">
+        <v>1</v>
+      </c>
+      <c r="G10" s="56" t="s">
         <v>213</v>
       </c>
-      <c r="H10" s="60" t="s">
+      <c r="H10" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="60" t="s">
+      <c r="I10" s="56" t="s">
         <v>217</v>
       </c>
-      <c r="J10" s="60"/>
-      <c r="K10" s="60">
-        <v>1000</v>
-      </c>
-      <c r="L10" s="60">
+      <c r="J10" s="59" t="s">
+        <v>242</v>
+      </c>
+      <c r="K10" s="56">
+        <v>1000</v>
+      </c>
+      <c r="L10" s="56">
         <v>6.9976000000000003</v>
       </c>
-      <c r="M10" s="60">
-        <v>1</v>
-      </c>
-      <c r="N10" s="60">
+      <c r="M10" s="56">
+        <v>1</v>
+      </c>
+      <c r="N10" s="56">
         <v>142.906139247742</v>
       </c>
-      <c r="O10" s="60">
+      <c r="O10" s="56">
         <v>1.80205774681044</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="60">
+      <c r="A11" s="56">
         <v>2021</v>
       </c>
-      <c r="B11" s="60">
+      <c r="B11" s="56">
         <v>7</v>
       </c>
-      <c r="C11" s="60">
-        <v>1</v>
-      </c>
-      <c r="D11" s="60">
-        <v>0</v>
-      </c>
-      <c r="E11" s="60">
-        <v>1</v>
-      </c>
-      <c r="F11" s="60">
-        <v>1</v>
-      </c>
-      <c r="G11" s="60" t="s">
+      <c r="C11" s="56">
+        <v>1</v>
+      </c>
+      <c r="D11" s="56">
+        <v>0</v>
+      </c>
+      <c r="E11" s="56">
+        <v>1</v>
+      </c>
+      <c r="F11" s="56">
+        <v>1</v>
+      </c>
+      <c r="G11" s="56" t="s">
         <v>213</v>
       </c>
-      <c r="H11" s="60" t="s">
+      <c r="H11" s="56" t="s">
         <v>248</v>
       </c>
-      <c r="I11" s="60">
+      <c r="I11" s="56">
         <v>4764</v>
       </c>
-      <c r="J11" s="60"/>
-      <c r="K11" s="60">
-        <v>1000</v>
-      </c>
-      <c r="L11" s="60">
+      <c r="J11" s="56"/>
+      <c r="K11" s="56">
+        <v>1000</v>
+      </c>
+      <c r="L11" s="56">
         <v>16.6112</v>
       </c>
-      <c r="M11" s="60">
-        <v>1</v>
-      </c>
-      <c r="N11" s="60">
+      <c r="M11" s="56">
+        <v>1</v>
+      </c>
+      <c r="N11" s="56">
         <v>60.200346753997302</v>
       </c>
-      <c r="O11" s="60">
+      <c r="O11" s="56">
         <v>0.76827735566056199</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="61">
+      <c r="A12" s="57">
         <v>2021</v>
       </c>
-      <c r="B12" s="61">
+      <c r="B12" s="57">
         <v>7</v>
       </c>
-      <c r="C12" s="61">
-        <v>1</v>
-      </c>
-      <c r="D12" s="61">
-        <v>0</v>
-      </c>
-      <c r="E12" s="61">
-        <v>1</v>
-      </c>
-      <c r="F12" s="61">
+      <c r="C12" s="57">
+        <v>1</v>
+      </c>
+      <c r="D12" s="57">
+        <v>0</v>
+      </c>
+      <c r="E12" s="57">
+        <v>1</v>
+      </c>
+      <c r="F12" s="57">
         <v>4</v>
       </c>
-      <c r="G12" s="61" t="s">
+      <c r="G12" s="57" t="s">
         <v>213</v>
       </c>
-      <c r="H12" s="61" t="s">
+      <c r="H12" s="57" t="s">
         <v>248</v>
       </c>
-      <c r="I12" s="61">
+      <c r="I12" s="57">
         <v>4764</v>
       </c>
-      <c r="J12" s="61" t="s">
+      <c r="J12" s="57" t="s">
         <v>242</v>
       </c>
-      <c r="K12" s="61"/>
-      <c r="L12" s="61"/>
-      <c r="M12" s="61"/>
-      <c r="N12" s="61"/>
-      <c r="O12" s="61"/>
+      <c r="K12" s="57"/>
+      <c r="L12" s="57"/>
+      <c r="M12" s="57"/>
+      <c r="N12" s="57"/>
+      <c r="O12" s="57"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="60">
+      <c r="A13" s="56">
         <v>2022</v>
       </c>
-      <c r="B13" s="60">
+      <c r="B13" s="56">
         <v>7</v>
       </c>
-      <c r="C13" s="60">
+      <c r="C13" s="56">
         <v>19</v>
       </c>
-      <c r="D13" s="60">
+      <c r="D13" s="56">
         <v>12</v>
       </c>
-      <c r="E13" s="60">
+      <c r="E13" s="56">
         <v>46</v>
       </c>
-      <c r="F13" s="60">
-        <v>1</v>
-      </c>
-      <c r="G13" s="60" t="s">
+      <c r="F13" s="56">
+        <v>1</v>
+      </c>
+      <c r="G13" s="56" t="s">
         <v>213</v>
       </c>
-      <c r="H13" s="60" t="s">
+      <c r="H13" s="56" t="s">
         <v>248</v>
       </c>
-      <c r="I13" s="60">
+      <c r="I13" s="56">
         <v>4764</v>
       </c>
-      <c r="J13" s="60"/>
-      <c r="K13" s="60">
-        <v>1000</v>
-      </c>
-      <c r="L13" s="60">
+      <c r="J13" s="56"/>
+      <c r="K13" s="56">
+        <v>1000</v>
+      </c>
+      <c r="L13" s="56">
         <v>16.624700000000001</v>
       </c>
-      <c r="M13" s="60">
-        <v>1</v>
-      </c>
-      <c r="N13" s="60">
+      <c r="M13" s="56">
+        <v>1</v>
+      </c>
+      <c r="N13" s="56">
         <v>60.151461379754203</v>
       </c>
-      <c r="O13" s="60">
+      <c r="O13" s="56">
         <v>1.16405016530411</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="61">
+      <c r="A14" s="57">
         <v>2022</v>
       </c>
-      <c r="B14" s="61">
+      <c r="B14" s="57">
         <v>7</v>
       </c>
-      <c r="C14" s="61">
+      <c r="C14" s="57">
         <v>19</v>
       </c>
-      <c r="D14" s="61">
+      <c r="D14" s="57">
         <v>12</v>
       </c>
-      <c r="E14" s="61">
+      <c r="E14" s="57">
         <v>46</v>
       </c>
-      <c r="F14" s="61">
+      <c r="F14" s="57">
         <v>4</v>
       </c>
-      <c r="G14" s="61" t="s">
+      <c r="G14" s="57" t="s">
         <v>213</v>
       </c>
-      <c r="H14" s="61" t="s">
+      <c r="H14" s="57" t="s">
         <v>248</v>
       </c>
-      <c r="I14" s="61">
+      <c r="I14" s="57">
         <v>4764</v>
       </c>
-      <c r="J14" s="61" t="s">
+      <c r="J14" s="57" t="s">
         <v>242</v>
       </c>
-      <c r="K14" s="61"/>
-      <c r="L14" s="61"/>
-      <c r="M14" s="61"/>
-      <c r="N14" s="61"/>
-      <c r="O14" s="61"/>
+      <c r="K14" s="57"/>
+      <c r="L14" s="57"/>
+      <c r="M14" s="57"/>
+      <c r="N14" s="57"/>
+      <c r="O14" s="57"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="61">
+      <c r="A15" s="57">
         <v>2024</v>
       </c>
-      <c r="B15" s="61">
+      <c r="B15" s="57">
         <v>2</v>
       </c>
-      <c r="C15" s="61">
-        <v>1</v>
-      </c>
-      <c r="D15" s="61">
-        <v>0</v>
-      </c>
-      <c r="E15" s="61">
-        <v>1</v>
-      </c>
-      <c r="F15" s="61">
+      <c r="C15" s="57">
+        <v>1</v>
+      </c>
+      <c r="D15" s="57">
+        <v>0</v>
+      </c>
+      <c r="E15" s="57">
+        <v>1</v>
+      </c>
+      <c r="F15" s="57">
         <v>3</v>
       </c>
-      <c r="G15" s="61" t="s">
+      <c r="G15" s="57" t="s">
         <v>213</v>
       </c>
-      <c r="H15" s="61" t="s">
+      <c r="H15" s="57" t="s">
         <v>248</v>
       </c>
-      <c r="I15" s="61">
+      <c r="I15" s="57">
         <v>4764</v>
       </c>
-      <c r="J15" s="61"/>
-      <c r="K15" s="61">
-        <v>1000</v>
-      </c>
-      <c r="L15" s="61">
+      <c r="J15" s="57"/>
+      <c r="K15" s="57">
+        <v>1000</v>
+      </c>
+      <c r="L15" s="57">
         <v>16.613499999999998</v>
       </c>
-      <c r="M15" s="61">
-        <v>1</v>
-      </c>
-      <c r="N15" s="61">
+      <c r="M15" s="57">
+        <v>1</v>
+      </c>
+      <c r="N15" s="57">
         <v>60.192012519938601</v>
       </c>
-      <c r="O15" s="61">
+      <c r="O15" s="57">
         <v>1.2587336487582701</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="60">
+      <c r="A16" s="56">
         <v>2024</v>
       </c>
-      <c r="B16" s="60">
+      <c r="B16" s="56">
         <v>2</v>
       </c>
-      <c r="C16" s="60">
-        <v>1</v>
-      </c>
-      <c r="D16" s="60">
-        <v>0</v>
-      </c>
-      <c r="E16" s="60">
-        <v>1</v>
-      </c>
-      <c r="F16" s="60">
+      <c r="C16" s="56">
+        <v>1</v>
+      </c>
+      <c r="D16" s="56">
+        <v>0</v>
+      </c>
+      <c r="E16" s="56">
+        <v>1</v>
+      </c>
+      <c r="F16" s="56">
         <v>4</v>
       </c>
-      <c r="G16" s="60" t="s">
+      <c r="G16" s="56" t="s">
         <v>213</v>
       </c>
-      <c r="H16" s="60" t="s">
+      <c r="H16" s="56" t="s">
         <v>248</v>
       </c>
-      <c r="I16" s="60">
+      <c r="I16" s="56">
         <v>4764</v>
       </c>
-      <c r="J16" s="60" t="s">
+      <c r="J16" s="56" t="s">
         <v>242</v>
       </c>
-      <c r="K16" s="60"/>
-      <c r="L16" s="60"/>
-      <c r="M16" s="60"/>
-      <c r="N16" s="60"/>
-      <c r="O16" s="60"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="56"/>
+      <c r="N16" s="56"/>
+      <c r="O16" s="56"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="60">
+      <c r="A17" s="56">
         <v>2024</v>
       </c>
-      <c r="B17" s="60">
+      <c r="B17" s="56">
         <v>2</v>
       </c>
-      <c r="C17" s="60">
-        <v>1</v>
-      </c>
-      <c r="D17" s="60">
-        <v>0</v>
-      </c>
-      <c r="E17" s="60">
-        <v>1</v>
-      </c>
-      <c r="F17" s="60">
+      <c r="C17" s="56">
+        <v>1</v>
+      </c>
+      <c r="D17" s="56">
+        <v>0</v>
+      </c>
+      <c r="E17" s="56">
+        <v>1</v>
+      </c>
+      <c r="F17" s="56">
         <v>20</v>
       </c>
-      <c r="G17" s="60" t="s">
+      <c r="G17" s="56" t="s">
         <v>213</v>
       </c>
-      <c r="H17" s="60" t="s">
+      <c r="H17" s="56" t="s">
         <v>248</v>
       </c>
-      <c r="I17" s="60">
+      <c r="I17" s="56">
         <v>4764</v>
       </c>
-      <c r="J17" s="60" t="s">
+      <c r="J17" s="56" t="s">
         <v>243</v>
       </c>
-      <c r="K17" s="60"/>
-      <c r="L17" s="60"/>
-      <c r="M17" s="60"/>
-      <c r="N17" s="60"/>
-      <c r="O17" s="60"/>
+      <c r="K17" s="56"/>
+      <c r="L17" s="56"/>
+      <c r="M17" s="56"/>
+      <c r="N17" s="56"/>
+      <c r="O17" s="56"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="61">
+      <c r="A18" s="57">
         <v>2025</v>
       </c>
-      <c r="B18" s="61">
+      <c r="B18" s="57">
         <v>8</v>
       </c>
-      <c r="C18" s="61">
-        <v>1</v>
-      </c>
-      <c r="D18" s="61">
-        <v>0</v>
-      </c>
-      <c r="E18" s="61">
-        <v>1</v>
-      </c>
-      <c r="F18" s="61">
+      <c r="C18" s="57">
+        <v>1</v>
+      </c>
+      <c r="D18" s="57">
+        <v>0</v>
+      </c>
+      <c r="E18" s="57">
+        <v>1</v>
+      </c>
+      <c r="F18" s="57">
         <v>3</v>
       </c>
-      <c r="G18" s="61" t="s">
+      <c r="G18" s="57" t="s">
         <v>213</v>
       </c>
-      <c r="H18" s="61" t="s">
+      <c r="H18" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="I18" s="61">
+      <c r="I18" s="57">
         <v>128907</v>
       </c>
-      <c r="J18" s="61" t="s">
+      <c r="J18" s="57" t="s">
         <v>215</v>
       </c>
-      <c r="K18" s="61"/>
-      <c r="L18" s="61"/>
-      <c r="M18" s="61"/>
-      <c r="N18" s="61"/>
-      <c r="O18" s="61"/>
+      <c r="K18" s="57"/>
+      <c r="L18" s="57"/>
+      <c r="M18" s="57"/>
+      <c r="N18" s="57"/>
+      <c r="O18" s="57"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="60">
+      <c r="A19" s="56">
         <v>2025</v>
       </c>
-      <c r="B19" s="60">
+      <c r="B19" s="56">
         <v>8</v>
       </c>
-      <c r="C19" s="60">
-        <v>1</v>
-      </c>
-      <c r="D19" s="60">
-        <v>0</v>
-      </c>
-      <c r="E19" s="60">
-        <v>1</v>
-      </c>
-      <c r="F19" s="60">
+      <c r="C19" s="56">
+        <v>1</v>
+      </c>
+      <c r="D19" s="56">
+        <v>0</v>
+      </c>
+      <c r="E19" s="56">
+        <v>1</v>
+      </c>
+      <c r="F19" s="56">
         <v>4</v>
       </c>
-      <c r="G19" s="60" t="s">
+      <c r="G19" s="56" t="s">
         <v>213</v>
       </c>
-      <c r="H19" s="60" t="s">
+      <c r="H19" s="56" t="s">
         <v>214</v>
       </c>
-      <c r="I19" s="60">
+      <c r="I19" s="56">
         <v>128907</v>
       </c>
-      <c r="J19" s="60"/>
-      <c r="K19" s="60">
+      <c r="J19" s="56"/>
+      <c r="K19" s="56">
         <v>8.8010999999999999</v>
       </c>
-      <c r="L19" s="60">
+      <c r="L19" s="56">
         <v>8.8010999999999999</v>
       </c>
-      <c r="M19" s="60">
+      <c r="M19" s="56">
         <v>113.622160866255</v>
       </c>
-      <c r="N19" s="60">
+      <c r="N19" s="56">
         <v>113.622160866255</v>
       </c>
-      <c r="O19" s="60">
+      <c r="O19" s="56">
         <v>1.7168308506891199</v>
       </c>
     </row>
@@ -20482,7 +20911,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51D50481-F00D-4F48-81C6-07265F307B30}">
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="9.7109375" customWidth="1"/>
@@ -20497,424 +20926,866 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="62" t="s">
         <v>201</v>
       </c>
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="62" t="s">
         <v>202</v>
       </c>
-      <c r="C1" s="66" t="s">
+      <c r="C1" s="62" t="s">
         <v>203</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="D1" s="62" t="s">
         <v>204</v>
       </c>
-      <c r="E1" s="66" t="s">
+      <c r="E1" s="62" t="s">
         <v>205</v>
       </c>
-      <c r="F1" s="66" t="s">
+      <c r="F1" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="G1" s="66" t="s">
+      <c r="G1" s="62" t="s">
         <v>207</v>
       </c>
-      <c r="H1" s="66" t="s">
+      <c r="H1" s="62" t="s">
         <v>208</v>
       </c>
-      <c r="I1" s="66" t="s">
+      <c r="I1" s="62" t="s">
         <v>209</v>
       </c>
-      <c r="J1" s="66" t="s">
+      <c r="J1" s="62" t="s">
         <v>239</v>
       </c>
-      <c r="K1" s="66" t="s">
+      <c r="K1" s="62" t="s">
         <v>210</v>
       </c>
-      <c r="L1" s="66" t="s">
+      <c r="L1" s="62" t="s">
         <v>211</v>
       </c>
-      <c r="M1" s="66" t="s">
+      <c r="M1" s="62" t="s">
         <v>245</v>
       </c>
-      <c r="N1" s="66" t="s">
+      <c r="N1" s="62" t="s">
         <v>246</v>
       </c>
-      <c r="O1" s="66" t="s">
+      <c r="O1" s="62" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="67">
+      <c r="A2" s="63">
         <v>2025</v>
       </c>
-      <c r="B2" s="67">
+      <c r="B2" s="63">
         <v>8</v>
       </c>
-      <c r="C2" s="67">
-        <v>1</v>
-      </c>
-      <c r="D2" s="67">
-        <v>0</v>
-      </c>
-      <c r="E2" s="67">
-        <v>1</v>
-      </c>
-      <c r="F2" s="67">
+      <c r="C2" s="63">
+        <v>1</v>
+      </c>
+      <c r="D2" s="63">
+        <v>0</v>
+      </c>
+      <c r="E2" s="63">
+        <v>1</v>
+      </c>
+      <c r="F2" s="63">
         <v>7</v>
       </c>
-      <c r="G2" s="67" t="s">
+      <c r="G2" s="63" t="s">
         <v>225</v>
       </c>
-      <c r="H2" s="67" t="s">
+      <c r="H2" s="63" t="s">
         <v>247</v>
       </c>
-      <c r="I2" s="69" t="s">
+      <c r="I2" s="65" t="s">
         <v>220</v>
       </c>
-      <c r="J2" s="67" t="s">
+      <c r="J2" s="63" t="s">
         <v>215</v>
       </c>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="68">
+      <c r="A3" s="64">
         <v>2025</v>
       </c>
-      <c r="B3" s="68">
+      <c r="B3" s="64">
         <v>8</v>
       </c>
-      <c r="C3" s="68">
-        <v>1</v>
-      </c>
-      <c r="D3" s="68">
-        <v>0</v>
-      </c>
-      <c r="E3" s="68">
-        <v>1</v>
-      </c>
-      <c r="F3" s="68">
+      <c r="C3" s="64">
+        <v>1</v>
+      </c>
+      <c r="D3" s="64">
+        <v>0</v>
+      </c>
+      <c r="E3" s="64">
+        <v>1</v>
+      </c>
+      <c r="F3" s="64">
         <v>8</v>
       </c>
-      <c r="G3" s="68" t="s">
+      <c r="G3" s="64" t="s">
         <v>225</v>
       </c>
-      <c r="H3" s="68" t="s">
+      <c r="H3" s="64" t="s">
         <v>247</v>
       </c>
-      <c r="I3" s="70" t="s">
+      <c r="I3" s="66" t="s">
         <v>220</v>
       </c>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68">
+      <c r="J3" s="64"/>
+      <c r="K3" s="64">
         <v>8.3796999999999997</v>
       </c>
-      <c r="L3" s="68">
+      <c r="L3" s="64">
         <v>8.3796999999999997</v>
       </c>
-      <c r="M3" s="68">
+      <c r="M3" s="64">
         <v>119.336014415791</v>
       </c>
-      <c r="N3" s="68">
+      <c r="N3" s="64">
         <v>119.336014415791</v>
       </c>
-      <c r="O3" s="68">
+      <c r="O3" s="64">
         <v>1.0501569268589599</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="67">
+      <c r="A4" s="63">
         <v>2024</v>
       </c>
-      <c r="B4" s="67">
+      <c r="B4" s="63">
         <v>2</v>
       </c>
-      <c r="C4" s="67">
-        <v>1</v>
-      </c>
-      <c r="D4" s="67">
-        <v>0</v>
-      </c>
-      <c r="E4" s="67">
-        <v>1</v>
-      </c>
-      <c r="F4" s="67">
+      <c r="C4" s="63">
+        <v>1</v>
+      </c>
+      <c r="D4" s="63">
+        <v>0</v>
+      </c>
+      <c r="E4" s="63">
+        <v>1</v>
+      </c>
+      <c r="F4" s="63">
         <v>7</v>
       </c>
-      <c r="G4" s="67" t="s">
+      <c r="G4" s="63" t="s">
         <v>225</v>
       </c>
-      <c r="H4" s="67" t="s">
+      <c r="H4" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="I4" s="69" t="s">
+      <c r="I4" s="65" t="s">
         <v>220</v>
       </c>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67">
-        <v>1000</v>
-      </c>
-      <c r="L4" s="67">
+      <c r="J4" s="63"/>
+      <c r="K4" s="63">
+        <v>1000</v>
+      </c>
+      <c r="L4" s="63">
         <v>8.3575999999999997</v>
       </c>
-      <c r="M4" s="67">
-        <v>1</v>
-      </c>
-      <c r="N4" s="67">
+      <c r="M4" s="63">
+        <v>1</v>
+      </c>
+      <c r="N4" s="63">
         <v>119.65157461472199</v>
       </c>
-      <c r="O4" s="67">
+      <c r="O4" s="63">
         <v>1.8811551773110999</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="68">
+      <c r="A5" s="64">
         <v>2024</v>
       </c>
-      <c r="B5" s="68">
+      <c r="B5" s="64">
         <v>2</v>
       </c>
-      <c r="C5" s="68">
-        <v>1</v>
-      </c>
-      <c r="D5" s="68">
-        <v>0</v>
-      </c>
-      <c r="E5" s="68">
-        <v>1</v>
-      </c>
-      <c r="F5" s="68">
+      <c r="C5" s="64">
+        <v>1</v>
+      </c>
+      <c r="D5" s="64">
+        <v>0</v>
+      </c>
+      <c r="E5" s="64">
+        <v>1</v>
+      </c>
+      <c r="F5" s="64">
         <v>8</v>
       </c>
-      <c r="G5" s="68" t="s">
+      <c r="G5" s="64" t="s">
         <v>225</v>
       </c>
-      <c r="H5" s="68" t="s">
+      <c r="H5" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="I5" s="70" t="s">
+      <c r="I5" s="66" t="s">
         <v>220</v>
       </c>
-      <c r="J5" s="68" t="s">
+      <c r="J5" s="64" t="s">
         <v>242</v>
       </c>
-      <c r="K5" s="68"/>
-      <c r="L5" s="68"/>
-      <c r="M5" s="68"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
+      <c r="K5" s="64"/>
+      <c r="L5" s="64"/>
+      <c r="M5" s="64"/>
+      <c r="N5" s="64"/>
+      <c r="O5" s="64"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="67">
+      <c r="A6" s="63">
         <v>2022</v>
       </c>
-      <c r="B6" s="67">
+      <c r="B6" s="63">
         <v>7</v>
       </c>
-      <c r="C6" s="67">
+      <c r="C6" s="63">
         <v>19</v>
       </c>
-      <c r="D6" s="67">
+      <c r="D6" s="63">
         <v>12</v>
       </c>
-      <c r="E6" s="67">
+      <c r="E6" s="63">
         <v>46</v>
       </c>
-      <c r="F6" s="67">
+      <c r="F6" s="63">
         <v>2</v>
       </c>
-      <c r="G6" s="67" t="s">
+      <c r="G6" s="63" t="s">
         <v>225</v>
       </c>
-      <c r="H6" s="67" t="s">
+      <c r="H6" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="69" t="s">
+      <c r="I6" s="65" t="s">
         <v>220</v>
       </c>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67">
-        <v>1000</v>
-      </c>
-      <c r="L6" s="67">
+      <c r="J6" s="63"/>
+      <c r="K6" s="63">
+        <v>1000</v>
+      </c>
+      <c r="L6" s="63">
         <v>8.3750999999999998</v>
       </c>
-      <c r="M6" s="67">
-        <v>1</v>
-      </c>
-      <c r="N6" s="67">
+      <c r="M6" s="63">
+        <v>1</v>
+      </c>
+      <c r="N6" s="63">
         <v>119.401559384366</v>
       </c>
-      <c r="O6" s="67">
+      <c r="O6" s="63">
         <v>1.8352099609999999</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="68">
+      <c r="A7" s="64">
         <v>2022</v>
       </c>
-      <c r="B7" s="68">
+      <c r="B7" s="64">
         <v>7</v>
       </c>
-      <c r="C7" s="68">
+      <c r="C7" s="64">
         <v>19</v>
       </c>
-      <c r="D7" s="68">
+      <c r="D7" s="64">
         <v>12</v>
       </c>
-      <c r="E7" s="68">
+      <c r="E7" s="64">
         <v>46</v>
       </c>
-      <c r="F7" s="68">
+      <c r="F7" s="64">
         <v>5</v>
       </c>
-      <c r="G7" s="68" t="s">
+      <c r="G7" s="64" t="s">
         <v>225</v>
       </c>
-      <c r="H7" s="68" t="s">
+      <c r="H7" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="I7" s="70" t="s">
+      <c r="I7" s="66" t="s">
         <v>220</v>
       </c>
-      <c r="J7" s="68" t="s">
+      <c r="J7" s="64" t="s">
         <v>242</v>
       </c>
-      <c r="K7" s="68"/>
-      <c r="L7" s="68"/>
-      <c r="M7" s="68"/>
-      <c r="N7" s="68"/>
-      <c r="O7" s="68"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="64"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="67">
+      <c r="A8" s="63">
         <v>2021</v>
       </c>
-      <c r="B8" s="67">
-        <v>1</v>
-      </c>
-      <c r="C8" s="67">
-        <v>1</v>
-      </c>
-      <c r="D8" s="67">
-        <v>0</v>
-      </c>
-      <c r="E8" s="67">
-        <v>1</v>
-      </c>
-      <c r="F8" s="67">
+      <c r="B8" s="63">
+        <v>1</v>
+      </c>
+      <c r="C8" s="63">
+        <v>1</v>
+      </c>
+      <c r="D8" s="63">
+        <v>0</v>
+      </c>
+      <c r="E8" s="63">
+        <v>1</v>
+      </c>
+      <c r="F8" s="63">
         <v>2</v>
       </c>
-      <c r="G8" s="67" t="s">
+      <c r="G8" s="63" t="s">
         <v>225</v>
       </c>
-      <c r="H8" s="67" t="s">
+      <c r="H8" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="I8" s="69" t="s">
+      <c r="I8" s="65" t="s">
         <v>220</v>
       </c>
-      <c r="J8" s="67"/>
-      <c r="K8" s="67">
-        <v>1000</v>
-      </c>
-      <c r="L8" s="67">
+      <c r="J8" s="63"/>
+      <c r="K8" s="63">
+        <v>1000</v>
+      </c>
+      <c r="L8" s="63">
         <v>8.3756000000000004</v>
       </c>
-      <c r="M8" s="67">
-        <v>1</v>
-      </c>
-      <c r="N8" s="67">
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
+      <c r="N8" s="63">
         <v>119.394431443717</v>
       </c>
-      <c r="O8" s="67">
+      <c r="O8" s="63">
         <v>2.03531169831321</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="68">
+      <c r="A9" s="64">
         <v>2021</v>
       </c>
-      <c r="B9" s="68">
+      <c r="B9" s="64">
         <v>7</v>
       </c>
-      <c r="C9" s="68">
-        <v>1</v>
-      </c>
-      <c r="D9" s="68">
-        <v>0</v>
-      </c>
-      <c r="E9" s="68">
-        <v>1</v>
-      </c>
-      <c r="F9" s="68">
+      <c r="C9" s="64">
+        <v>1</v>
+      </c>
+      <c r="D9" s="64">
+        <v>0</v>
+      </c>
+      <c r="E9" s="64">
+        <v>1</v>
+      </c>
+      <c r="F9" s="64">
         <v>2</v>
       </c>
-      <c r="G9" s="68" t="s">
+      <c r="G9" s="64" t="s">
         <v>225</v>
       </c>
-      <c r="H9" s="68" t="s">
+      <c r="H9" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="I9" s="70" t="s">
+      <c r="I9" s="66" t="s">
         <v>220</v>
       </c>
-      <c r="J9" s="68"/>
-      <c r="K9" s="68">
-        <v>1000</v>
-      </c>
-      <c r="L9" s="68">
+      <c r="J9" s="64"/>
+      <c r="K9" s="64">
+        <v>1000</v>
+      </c>
+      <c r="L9" s="64">
         <v>8.3756000000000004</v>
       </c>
-      <c r="M9" s="68">
-        <v>1</v>
-      </c>
-      <c r="N9" s="68">
+      <c r="M9" s="64">
+        <v>1</v>
+      </c>
+      <c r="N9" s="64">
         <v>119.394431443717</v>
       </c>
-      <c r="O9" s="68">
+      <c r="O9" s="64">
         <v>2.03531169831321</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="67">
+      <c r="A10" s="69">
         <v>2021</v>
       </c>
-      <c r="B10" s="67">
+      <c r="B10" s="69">
         <v>7</v>
       </c>
-      <c r="C10" s="67">
-        <v>1</v>
-      </c>
-      <c r="D10" s="67">
-        <v>0</v>
-      </c>
-      <c r="E10" s="67">
-        <v>1</v>
-      </c>
-      <c r="F10" s="67">
+      <c r="C10" s="69">
+        <v>1</v>
+      </c>
+      <c r="D10" s="69">
+        <v>0</v>
+      </c>
+      <c r="E10" s="69">
+        <v>1</v>
+      </c>
+      <c r="F10" s="69">
         <v>5</v>
       </c>
-      <c r="G10" s="67" t="s">
+      <c r="G10" s="69" t="s">
         <v>225</v>
       </c>
-      <c r="H10" s="67" t="s">
+      <c r="H10" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="I10" s="69" t="s">
+      <c r="I10" s="70" t="s">
         <v>220</v>
       </c>
-      <c r="J10" s="67" t="s">
+      <c r="J10" s="69" t="s">
         <v>242</v>
       </c>
-      <c r="K10" s="67"/>
-      <c r="L10" s="67"/>
-      <c r="M10" s="67"/>
-      <c r="N10" s="67"/>
-      <c r="O10" s="67"/>
+      <c r="K10" s="69"/>
+      <c r="L10" s="69"/>
+      <c r="M10" s="69"/>
+      <c r="N10" s="69"/>
+      <c r="O10" s="69"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="76">
+        <v>2024</v>
+      </c>
+      <c r="B11" s="67">
+        <v>8</v>
+      </c>
+      <c r="C11" s="67">
+        <v>1</v>
+      </c>
+      <c r="D11" s="67">
+        <v>0</v>
+      </c>
+      <c r="E11" s="67">
+        <v>1</v>
+      </c>
+      <c r="F11" s="67">
+        <v>7</v>
+      </c>
+      <c r="G11" s="67" t="s">
+        <v>225</v>
+      </c>
+      <c r="H11" s="67" t="s">
+        <v>247</v>
+      </c>
+      <c r="I11" s="68" t="s">
+        <v>221</v>
+      </c>
+      <c r="J11" s="67"/>
+      <c r="K11" s="67">
+        <v>1000</v>
+      </c>
+      <c r="L11" s="67">
+        <v>7.2114000000000003</v>
+      </c>
+      <c r="M11" s="67">
+        <v>1</v>
+      </c>
+      <c r="N11" s="67">
+        <v>138.66932911778599</v>
+      </c>
+      <c r="O11" s="78">
+        <v>0.929754688179387</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="80">
+        <v>2024</v>
+      </c>
+      <c r="B12" s="69">
+        <v>8</v>
+      </c>
+      <c r="C12" s="69">
+        <v>1</v>
+      </c>
+      <c r="D12" s="69">
+        <v>0</v>
+      </c>
+      <c r="E12" s="69">
+        <v>1</v>
+      </c>
+      <c r="F12" s="69">
+        <v>8</v>
+      </c>
+      <c r="G12" s="69" t="s">
+        <v>225</v>
+      </c>
+      <c r="H12" s="69" t="s">
+        <v>247</v>
+      </c>
+      <c r="I12" s="70" t="s">
+        <v>221</v>
+      </c>
+      <c r="J12" s="69" t="s">
+        <v>242</v>
+      </c>
+      <c r="K12" s="69"/>
+      <c r="L12" s="69"/>
+      <c r="M12" s="69"/>
+      <c r="N12" s="69"/>
+      <c r="O12" s="81"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="76">
+        <v>2020</v>
+      </c>
+      <c r="B13" s="67">
+        <v>8</v>
+      </c>
+      <c r="C13" s="67">
+        <v>1</v>
+      </c>
+      <c r="D13" s="67">
+        <v>0</v>
+      </c>
+      <c r="E13" s="67">
+        <v>1</v>
+      </c>
+      <c r="F13" s="67">
+        <v>2</v>
+      </c>
+      <c r="G13" s="67" t="s">
+        <v>225</v>
+      </c>
+      <c r="H13" s="67" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="68" t="s">
+        <v>220</v>
+      </c>
+      <c r="J13" s="67"/>
+      <c r="K13" s="67">
+        <v>1000</v>
+      </c>
+      <c r="L13" s="67">
+        <v>8.3513999999999999</v>
+      </c>
+      <c r="M13" s="67">
+        <v>1</v>
+      </c>
+      <c r="N13" s="67">
+        <v>119.740402806715</v>
+      </c>
+      <c r="O13" s="78">
+        <v>1.9286659923145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="80">
+        <v>2020</v>
+      </c>
+      <c r="B14" s="69">
+        <v>1</v>
+      </c>
+      <c r="C14" s="69">
+        <v>1</v>
+      </c>
+      <c r="D14" s="69">
+        <v>0</v>
+      </c>
+      <c r="E14" s="69">
+        <v>1</v>
+      </c>
+      <c r="F14" s="69">
+        <v>2</v>
+      </c>
+      <c r="G14" s="69" t="s">
+        <v>225</v>
+      </c>
+      <c r="H14" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" s="70" t="s">
+        <v>220</v>
+      </c>
+      <c r="J14" s="69"/>
+      <c r="K14" s="69">
+        <v>8.4133300801790405</v>
+      </c>
+      <c r="L14" s="69">
+        <v>8.3513999999999999</v>
+      </c>
+      <c r="M14" s="69">
+        <v>118.85899999999999</v>
+      </c>
+      <c r="N14" s="69">
+        <v>119.740402806715</v>
+      </c>
+      <c r="O14" s="81">
+        <v>1.9286659923145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="76">
+        <v>2019</v>
+      </c>
+      <c r="B15" s="67">
+        <v>1</v>
+      </c>
+      <c r="C15" s="67">
+        <v>1</v>
+      </c>
+      <c r="D15" s="67">
+        <v>0</v>
+      </c>
+      <c r="E15" s="67">
+        <v>1</v>
+      </c>
+      <c r="F15" s="67">
+        <v>2</v>
+      </c>
+      <c r="G15" s="67" t="s">
+        <v>225</v>
+      </c>
+      <c r="H15" s="67" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="68" t="s">
+        <v>220</v>
+      </c>
+      <c r="J15" s="67"/>
+      <c r="K15" s="67">
+        <v>8.4133300801790405</v>
+      </c>
+      <c r="L15" s="67">
+        <v>8.3513999999999999</v>
+      </c>
+      <c r="M15" s="67">
+        <v>118.85899999999999</v>
+      </c>
+      <c r="N15" s="67">
+        <v>119.740402806715</v>
+      </c>
+      <c r="O15" s="78">
+        <v>1.9286659923145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="80">
+        <v>2018</v>
+      </c>
+      <c r="B16" s="69">
+        <v>1</v>
+      </c>
+      <c r="C16" s="69">
+        <v>1</v>
+      </c>
+      <c r="D16" s="69">
+        <v>0</v>
+      </c>
+      <c r="E16" s="69">
+        <v>1</v>
+      </c>
+      <c r="F16" s="69">
+        <v>2</v>
+      </c>
+      <c r="G16" s="69" t="s">
+        <v>225</v>
+      </c>
+      <c r="H16" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="70" t="s">
+        <v>220</v>
+      </c>
+      <c r="J16" s="69"/>
+      <c r="K16" s="69">
+        <v>8.4133300801790405</v>
+      </c>
+      <c r="L16" s="69">
+        <v>8.3513999999999999</v>
+      </c>
+      <c r="M16" s="69">
+        <v>118.85899999999999</v>
+      </c>
+      <c r="N16" s="69">
+        <v>119.740402806715</v>
+      </c>
+      <c r="O16" s="81">
+        <v>1.9286659923145</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="76">
+        <v>2017</v>
+      </c>
+      <c r="B17" s="67">
+        <v>8</v>
+      </c>
+      <c r="C17" s="67">
+        <v>1</v>
+      </c>
+      <c r="D17" s="67">
+        <v>11</v>
+      </c>
+      <c r="E17" s="67">
+        <v>40</v>
+      </c>
+      <c r="F17" s="67">
+        <v>2</v>
+      </c>
+      <c r="G17" s="67" t="s">
+        <v>225</v>
+      </c>
+      <c r="H17" s="67" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="68" t="s">
+        <v>220</v>
+      </c>
+      <c r="J17" s="67"/>
+      <c r="K17" s="67">
+        <v>8.4133300801790405</v>
+      </c>
+      <c r="L17" s="67">
+        <v>8.3513999999999999</v>
+      </c>
+      <c r="M17" s="67">
+        <v>118.85899999999999</v>
+      </c>
+      <c r="N17" s="67">
+        <v>119.740402806715</v>
+      </c>
+      <c r="O17" s="78">
+        <v>1.9286659923145</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="80">
+        <v>2017</v>
+      </c>
+      <c r="B18" s="69">
+        <v>1</v>
+      </c>
+      <c r="C18" s="69">
+        <v>1</v>
+      </c>
+      <c r="D18" s="69">
+        <v>0</v>
+      </c>
+      <c r="E18" s="69">
+        <v>1</v>
+      </c>
+      <c r="F18" s="69">
+        <v>2</v>
+      </c>
+      <c r="G18" s="69" t="s">
+        <v>225</v>
+      </c>
+      <c r="H18" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" s="70" t="s">
+        <v>220</v>
+      </c>
+      <c r="J18" s="69"/>
+      <c r="K18" s="69">
+        <v>8.4133300801790405</v>
+      </c>
+      <c r="L18" s="69">
+        <v>8.3513999999999999</v>
+      </c>
+      <c r="M18" s="69">
+        <v>118.85899999999999</v>
+      </c>
+      <c r="N18" s="69">
+        <v>119.740402806715</v>
+      </c>
+      <c r="O18" s="81">
+        <v>1.9286659923145</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="76">
+        <v>2016</v>
+      </c>
+      <c r="B19" s="67">
+        <v>1</v>
+      </c>
+      <c r="C19" s="67">
+        <v>1</v>
+      </c>
+      <c r="D19" s="67">
+        <v>0</v>
+      </c>
+      <c r="E19" s="67">
+        <v>1</v>
+      </c>
+      <c r="F19" s="67">
+        <v>2</v>
+      </c>
+      <c r="G19" s="67" t="s">
+        <v>225</v>
+      </c>
+      <c r="H19" s="67" t="s">
+        <v>37</v>
+      </c>
+      <c r="I19" s="68" t="s">
+        <v>220</v>
+      </c>
+      <c r="J19" s="67"/>
+      <c r="K19" s="67">
+        <v>8.4133300801790405</v>
+      </c>
+      <c r="L19" s="67">
+        <v>8.3513999999999999</v>
+      </c>
+      <c r="M19" s="67">
+        <v>118.85899999999999</v>
+      </c>
+      <c r="N19" s="67">
+        <v>119.740402806715</v>
+      </c>
+      <c r="O19" s="78">
+        <v>1.9286659923145</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="77">
+        <v>2015</v>
+      </c>
+      <c r="B20" s="63">
+        <v>9</v>
+      </c>
+      <c r="C20" s="63">
+        <v>30</v>
+      </c>
+      <c r="D20" s="63">
+        <v>23</v>
+      </c>
+      <c r="E20" s="63">
+        <v>0</v>
+      </c>
+      <c r="F20" s="63">
+        <v>2</v>
+      </c>
+      <c r="G20" s="63" t="s">
+        <v>225</v>
+      </c>
+      <c r="H20" s="63" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20" s="65" t="s">
+        <v>220</v>
+      </c>
+      <c r="J20" s="63"/>
+      <c r="K20" s="63">
+        <v>8.4133300801790405</v>
+      </c>
+      <c r="L20" s="63">
+        <v>8.3513999999999999</v>
+      </c>
+      <c r="M20" s="63">
+        <v>118.85899999999999</v>
+      </c>
+      <c r="N20" s="63">
+        <v>119.740402806715</v>
+      </c>
+      <c r="O20" s="79">
+        <v>1.9286659923145</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20926,7 +21797,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71D78007-B334-4AFA-9368-61BFA621700B}">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="9.7109375" customWidth="1"/>
@@ -20941,461 +21812,588 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="62" t="s">
         <v>201</v>
       </c>
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="62" t="s">
         <v>202</v>
       </c>
-      <c r="C1" s="66" t="s">
+      <c r="C1" s="62" t="s">
         <v>203</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="D1" s="62" t="s">
         <v>204</v>
       </c>
-      <c r="E1" s="66" t="s">
+      <c r="E1" s="62" t="s">
         <v>205</v>
       </c>
-      <c r="F1" s="66" t="s">
+      <c r="F1" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="G1" s="66" t="s">
+      <c r="G1" s="62" t="s">
         <v>207</v>
       </c>
-      <c r="H1" s="66" t="s">
+      <c r="H1" s="62" t="s">
         <v>208</v>
       </c>
-      <c r="I1" s="66" t="s">
+      <c r="I1" s="62" t="s">
         <v>209</v>
       </c>
-      <c r="J1" s="66" t="s">
+      <c r="J1" s="62" t="s">
         <v>239</v>
       </c>
-      <c r="K1" s="66" t="s">
+      <c r="K1" s="62" t="s">
         <v>210</v>
       </c>
-      <c r="L1" s="66" t="s">
+      <c r="L1" s="62" t="s">
         <v>211</v>
       </c>
-      <c r="M1" s="66" t="s">
+      <c r="M1" s="62" t="s">
         <v>245</v>
       </c>
-      <c r="N1" s="66" t="s">
+      <c r="N1" s="62" t="s">
         <v>246</v>
       </c>
-      <c r="O1" s="66" t="s">
+      <c r="O1" s="62" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="67">
+      <c r="A2" s="63">
         <v>2025</v>
       </c>
-      <c r="B2" s="67">
+      <c r="B2" s="63">
         <v>8</v>
       </c>
-      <c r="C2" s="67">
-        <v>1</v>
-      </c>
-      <c r="D2" s="67">
-        <v>0</v>
-      </c>
-      <c r="E2" s="67">
-        <v>1</v>
-      </c>
-      <c r="F2" s="67">
+      <c r="C2" s="63">
+        <v>1</v>
+      </c>
+      <c r="D2" s="63">
+        <v>0</v>
+      </c>
+      <c r="E2" s="63">
+        <v>1</v>
+      </c>
+      <c r="F2" s="63">
         <v>11</v>
       </c>
-      <c r="G2" s="67" t="s">
+      <c r="G2" s="63" t="s">
         <v>226</v>
       </c>
-      <c r="H2" s="67" t="s">
+      <c r="H2" s="63" t="s">
         <v>214</v>
       </c>
-      <c r="I2" s="69" t="s">
+      <c r="I2" s="65" t="s">
         <v>253</v>
       </c>
-      <c r="J2" s="67" t="s">
+      <c r="J2" s="63" t="s">
         <v>215</v>
       </c>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="68">
+      <c r="A3" s="64">
         <v>2025</v>
       </c>
-      <c r="B3" s="68">
+      <c r="B3" s="64">
         <v>8</v>
       </c>
-      <c r="C3" s="68">
-        <v>1</v>
-      </c>
-      <c r="D3" s="68">
-        <v>0</v>
-      </c>
-      <c r="E3" s="68">
-        <v>1</v>
-      </c>
-      <c r="F3" s="68">
+      <c r="C3" s="64">
+        <v>1</v>
+      </c>
+      <c r="D3" s="64">
+        <v>0</v>
+      </c>
+      <c r="E3" s="64">
+        <v>1</v>
+      </c>
+      <c r="F3" s="64">
         <v>12</v>
       </c>
-      <c r="G3" s="68" t="s">
+      <c r="G3" s="64" t="s">
         <v>226</v>
       </c>
-      <c r="H3" s="68" t="s">
+      <c r="H3" s="64" t="s">
         <v>214</v>
       </c>
-      <c r="I3" s="70" t="s">
+      <c r="I3" s="66" t="s">
         <v>253</v>
       </c>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68">
+      <c r="J3" s="64"/>
+      <c r="K3" s="64">
         <v>8.2452000000000005</v>
       </c>
-      <c r="L3" s="68">
+      <c r="L3" s="64">
         <v>8.2452000000000005</v>
       </c>
-      <c r="M3" s="68">
+      <c r="M3" s="64">
         <v>121.282685683792</v>
       </c>
-      <c r="N3" s="68">
+      <c r="N3" s="64">
         <v>121.282685683792</v>
       </c>
-      <c r="O3" s="68">
+      <c r="O3" s="64">
         <v>0.94600494833357596</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="68">
+      <c r="A4" s="64">
         <v>2024</v>
       </c>
-      <c r="B4" s="68">
+      <c r="B4" s="64">
         <v>2</v>
       </c>
-      <c r="C4" s="68">
-        <v>1</v>
-      </c>
-      <c r="D4" s="68">
-        <v>0</v>
-      </c>
-      <c r="E4" s="68">
-        <v>1</v>
-      </c>
-      <c r="F4" s="68">
+      <c r="C4" s="64">
+        <v>1</v>
+      </c>
+      <c r="D4" s="64">
+        <v>0</v>
+      </c>
+      <c r="E4" s="64">
+        <v>1</v>
+      </c>
+      <c r="F4" s="64">
         <v>11</v>
       </c>
-      <c r="G4" s="68" t="s">
+      <c r="G4" s="64" t="s">
         <v>226</v>
       </c>
-      <c r="H4" s="68" t="s">
+      <c r="H4" s="64" t="s">
         <v>248</v>
       </c>
-      <c r="I4" s="70" t="s">
+      <c r="I4" s="66" t="s">
         <v>255</v>
       </c>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68">
-        <v>1000</v>
-      </c>
-      <c r="L4" s="68">
+      <c r="J4" s="64"/>
+      <c r="K4" s="64">
+        <v>1000</v>
+      </c>
+      <c r="L4" s="64">
         <v>13.308199999999999</v>
       </c>
-      <c r="M4" s="68">
-        <v>1</v>
-      </c>
-      <c r="N4" s="68">
+      <c r="M4" s="64">
+        <v>1</v>
+      </c>
+      <c r="N4" s="64">
         <v>75.141641995160896</v>
       </c>
-      <c r="O4" s="68">
+      <c r="O4" s="64">
         <v>1.2914628942617901</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="67">
+      <c r="A5" s="63">
         <v>2024</v>
       </c>
-      <c r="B5" s="67">
+      <c r="B5" s="63">
         <v>2</v>
       </c>
-      <c r="C5" s="67">
-        <v>1</v>
-      </c>
-      <c r="D5" s="67">
-        <v>0</v>
-      </c>
-      <c r="E5" s="67">
-        <v>1</v>
-      </c>
-      <c r="F5" s="67">
+      <c r="C5" s="63">
+        <v>1</v>
+      </c>
+      <c r="D5" s="63">
+        <v>0</v>
+      </c>
+      <c r="E5" s="63">
+        <v>1</v>
+      </c>
+      <c r="F5" s="63">
         <v>12</v>
       </c>
-      <c r="G5" s="67" t="s">
+      <c r="G5" s="63" t="s">
         <v>226</v>
       </c>
-      <c r="H5" s="67" t="s">
+      <c r="H5" s="63" t="s">
         <v>248</v>
       </c>
-      <c r="I5" s="69" t="s">
+      <c r="I5" s="65" t="s">
         <v>255</v>
       </c>
-      <c r="J5" s="67" t="s">
+      <c r="J5" s="63" t="s">
         <v>242</v>
       </c>
-      <c r="K5" s="67"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="67"/>
+      <c r="K5" s="63"/>
+      <c r="L5" s="63"/>
+      <c r="M5" s="63"/>
+      <c r="N5" s="63"/>
+      <c r="O5" s="63"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="68">
+      <c r="A6" s="64">
         <v>2024</v>
       </c>
-      <c r="B6" s="68">
+      <c r="B6" s="64">
         <v>2</v>
       </c>
-      <c r="C6" s="68">
-        <v>1</v>
-      </c>
-      <c r="D6" s="68">
-        <v>0</v>
-      </c>
-      <c r="E6" s="68">
-        <v>1</v>
-      </c>
-      <c r="F6" s="68">
+      <c r="C6" s="64">
+        <v>1</v>
+      </c>
+      <c r="D6" s="64">
+        <v>0</v>
+      </c>
+      <c r="E6" s="64">
+        <v>1</v>
+      </c>
+      <c r="F6" s="64">
         <v>21</v>
       </c>
-      <c r="G6" s="68" t="s">
+      <c r="G6" s="64" t="s">
         <v>226</v>
       </c>
-      <c r="H6" s="68" t="s">
+      <c r="H6" s="64" t="s">
         <v>248</v>
       </c>
-      <c r="I6" s="70" t="s">
+      <c r="I6" s="66" t="s">
         <v>255</v>
       </c>
-      <c r="J6" s="68" t="s">
+      <c r="J6" s="64" t="s">
         <v>243</v>
       </c>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
-      <c r="N6" s="68"/>
-      <c r="O6" s="68"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="64"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="68">
+      <c r="A7" s="64">
         <v>2022</v>
       </c>
-      <c r="B7" s="68">
+      <c r="B7" s="64">
         <v>7</v>
       </c>
-      <c r="C7" s="68">
+      <c r="C7" s="64">
         <v>19</v>
       </c>
-      <c r="D7" s="68">
+      <c r="D7" s="64">
         <v>12</v>
       </c>
-      <c r="E7" s="68">
+      <c r="E7" s="64">
         <v>46</v>
       </c>
-      <c r="F7" s="68">
+      <c r="F7" s="64">
         <v>3</v>
       </c>
-      <c r="G7" s="68" t="s">
+      <c r="G7" s="64" t="s">
         <v>226</v>
       </c>
-      <c r="H7" s="68" t="s">
+      <c r="H7" s="64" t="s">
         <v>248</v>
       </c>
-      <c r="I7" s="70" t="s">
+      <c r="I7" s="66" t="s">
         <v>255</v>
       </c>
-      <c r="J7" s="68"/>
-      <c r="K7" s="68">
-        <v>1000</v>
-      </c>
-      <c r="L7" s="68">
+      <c r="J7" s="64"/>
+      <c r="K7" s="64">
+        <v>1000</v>
+      </c>
+      <c r="L7" s="64">
         <v>13.317600000000001</v>
       </c>
-      <c r="M7" s="68">
-        <v>1</v>
-      </c>
-      <c r="N7" s="68">
+      <c r="M7" s="64">
+        <v>1</v>
+      </c>
+      <c r="N7" s="64">
         <v>75.088604553373003</v>
       </c>
-      <c r="O7" s="68">
+      <c r="O7" s="64">
         <v>1.2169603471391199</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="67">
+      <c r="A8" s="63">
         <v>2022</v>
       </c>
-      <c r="B8" s="67">
+      <c r="B8" s="63">
         <v>7</v>
       </c>
-      <c r="C8" s="67">
+      <c r="C8" s="63">
         <v>19</v>
       </c>
-      <c r="D8" s="67">
+      <c r="D8" s="63">
         <v>12</v>
       </c>
-      <c r="E8" s="67">
+      <c r="E8" s="63">
         <v>46</v>
       </c>
-      <c r="F8" s="67">
+      <c r="F8" s="63">
         <v>6</v>
       </c>
-      <c r="G8" s="67" t="s">
+      <c r="G8" s="63" t="s">
         <v>226</v>
       </c>
-      <c r="H8" s="67" t="s">
+      <c r="H8" s="63" t="s">
         <v>248</v>
       </c>
-      <c r="I8" s="69" t="s">
+      <c r="I8" s="65" t="s">
         <v>255</v>
       </c>
-      <c r="J8" s="67" t="s">
+      <c r="J8" s="63" t="s">
         <v>242</v>
       </c>
-      <c r="K8" s="67"/>
-      <c r="L8" s="67"/>
-      <c r="M8" s="67"/>
-      <c r="N8" s="67"/>
-      <c r="O8" s="67"/>
+      <c r="K8" s="63"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="63"/>
+      <c r="O8" s="63"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="68">
+      <c r="A9" s="64">
         <v>2021</v>
       </c>
-      <c r="B9" s="68">
-        <v>1</v>
-      </c>
-      <c r="C9" s="68">
-        <v>1</v>
-      </c>
-      <c r="D9" s="68">
-        <v>0</v>
-      </c>
-      <c r="E9" s="68">
-        <v>1</v>
-      </c>
-      <c r="F9" s="68">
+      <c r="B9" s="64">
+        <v>1</v>
+      </c>
+      <c r="C9" s="64">
+        <v>1</v>
+      </c>
+      <c r="D9" s="64">
+        <v>0</v>
+      </c>
+      <c r="E9" s="64">
+        <v>1</v>
+      </c>
+      <c r="F9" s="64">
         <v>3</v>
       </c>
-      <c r="G9" s="68" t="s">
+      <c r="G9" s="64" t="s">
         <v>226</v>
       </c>
-      <c r="H9" s="68" t="s">
+      <c r="H9" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="I9" s="70" t="s">
+      <c r="I9" s="66" t="s">
         <v>218</v>
       </c>
-      <c r="J9" s="68"/>
-      <c r="K9" s="68">
-        <v>1000</v>
-      </c>
-      <c r="L9" s="68">
+      <c r="J9" s="64"/>
+      <c r="K9" s="64">
+        <v>1000</v>
+      </c>
+      <c r="L9" s="64">
         <v>8.4390000000000001</v>
       </c>
-      <c r="M9" s="68">
-        <v>1</v>
-      </c>
-      <c r="N9" s="68">
+      <c r="M9" s="64">
+        <v>1</v>
+      </c>
+      <c r="N9" s="64">
         <v>118.497452304775</v>
       </c>
-      <c r="O9" s="68">
+      <c r="O9" s="64">
         <v>2.20773173146471</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="67">
+      <c r="A10" s="63">
         <v>2021</v>
       </c>
-      <c r="B10" s="67">
+      <c r="B10" s="63">
         <v>7</v>
       </c>
-      <c r="C10" s="67">
-        <v>1</v>
-      </c>
-      <c r="D10" s="67">
-        <v>0</v>
-      </c>
-      <c r="E10" s="67">
-        <v>1</v>
-      </c>
-      <c r="F10" s="67">
+      <c r="C10" s="63">
+        <v>1</v>
+      </c>
+      <c r="D10" s="63">
+        <v>0</v>
+      </c>
+      <c r="E10" s="63">
+        <v>1</v>
+      </c>
+      <c r="F10" s="63">
         <v>3</v>
       </c>
-      <c r="G10" s="67" t="s">
+      <c r="G10" s="63" t="s">
         <v>226</v>
       </c>
-      <c r="H10" s="67" t="s">
+      <c r="H10" s="63" t="s">
         <v>248</v>
       </c>
-      <c r="I10" s="69" t="s">
+      <c r="I10" s="65" t="s">
         <v>255</v>
       </c>
-      <c r="J10" s="67"/>
-      <c r="K10" s="67">
-        <v>1000</v>
-      </c>
-      <c r="L10" s="67">
+      <c r="J10" s="63"/>
+      <c r="K10" s="63">
+        <v>1000</v>
+      </c>
+      <c r="L10" s="63">
         <v>13.3057</v>
       </c>
-      <c r="M10" s="67">
-        <v>1</v>
-      </c>
-      <c r="N10" s="67">
+      <c r="M10" s="63">
+        <v>1</v>
+      </c>
+      <c r="N10" s="63">
         <v>75.155760313249203</v>
       </c>
-      <c r="O10" s="67">
+      <c r="O10" s="63">
         <v>0.83122061412608705</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="68">
+      <c r="A11" s="64">
         <v>2021</v>
       </c>
-      <c r="B11" s="68">
+      <c r="B11" s="64">
         <v>7</v>
       </c>
-      <c r="C11" s="68">
-        <v>1</v>
-      </c>
-      <c r="D11" s="68">
-        <v>0</v>
-      </c>
-      <c r="E11" s="68">
-        <v>1</v>
-      </c>
-      <c r="F11" s="68">
+      <c r="C11" s="64">
+        <v>1</v>
+      </c>
+      <c r="D11" s="64">
+        <v>0</v>
+      </c>
+      <c r="E11" s="64">
+        <v>1</v>
+      </c>
+      <c r="F11" s="64">
         <v>6</v>
       </c>
-      <c r="G11" s="68" t="s">
+      <c r="G11" s="64" t="s">
         <v>226</v>
       </c>
-      <c r="H11" s="68" t="s">
+      <c r="H11" s="64" t="s">
         <v>248</v>
       </c>
-      <c r="I11" s="70" t="s">
+      <c r="I11" s="66" t="s">
         <v>255</v>
       </c>
-      <c r="J11" s="68" t="s">
+      <c r="J11" s="64" t="s">
         <v>242</v>
       </c>
-      <c r="K11" s="68"/>
-      <c r="L11" s="68"/>
-      <c r="M11" s="68"/>
-      <c r="N11" s="68"/>
-      <c r="O11" s="68"/>
+      <c r="K11" s="64"/>
+      <c r="L11" s="64"/>
+      <c r="M11" s="64"/>
+      <c r="N11" s="64"/>
+      <c r="O11" s="64"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="69">
+        <v>2024</v>
+      </c>
+      <c r="B12" s="69">
+        <v>8</v>
+      </c>
+      <c r="C12" s="69">
+        <v>1</v>
+      </c>
+      <c r="D12" s="69">
+        <v>0</v>
+      </c>
+      <c r="E12" s="69">
+        <v>1</v>
+      </c>
+      <c r="F12" s="69">
+        <v>11</v>
+      </c>
+      <c r="G12" s="69" t="s">
+        <v>226</v>
+      </c>
+      <c r="H12" s="69" t="s">
+        <v>214</v>
+      </c>
+      <c r="I12" s="70" t="s">
+        <v>271</v>
+      </c>
+      <c r="J12" s="69"/>
+      <c r="K12" s="69">
+        <v>1000</v>
+      </c>
+      <c r="L12" s="69">
+        <v>8.6873000000000005</v>
+      </c>
+      <c r="M12" s="69">
+        <v>1</v>
+      </c>
+      <c r="N12" s="69">
+        <v>115.11056369643001</v>
+      </c>
+      <c r="O12" s="69">
+        <v>2.4150196263511101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="67">
+        <v>2024</v>
+      </c>
+      <c r="B13" s="67">
+        <v>8</v>
+      </c>
+      <c r="C13" s="67">
+        <v>1</v>
+      </c>
+      <c r="D13" s="67">
+        <v>0</v>
+      </c>
+      <c r="E13" s="67">
+        <v>1</v>
+      </c>
+      <c r="F13" s="67">
+        <v>12</v>
+      </c>
+      <c r="G13" s="67" t="s">
+        <v>226</v>
+      </c>
+      <c r="H13" s="67" t="s">
+        <v>214</v>
+      </c>
+      <c r="I13" s="68" t="s">
+        <v>271</v>
+      </c>
+      <c r="J13" s="67" t="s">
+        <v>242</v>
+      </c>
+      <c r="K13" s="67"/>
+      <c r="L13" s="67"/>
+      <c r="M13" s="67"/>
+      <c r="N13" s="67"/>
+      <c r="O13" s="67"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="69">
+        <v>2020</v>
+      </c>
+      <c r="B14" s="69">
+        <v>8</v>
+      </c>
+      <c r="C14" s="69">
+        <v>1</v>
+      </c>
+      <c r="D14" s="69">
+        <v>0</v>
+      </c>
+      <c r="E14" s="69">
+        <v>1</v>
+      </c>
+      <c r="F14" s="69">
+        <v>3</v>
+      </c>
+      <c r="G14" s="69" t="s">
+        <v>226</v>
+      </c>
+      <c r="H14" s="69" t="s">
+        <v>86</v>
+      </c>
+      <c r="I14" s="70" t="s">
+        <v>218</v>
+      </c>
+      <c r="J14" s="69"/>
+      <c r="K14" s="69">
+        <v>1000</v>
+      </c>
+      <c r="L14" s="69">
+        <v>8.4176000000000002</v>
+      </c>
+      <c r="M14" s="69">
+        <v>1</v>
+      </c>
+      <c r="N14" s="69">
+        <v>118.79870747006299</v>
+      </c>
+      <c r="O14" s="69">
+        <v>2.2908047722416698</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21422,319 +22420,319 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="62" t="s">
         <v>201</v>
       </c>
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="62" t="s">
         <v>202</v>
       </c>
-      <c r="C1" s="66" t="s">
+      <c r="C1" s="62" t="s">
         <v>203</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="D1" s="62" t="s">
         <v>204</v>
       </c>
-      <c r="E1" s="66" t="s">
+      <c r="E1" s="62" t="s">
         <v>205</v>
       </c>
-      <c r="F1" s="66" t="s">
+      <c r="F1" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="G1" s="66" t="s">
+      <c r="G1" s="62" t="s">
         <v>207</v>
       </c>
-      <c r="H1" s="66" t="s">
+      <c r="H1" s="62" t="s">
         <v>208</v>
       </c>
-      <c r="I1" s="66" t="s">
+      <c r="I1" s="62" t="s">
         <v>209</v>
       </c>
-      <c r="J1" s="66" t="s">
+      <c r="J1" s="62" t="s">
         <v>239</v>
       </c>
-      <c r="K1" s="66" t="s">
+      <c r="K1" s="62" t="s">
         <v>210</v>
       </c>
-      <c r="L1" s="66" t="s">
+      <c r="L1" s="62" t="s">
         <v>211</v>
       </c>
-      <c r="M1" s="66" t="s">
+      <c r="M1" s="62" t="s">
         <v>245</v>
       </c>
-      <c r="N1" s="66" t="s">
+      <c r="N1" s="62" t="s">
         <v>246</v>
       </c>
-      <c r="O1" s="66" t="s">
+      <c r="O1" s="62" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="67">
+      <c r="A2" s="63">
         <v>2025</v>
       </c>
-      <c r="B2" s="67">
+      <c r="B2" s="63">
         <v>8</v>
       </c>
-      <c r="C2" s="67">
-        <v>1</v>
-      </c>
-      <c r="D2" s="67">
-        <v>0</v>
-      </c>
-      <c r="E2" s="67">
-        <v>1</v>
-      </c>
-      <c r="F2" s="67">
+      <c r="C2" s="63">
+        <v>1</v>
+      </c>
+      <c r="D2" s="63">
+        <v>0</v>
+      </c>
+      <c r="E2" s="63">
+        <v>1</v>
+      </c>
+      <c r="F2" s="63">
         <v>16</v>
       </c>
-      <c r="G2" s="67" t="s">
+      <c r="G2" s="63" t="s">
         <v>228</v>
       </c>
-      <c r="H2" s="67" t="s">
+      <c r="H2" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="69" t="s">
+      <c r="I2" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67">
-        <v>1000</v>
-      </c>
-      <c r="L2" s="67">
-        <v>1000</v>
-      </c>
-      <c r="M2" s="67">
-        <v>1</v>
-      </c>
-      <c r="N2" s="67">
-        <v>1</v>
-      </c>
-      <c r="O2" s="67">
+      <c r="J2" s="63"/>
+      <c r="K2" s="63">
+        <v>1000</v>
+      </c>
+      <c r="L2" s="63">
+        <v>1000</v>
+      </c>
+      <c r="M2" s="63">
+        <v>1</v>
+      </c>
+      <c r="N2" s="63">
+        <v>1</v>
+      </c>
+      <c r="O2" s="63">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="68">
+      <c r="A3" s="64">
         <v>2024</v>
       </c>
-      <c r="B3" s="68">
+      <c r="B3" s="64">
         <v>2</v>
       </c>
-      <c r="C3" s="68">
-        <v>1</v>
-      </c>
-      <c r="D3" s="68">
-        <v>0</v>
-      </c>
-      <c r="E3" s="68">
-        <v>1</v>
-      </c>
-      <c r="F3" s="68">
+      <c r="C3" s="64">
+        <v>1</v>
+      </c>
+      <c r="D3" s="64">
+        <v>0</v>
+      </c>
+      <c r="E3" s="64">
+        <v>1</v>
+      </c>
+      <c r="F3" s="64">
         <v>16</v>
       </c>
-      <c r="G3" s="68" t="s">
+      <c r="G3" s="64" t="s">
         <v>228</v>
       </c>
-      <c r="H3" s="68" t="s">
+      <c r="H3" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="70" t="s">
+      <c r="I3" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68">
-        <v>1000</v>
-      </c>
-      <c r="L3" s="68">
-        <v>1000</v>
-      </c>
-      <c r="M3" s="68">
-        <v>1</v>
-      </c>
-      <c r="N3" s="68">
-        <v>1</v>
-      </c>
-      <c r="O3" s="68">
+      <c r="J3" s="64"/>
+      <c r="K3" s="64">
+        <v>1000</v>
+      </c>
+      <c r="L3" s="64">
+        <v>1000</v>
+      </c>
+      <c r="M3" s="64">
+        <v>1</v>
+      </c>
+      <c r="N3" s="64">
+        <v>1</v>
+      </c>
+      <c r="O3" s="64">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="67">
+      <c r="A4" s="63">
         <v>2024</v>
       </c>
-      <c r="B4" s="67">
+      <c r="B4" s="63">
         <v>8</v>
       </c>
-      <c r="C4" s="67">
-        <v>1</v>
-      </c>
-      <c r="D4" s="67">
-        <v>0</v>
-      </c>
-      <c r="E4" s="67">
-        <v>1</v>
-      </c>
-      <c r="F4" s="67">
+      <c r="C4" s="63">
+        <v>1</v>
+      </c>
+      <c r="D4" s="63">
+        <v>0</v>
+      </c>
+      <c r="E4" s="63">
+        <v>1</v>
+      </c>
+      <c r="F4" s="63">
         <v>16</v>
       </c>
-      <c r="G4" s="67" t="s">
+      <c r="G4" s="63" t="s">
         <v>228</v>
       </c>
-      <c r="H4" s="67" t="s">
+      <c r="H4" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="69" t="s">
+      <c r="I4" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67">
-        <v>1000</v>
-      </c>
-      <c r="L4" s="67">
-        <v>1000</v>
-      </c>
-      <c r="M4" s="67">
-        <v>1</v>
-      </c>
-      <c r="N4" s="67">
-        <v>1</v>
-      </c>
-      <c r="O4" s="67">
+      <c r="J4" s="63"/>
+      <c r="K4" s="63">
+        <v>1000</v>
+      </c>
+      <c r="L4" s="63">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="63">
+        <v>1</v>
+      </c>
+      <c r="N4" s="63">
+        <v>1</v>
+      </c>
+      <c r="O4" s="63">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="68">
+      <c r="A5" s="64">
         <v>2022</v>
       </c>
-      <c r="B5" s="68">
+      <c r="B5" s="64">
         <v>7</v>
       </c>
-      <c r="C5" s="68">
+      <c r="C5" s="64">
         <v>19</v>
       </c>
-      <c r="D5" s="68">
+      <c r="D5" s="64">
         <v>12</v>
       </c>
-      <c r="E5" s="68">
+      <c r="E5" s="64">
         <v>46</v>
       </c>
-      <c r="F5" s="68">
+      <c r="F5" s="64">
         <v>10</v>
       </c>
-      <c r="G5" s="68" t="s">
+      <c r="G5" s="64" t="s">
         <v>228</v>
       </c>
-      <c r="H5" s="68" t="s">
+      <c r="H5" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="70" t="s">
+      <c r="I5" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68">
-        <v>1000</v>
-      </c>
-      <c r="L5" s="68">
-        <v>1000</v>
-      </c>
-      <c r="M5" s="68">
-        <v>1</v>
-      </c>
-      <c r="N5" s="68">
-        <v>1</v>
-      </c>
-      <c r="O5" s="68">
+      <c r="J5" s="64"/>
+      <c r="K5" s="64">
+        <v>1000</v>
+      </c>
+      <c r="L5" s="64">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="64">
+        <v>1</v>
+      </c>
+      <c r="N5" s="64">
+        <v>1</v>
+      </c>
+      <c r="O5" s="64">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="67">
+      <c r="A6" s="63">
         <v>2021</v>
       </c>
-      <c r="B6" s="67">
-        <v>1</v>
-      </c>
-      <c r="C6" s="67">
-        <v>1</v>
-      </c>
-      <c r="D6" s="67">
-        <v>0</v>
-      </c>
-      <c r="E6" s="67">
-        <v>1</v>
-      </c>
-      <c r="F6" s="67">
+      <c r="B6" s="63">
+        <v>1</v>
+      </c>
+      <c r="C6" s="63">
+        <v>1</v>
+      </c>
+      <c r="D6" s="63">
+        <v>0</v>
+      </c>
+      <c r="E6" s="63">
+        <v>1</v>
+      </c>
+      <c r="F6" s="63">
         <v>14</v>
       </c>
-      <c r="G6" s="67" t="s">
+      <c r="G6" s="63" t="s">
         <v>228</v>
       </c>
-      <c r="H6" s="67" t="s">
+      <c r="H6" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="69" t="s">
+      <c r="I6" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67">
-        <v>1000</v>
-      </c>
-      <c r="L6" s="67">
-        <v>1000</v>
-      </c>
-      <c r="M6" s="67">
-        <v>1</v>
-      </c>
-      <c r="N6" s="67">
-        <v>1</v>
-      </c>
-      <c r="O6" s="67">
+      <c r="J6" s="63"/>
+      <c r="K6" s="63">
+        <v>1000</v>
+      </c>
+      <c r="L6" s="63">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="63">
+        <v>1</v>
+      </c>
+      <c r="N6" s="63">
+        <v>1</v>
+      </c>
+      <c r="O6" s="63">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="71">
+      <c r="A7" s="67">
         <v>2021</v>
       </c>
-      <c r="B7" s="71">
+      <c r="B7" s="67">
         <v>7</v>
       </c>
-      <c r="C7" s="71">
-        <v>1</v>
-      </c>
-      <c r="D7" s="71">
-        <v>0</v>
-      </c>
-      <c r="E7" s="71">
-        <v>1</v>
-      </c>
-      <c r="F7" s="71">
+      <c r="C7" s="67">
+        <v>1</v>
+      </c>
+      <c r="D7" s="67">
+        <v>0</v>
+      </c>
+      <c r="E7" s="67">
+        <v>1</v>
+      </c>
+      <c r="F7" s="67">
         <v>10</v>
       </c>
-      <c r="G7" s="71" t="s">
+      <c r="G7" s="67" t="s">
         <v>228</v>
       </c>
-      <c r="H7" s="71" t="s">
+      <c r="H7" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="72" t="s">
+      <c r="I7" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="71"/>
-      <c r="K7" s="71">
-        <v>1000</v>
-      </c>
-      <c r="L7" s="71">
-        <v>1000</v>
-      </c>
-      <c r="M7" s="71">
-        <v>1</v>
-      </c>
-      <c r="N7" s="71">
-        <v>1</v>
-      </c>
-      <c r="O7" s="71">
+      <c r="J7" s="67"/>
+      <c r="K7" s="67">
+        <v>1000</v>
+      </c>
+      <c r="L7" s="67">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="67">
+        <v>1</v>
+      </c>
+      <c r="N7" s="67">
+        <v>1</v>
+      </c>
+      <c r="O7" s="67">
         <v>1</v>
       </c>
     </row>
@@ -21763,619 +22761,619 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="62" t="s">
         <v>201</v>
       </c>
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="62" t="s">
         <v>202</v>
       </c>
-      <c r="C1" s="66" t="s">
+      <c r="C1" s="62" t="s">
         <v>203</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="D1" s="62" t="s">
         <v>204</v>
       </c>
-      <c r="E1" s="66" t="s">
+      <c r="E1" s="62" t="s">
         <v>205</v>
       </c>
-      <c r="F1" s="66" t="s">
+      <c r="F1" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="G1" s="66" t="s">
+      <c r="G1" s="62" t="s">
         <v>207</v>
       </c>
-      <c r="H1" s="66" t="s">
+      <c r="H1" s="62" t="s">
         <v>208</v>
       </c>
-      <c r="I1" s="66" t="s">
+      <c r="I1" s="62" t="s">
         <v>209</v>
       </c>
-      <c r="J1" s="66" t="s">
+      <c r="J1" s="62" t="s">
         <v>239</v>
       </c>
-      <c r="K1" s="66" t="s">
+      <c r="K1" s="62" t="s">
         <v>210</v>
       </c>
-      <c r="L1" s="66" t="s">
+      <c r="L1" s="62" t="s">
         <v>211</v>
       </c>
-      <c r="M1" s="66" t="s">
+      <c r="M1" s="62" t="s">
         <v>245</v>
       </c>
-      <c r="N1" s="66" t="s">
+      <c r="N1" s="62" t="s">
         <v>246</v>
       </c>
-      <c r="O1" s="66" t="s">
+      <c r="O1" s="62" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="67">
+      <c r="A2" s="63">
         <v>2021</v>
       </c>
-      <c r="B2" s="67">
-        <v>1</v>
-      </c>
-      <c r="C2" s="67">
-        <v>1</v>
-      </c>
-      <c r="D2" s="67">
-        <v>0</v>
-      </c>
-      <c r="E2" s="67">
-        <v>1</v>
-      </c>
-      <c r="F2" s="67">
+      <c r="B2" s="63">
+        <v>1</v>
+      </c>
+      <c r="C2" s="63">
+        <v>1</v>
+      </c>
+      <c r="D2" s="63">
+        <v>0</v>
+      </c>
+      <c r="E2" s="63">
+        <v>1</v>
+      </c>
+      <c r="F2" s="63">
         <v>4</v>
       </c>
-      <c r="G2" s="67" t="s">
+      <c r="G2" s="63" t="s">
         <v>230</v>
       </c>
-      <c r="H2" s="67" t="s">
+      <c r="H2" s="63" t="s">
         <v>231</v>
       </c>
-      <c r="I2" s="69" t="s">
+      <c r="I2" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="68">
+      <c r="A3" s="64">
         <v>2021</v>
       </c>
-      <c r="B3" s="68">
-        <v>1</v>
-      </c>
-      <c r="C3" s="68">
-        <v>1</v>
-      </c>
-      <c r="D3" s="68">
-        <v>0</v>
-      </c>
-      <c r="E3" s="68">
-        <v>1</v>
-      </c>
-      <c r="F3" s="68">
+      <c r="B3" s="64">
+        <v>1</v>
+      </c>
+      <c r="C3" s="64">
+        <v>1</v>
+      </c>
+      <c r="D3" s="64">
+        <v>0</v>
+      </c>
+      <c r="E3" s="64">
+        <v>1</v>
+      </c>
+      <c r="F3" s="64">
         <v>5</v>
       </c>
-      <c r="G3" s="68" t="s">
+      <c r="G3" s="64" t="s">
         <v>230</v>
       </c>
-      <c r="H3" s="68" t="s">
+      <c r="H3" s="64" t="s">
         <v>232</v>
       </c>
-      <c r="I3" s="70" t="s">
+      <c r="I3" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="67">
+      <c r="A4" s="63">
         <v>2021</v>
       </c>
-      <c r="B4" s="67">
-        <v>1</v>
-      </c>
-      <c r="C4" s="67">
-        <v>1</v>
-      </c>
-      <c r="D4" s="67">
-        <v>0</v>
-      </c>
-      <c r="E4" s="67">
-        <v>1</v>
-      </c>
-      <c r="F4" s="67">
+      <c r="B4" s="63">
+        <v>1</v>
+      </c>
+      <c r="C4" s="63">
+        <v>1</v>
+      </c>
+      <c r="D4" s="63">
+        <v>0</v>
+      </c>
+      <c r="E4" s="63">
+        <v>1</v>
+      </c>
+      <c r="F4" s="63">
         <v>6</v>
       </c>
-      <c r="G4" s="67" t="s">
+      <c r="G4" s="63" t="s">
         <v>230</v>
       </c>
-      <c r="H4" s="67" t="s">
+      <c r="H4" s="63" t="s">
         <v>233</v>
       </c>
-      <c r="I4" s="69" t="s">
+      <c r="I4" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="67"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="63"/>
+      <c r="L4" s="63"/>
+      <c r="M4" s="63"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="63"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="68">
+      <c r="A5" s="64">
         <v>2021</v>
       </c>
-      <c r="B5" s="68">
-        <v>1</v>
-      </c>
-      <c r="C5" s="68">
-        <v>1</v>
-      </c>
-      <c r="D5" s="68">
-        <v>0</v>
-      </c>
-      <c r="E5" s="68">
-        <v>1</v>
-      </c>
-      <c r="F5" s="68">
+      <c r="B5" s="64">
+        <v>1</v>
+      </c>
+      <c r="C5" s="64">
+        <v>1</v>
+      </c>
+      <c r="D5" s="64">
+        <v>0</v>
+      </c>
+      <c r="E5" s="64">
+        <v>1</v>
+      </c>
+      <c r="F5" s="64">
         <v>10</v>
       </c>
-      <c r="G5" s="68" t="s">
+      <c r="G5" s="64" t="s">
         <v>230</v>
       </c>
-      <c r="H5" s="68" t="s">
+      <c r="H5" s="64" t="s">
         <v>234</v>
       </c>
-      <c r="I5" s="70" t="s">
+      <c r="I5" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68">
-        <v>1000</v>
-      </c>
-      <c r="L5" s="68">
-        <v>1000</v>
-      </c>
-      <c r="M5" s="68">
-        <v>1</v>
-      </c>
-      <c r="N5" s="68">
-        <v>1</v>
-      </c>
-      <c r="O5" s="68">
+      <c r="J5" s="64"/>
+      <c r="K5" s="64">
+        <v>1000</v>
+      </c>
+      <c r="L5" s="64">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="64">
+        <v>1</v>
+      </c>
+      <c r="N5" s="64">
+        <v>1</v>
+      </c>
+      <c r="O5" s="64">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="67">
+      <c r="A6" s="63">
         <v>2021</v>
       </c>
-      <c r="B6" s="67">
-        <v>1</v>
-      </c>
-      <c r="C6" s="67">
-        <v>1</v>
-      </c>
-      <c r="D6" s="67">
-        <v>0</v>
-      </c>
-      <c r="E6" s="67">
-        <v>1</v>
-      </c>
-      <c r="F6" s="67">
+      <c r="B6" s="63">
+        <v>1</v>
+      </c>
+      <c r="C6" s="63">
+        <v>1</v>
+      </c>
+      <c r="D6" s="63">
+        <v>0</v>
+      </c>
+      <c r="E6" s="63">
+        <v>1</v>
+      </c>
+      <c r="F6" s="63">
         <v>11</v>
       </c>
-      <c r="G6" s="67" t="s">
+      <c r="G6" s="63" t="s">
         <v>230</v>
       </c>
-      <c r="H6" s="67" t="s">
+      <c r="H6" s="63" t="s">
         <v>235</v>
       </c>
-      <c r="I6" s="69" t="s">
+      <c r="I6" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67">
-        <v>1000</v>
-      </c>
-      <c r="L6" s="67">
-        <v>1000</v>
-      </c>
-      <c r="M6" s="67">
-        <v>1</v>
-      </c>
-      <c r="N6" s="67">
-        <v>1</v>
-      </c>
-      <c r="O6" s="67">
+      <c r="J6" s="63"/>
+      <c r="K6" s="63">
+        <v>1000</v>
+      </c>
+      <c r="L6" s="63">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="63">
+        <v>1</v>
+      </c>
+      <c r="N6" s="63">
+        <v>1</v>
+      </c>
+      <c r="O6" s="63">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="68">
+      <c r="A7" s="64">
         <v>2021</v>
       </c>
-      <c r="B7" s="68">
-        <v>1</v>
-      </c>
-      <c r="C7" s="68">
-        <v>1</v>
-      </c>
-      <c r="D7" s="68">
-        <v>0</v>
-      </c>
-      <c r="E7" s="68">
-        <v>1</v>
-      </c>
-      <c r="F7" s="68">
+      <c r="B7" s="64">
+        <v>1</v>
+      </c>
+      <c r="C7" s="64">
+        <v>1</v>
+      </c>
+      <c r="D7" s="64">
+        <v>0</v>
+      </c>
+      <c r="E7" s="64">
+        <v>1</v>
+      </c>
+      <c r="F7" s="64">
         <v>12</v>
       </c>
-      <c r="G7" s="68" t="s">
+      <c r="G7" s="64" t="s">
         <v>230</v>
       </c>
-      <c r="H7" s="68" t="s">
+      <c r="H7" s="64" t="s">
         <v>236</v>
       </c>
-      <c r="I7" s="70" t="s">
+      <c r="I7" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="J7" s="68"/>
-      <c r="K7" s="68">
-        <v>1000</v>
-      </c>
-      <c r="L7" s="68">
-        <v>1000</v>
-      </c>
-      <c r="M7" s="68">
-        <v>1</v>
-      </c>
-      <c r="N7" s="68">
-        <v>1</v>
-      </c>
-      <c r="O7" s="68">
+      <c r="J7" s="64"/>
+      <c r="K7" s="64">
+        <v>1000</v>
+      </c>
+      <c r="L7" s="64">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="64">
+        <v>1</v>
+      </c>
+      <c r="N7" s="64">
+        <v>1</v>
+      </c>
+      <c r="O7" s="64">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="67">
+      <c r="A8" s="63">
         <v>2021</v>
       </c>
-      <c r="B8" s="67">
-        <v>1</v>
-      </c>
-      <c r="C8" s="67">
-        <v>1</v>
-      </c>
-      <c r="D8" s="67">
-        <v>0</v>
-      </c>
-      <c r="E8" s="67">
-        <v>1</v>
-      </c>
-      <c r="F8" s="67">
+      <c r="B8" s="63">
+        <v>1</v>
+      </c>
+      <c r="C8" s="63">
+        <v>1</v>
+      </c>
+      <c r="D8" s="63">
+        <v>0</v>
+      </c>
+      <c r="E8" s="63">
+        <v>1</v>
+      </c>
+      <c r="F8" s="63">
         <v>13</v>
       </c>
-      <c r="G8" s="67" t="s">
+      <c r="G8" s="63" t="s">
         <v>230</v>
       </c>
-      <c r="H8" s="67" t="s">
+      <c r="H8" s="63" t="s">
         <v>237</v>
       </c>
-      <c r="I8" s="69" t="s">
+      <c r="I8" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="J8" s="67"/>
-      <c r="K8" s="67">
-        <v>1000</v>
-      </c>
-      <c r="L8" s="67">
-        <v>1000</v>
-      </c>
-      <c r="M8" s="67">
-        <v>1</v>
-      </c>
-      <c r="N8" s="67">
-        <v>1</v>
-      </c>
-      <c r="O8" s="67">
+      <c r="J8" s="63"/>
+      <c r="K8" s="63">
+        <v>1000</v>
+      </c>
+      <c r="L8" s="63">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="63">
+        <v>1</v>
+      </c>
+      <c r="N8" s="63">
+        <v>1</v>
+      </c>
+      <c r="O8" s="63">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="68">
+      <c r="A9" s="64">
         <v>2020</v>
       </c>
-      <c r="B9" s="68">
+      <c r="B9" s="64">
         <v>8</v>
       </c>
-      <c r="C9" s="68">
-        <v>1</v>
-      </c>
-      <c r="D9" s="68">
-        <v>0</v>
-      </c>
-      <c r="E9" s="68">
-        <v>1</v>
-      </c>
-      <c r="F9" s="68">
+      <c r="C9" s="64">
+        <v>1</v>
+      </c>
+      <c r="D9" s="64">
+        <v>0</v>
+      </c>
+      <c r="E9" s="64">
+        <v>1</v>
+      </c>
+      <c r="F9" s="64">
         <v>4</v>
       </c>
-      <c r="G9" s="68" t="s">
+      <c r="G9" s="64" t="s">
         <v>230</v>
       </c>
-      <c r="H9" s="68" t="s">
+      <c r="H9" s="64" t="s">
         <v>231</v>
       </c>
-      <c r="I9" s="70" t="s">
+      <c r="I9" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="J9" s="68"/>
-      <c r="K9" s="68"/>
-      <c r="L9" s="68"/>
-      <c r="M9" s="68"/>
-      <c r="N9" s="68"/>
-      <c r="O9" s="68"/>
+      <c r="J9" s="64"/>
+      <c r="K9" s="64"/>
+      <c r="L9" s="64"/>
+      <c r="M9" s="64"/>
+      <c r="N9" s="64"/>
+      <c r="O9" s="64"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="67">
+      <c r="A10" s="63">
         <v>2020</v>
       </c>
-      <c r="B10" s="67">
+      <c r="B10" s="63">
         <v>8</v>
       </c>
-      <c r="C10" s="67">
-        <v>1</v>
-      </c>
-      <c r="D10" s="67">
-        <v>0</v>
-      </c>
-      <c r="E10" s="67">
-        <v>1</v>
-      </c>
-      <c r="F10" s="67">
+      <c r="C10" s="63">
+        <v>1</v>
+      </c>
+      <c r="D10" s="63">
+        <v>0</v>
+      </c>
+      <c r="E10" s="63">
+        <v>1</v>
+      </c>
+      <c r="F10" s="63">
         <v>5</v>
       </c>
-      <c r="G10" s="67" t="s">
+      <c r="G10" s="63" t="s">
         <v>230</v>
       </c>
-      <c r="H10" s="67" t="s">
+      <c r="H10" s="63" t="s">
         <v>232</v>
       </c>
-      <c r="I10" s="69" t="s">
+      <c r="I10" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="J10" s="67"/>
-      <c r="K10" s="67"/>
-      <c r="L10" s="67"/>
-      <c r="M10" s="67"/>
-      <c r="N10" s="67"/>
-      <c r="O10" s="67"/>
+      <c r="J10" s="63"/>
+      <c r="K10" s="63"/>
+      <c r="L10" s="63"/>
+      <c r="M10" s="63"/>
+      <c r="N10" s="63"/>
+      <c r="O10" s="63"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="68">
+      <c r="A11" s="64">
         <v>2020</v>
       </c>
-      <c r="B11" s="68">
+      <c r="B11" s="64">
         <v>8</v>
       </c>
-      <c r="C11" s="68">
-        <v>1</v>
-      </c>
-      <c r="D11" s="68">
-        <v>0</v>
-      </c>
-      <c r="E11" s="68">
-        <v>1</v>
-      </c>
-      <c r="F11" s="68">
+      <c r="C11" s="64">
+        <v>1</v>
+      </c>
+      <c r="D11" s="64">
+        <v>0</v>
+      </c>
+      <c r="E11" s="64">
+        <v>1</v>
+      </c>
+      <c r="F11" s="64">
         <v>6</v>
       </c>
-      <c r="G11" s="68" t="s">
+      <c r="G11" s="64" t="s">
         <v>230</v>
       </c>
-      <c r="H11" s="68" t="s">
+      <c r="H11" s="64" t="s">
         <v>233</v>
       </c>
-      <c r="I11" s="70" t="s">
+      <c r="I11" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="J11" s="68"/>
-      <c r="K11" s="68"/>
-      <c r="L11" s="68"/>
-      <c r="M11" s="68"/>
-      <c r="N11" s="68"/>
-      <c r="O11" s="68"/>
+      <c r="J11" s="64"/>
+      <c r="K11" s="64"/>
+      <c r="L11" s="64"/>
+      <c r="M11" s="64"/>
+      <c r="N11" s="64"/>
+      <c r="O11" s="64"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="67">
+      <c r="A12" s="63">
         <v>2020</v>
       </c>
-      <c r="B12" s="67">
+      <c r="B12" s="63">
         <v>8</v>
       </c>
-      <c r="C12" s="67">
-        <v>1</v>
-      </c>
-      <c r="D12" s="67">
-        <v>0</v>
-      </c>
-      <c r="E12" s="67">
-        <v>1</v>
-      </c>
-      <c r="F12" s="67">
+      <c r="C12" s="63">
+        <v>1</v>
+      </c>
+      <c r="D12" s="63">
+        <v>0</v>
+      </c>
+      <c r="E12" s="63">
+        <v>1</v>
+      </c>
+      <c r="F12" s="63">
         <v>10</v>
       </c>
-      <c r="G12" s="67" t="s">
+      <c r="G12" s="63" t="s">
         <v>230</v>
       </c>
-      <c r="H12" s="67" t="s">
+      <c r="H12" s="63" t="s">
         <v>234</v>
       </c>
-      <c r="I12" s="69" t="s">
+      <c r="I12" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="J12" s="67"/>
-      <c r="K12" s="67">
-        <v>1000</v>
-      </c>
-      <c r="L12" s="67">
-        <v>1000</v>
-      </c>
-      <c r="M12" s="67">
-        <v>1</v>
-      </c>
-      <c r="N12" s="67">
-        <v>1</v>
-      </c>
-      <c r="O12" s="67">
+      <c r="J12" s="63"/>
+      <c r="K12" s="63">
+        <v>1000</v>
+      </c>
+      <c r="L12" s="63">
+        <v>1000</v>
+      </c>
+      <c r="M12" s="63">
+        <v>1</v>
+      </c>
+      <c r="N12" s="63">
+        <v>1</v>
+      </c>
+      <c r="O12" s="63">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="68">
+      <c r="A13" s="64">
         <v>2020</v>
       </c>
-      <c r="B13" s="68">
+      <c r="B13" s="64">
         <v>8</v>
       </c>
-      <c r="C13" s="68">
-        <v>1</v>
-      </c>
-      <c r="D13" s="68">
-        <v>0</v>
-      </c>
-      <c r="E13" s="68">
-        <v>1</v>
-      </c>
-      <c r="F13" s="68">
+      <c r="C13" s="64">
+        <v>1</v>
+      </c>
+      <c r="D13" s="64">
+        <v>0</v>
+      </c>
+      <c r="E13" s="64">
+        <v>1</v>
+      </c>
+      <c r="F13" s="64">
         <v>11</v>
       </c>
-      <c r="G13" s="68" t="s">
+      <c r="G13" s="64" t="s">
         <v>230</v>
       </c>
-      <c r="H13" s="68" t="s">
+      <c r="H13" s="64" t="s">
         <v>235</v>
       </c>
-      <c r="I13" s="70" t="s">
+      <c r="I13" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="J13" s="68"/>
-      <c r="K13" s="68">
-        <v>1000</v>
-      </c>
-      <c r="L13" s="68">
-        <v>1000</v>
-      </c>
-      <c r="M13" s="68">
-        <v>1</v>
-      </c>
-      <c r="N13" s="68">
-        <v>1</v>
-      </c>
-      <c r="O13" s="68">
+      <c r="J13" s="64"/>
+      <c r="K13" s="64">
+        <v>1000</v>
+      </c>
+      <c r="L13" s="64">
+        <v>1000</v>
+      </c>
+      <c r="M13" s="64">
+        <v>1</v>
+      </c>
+      <c r="N13" s="64">
+        <v>1</v>
+      </c>
+      <c r="O13" s="64">
         <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="67">
+      <c r="A14" s="63">
         <v>2020</v>
       </c>
-      <c r="B14" s="67">
+      <c r="B14" s="63">
         <v>8</v>
       </c>
-      <c r="C14" s="67">
-        <v>1</v>
-      </c>
-      <c r="D14" s="67">
-        <v>0</v>
-      </c>
-      <c r="E14" s="67">
-        <v>1</v>
-      </c>
-      <c r="F14" s="67">
+      <c r="C14" s="63">
+        <v>1</v>
+      </c>
+      <c r="D14" s="63">
+        <v>0</v>
+      </c>
+      <c r="E14" s="63">
+        <v>1</v>
+      </c>
+      <c r="F14" s="63">
         <v>12</v>
       </c>
-      <c r="G14" s="67" t="s">
+      <c r="G14" s="63" t="s">
         <v>230</v>
       </c>
-      <c r="H14" s="67" t="s">
+      <c r="H14" s="63" t="s">
         <v>236</v>
       </c>
-      <c r="I14" s="69" t="s">
+      <c r="I14" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="J14" s="67"/>
-      <c r="K14" s="67">
-        <v>1000</v>
-      </c>
-      <c r="L14" s="67">
-        <v>1000</v>
-      </c>
-      <c r="M14" s="67">
-        <v>1</v>
-      </c>
-      <c r="N14" s="67">
-        <v>1</v>
-      </c>
-      <c r="O14" s="67">
+      <c r="J14" s="63"/>
+      <c r="K14" s="63">
+        <v>1000</v>
+      </c>
+      <c r="L14" s="63">
+        <v>1000</v>
+      </c>
+      <c r="M14" s="63">
+        <v>1</v>
+      </c>
+      <c r="N14" s="63">
+        <v>1</v>
+      </c>
+      <c r="O14" s="63">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="71">
+      <c r="A15" s="67">
         <v>2020</v>
       </c>
-      <c r="B15" s="71">
+      <c r="B15" s="67">
         <v>8</v>
       </c>
-      <c r="C15" s="71">
-        <v>1</v>
-      </c>
-      <c r="D15" s="71">
-        <v>0</v>
-      </c>
-      <c r="E15" s="71">
-        <v>1</v>
-      </c>
-      <c r="F15" s="71">
+      <c r="C15" s="67">
+        <v>1</v>
+      </c>
+      <c r="D15" s="67">
+        <v>0</v>
+      </c>
+      <c r="E15" s="67">
+        <v>1</v>
+      </c>
+      <c r="F15" s="67">
         <v>13</v>
       </c>
-      <c r="G15" s="71" t="s">
+      <c r="G15" s="67" t="s">
         <v>230</v>
       </c>
-      <c r="H15" s="71" t="s">
+      <c r="H15" s="67" t="s">
         <v>237</v>
       </c>
-      <c r="I15" s="72" t="s">
+      <c r="I15" s="68" t="s">
         <v>219</v>
       </c>
-      <c r="J15" s="71"/>
-      <c r="K15" s="71">
-        <v>1000</v>
-      </c>
-      <c r="L15" s="71">
-        <v>1000</v>
-      </c>
-      <c r="M15" s="71">
-        <v>1</v>
-      </c>
-      <c r="N15" s="71">
-        <v>1</v>
-      </c>
-      <c r="O15" s="71">
+      <c r="J15" s="67"/>
+      <c r="K15" s="67">
+        <v>1000</v>
+      </c>
+      <c r="L15" s="67">
+        <v>1000</v>
+      </c>
+      <c r="M15" s="67">
+        <v>1</v>
+      </c>
+      <c r="N15" s="67">
+        <v>1</v>
+      </c>
+      <c r="O15" s="67">
         <v>1</v>
       </c>
     </row>
@@ -22404,156 +23402,156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="62" t="s">
         <v>201</v>
       </c>
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="62" t="s">
         <v>202</v>
       </c>
-      <c r="C1" s="66" t="s">
+      <c r="C1" s="62" t="s">
         <v>203</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="D1" s="62" t="s">
         <v>204</v>
       </c>
-      <c r="E1" s="66" t="s">
+      <c r="E1" s="62" t="s">
         <v>205</v>
       </c>
-      <c r="F1" s="66" t="s">
+      <c r="F1" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="G1" s="66" t="s">
+      <c r="G1" s="62" t="s">
         <v>207</v>
       </c>
-      <c r="H1" s="66" t="s">
+      <c r="H1" s="62" t="s">
         <v>208</v>
       </c>
-      <c r="I1" s="66" t="s">
+      <c r="I1" s="62" t="s">
         <v>209</v>
       </c>
-      <c r="J1" s="66" t="s">
+      <c r="J1" s="62" t="s">
         <v>239</v>
       </c>
-      <c r="K1" s="66" t="s">
+      <c r="K1" s="62" t="s">
         <v>210</v>
       </c>
-      <c r="L1" s="66" t="s">
+      <c r="L1" s="62" t="s">
         <v>211</v>
       </c>
-      <c r="M1" s="66" t="s">
+      <c r="M1" s="62" t="s">
         <v>245</v>
       </c>
-      <c r="N1" s="66" t="s">
+      <c r="N1" s="62" t="s">
         <v>246</v>
       </c>
-      <c r="O1" s="66" t="s">
+      <c r="O1" s="62" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="67">
+      <c r="A2" s="63">
         <v>2025</v>
       </c>
-      <c r="B2" s="67">
+      <c r="B2" s="63">
         <v>8</v>
       </c>
-      <c r="C2" s="67">
-        <v>1</v>
-      </c>
-      <c r="D2" s="67">
-        <v>0</v>
-      </c>
-      <c r="E2" s="67">
-        <v>1</v>
-      </c>
-      <c r="F2" s="67">
-        <v>1</v>
-      </c>
-      <c r="G2" s="67" t="s">
+      <c r="C2" s="63">
+        <v>1</v>
+      </c>
+      <c r="D2" s="63">
+        <v>0</v>
+      </c>
+      <c r="E2" s="63">
+        <v>1</v>
+      </c>
+      <c r="F2" s="63">
+        <v>1</v>
+      </c>
+      <c r="G2" s="63" t="s">
         <v>222</v>
       </c>
-      <c r="H2" s="67" t="s">
+      <c r="H2" s="63" t="s">
         <v>223</v>
       </c>
-      <c r="I2" s="69" t="s">
+      <c r="I2" s="65" t="s">
         <v>254</v>
       </c>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="68">
+      <c r="A3" s="64">
         <v>2024</v>
       </c>
-      <c r="B3" s="68">
+      <c r="B3" s="64">
         <v>2</v>
       </c>
-      <c r="C3" s="68">
-        <v>1</v>
-      </c>
-      <c r="D3" s="68">
-        <v>0</v>
-      </c>
-      <c r="E3" s="68">
-        <v>1</v>
-      </c>
-      <c r="F3" s="68">
-        <v>1</v>
-      </c>
-      <c r="G3" s="68" t="s">
+      <c r="C3" s="64">
+        <v>1</v>
+      </c>
+      <c r="D3" s="64">
+        <v>0</v>
+      </c>
+      <c r="E3" s="64">
+        <v>1</v>
+      </c>
+      <c r="F3" s="64">
+        <v>1</v>
+      </c>
+      <c r="G3" s="64" t="s">
         <v>222</v>
       </c>
-      <c r="H3" s="68" t="s">
+      <c r="H3" s="64" t="s">
         <v>223</v>
       </c>
-      <c r="I3" s="70" t="s">
+      <c r="I3" s="66" t="s">
         <v>254</v>
       </c>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="73">
+      <c r="A4" s="69">
         <v>2024</v>
       </c>
-      <c r="B4" s="73">
+      <c r="B4" s="69">
         <v>8</v>
       </c>
-      <c r="C4" s="73">
-        <v>1</v>
-      </c>
-      <c r="D4" s="73">
-        <v>0</v>
-      </c>
-      <c r="E4" s="73">
-        <v>1</v>
-      </c>
-      <c r="F4" s="73">
-        <v>1</v>
-      </c>
-      <c r="G4" s="73" t="s">
+      <c r="C4" s="69">
+        <v>1</v>
+      </c>
+      <c r="D4" s="69">
+        <v>0</v>
+      </c>
+      <c r="E4" s="69">
+        <v>1</v>
+      </c>
+      <c r="F4" s="69">
+        <v>1</v>
+      </c>
+      <c r="G4" s="69" t="s">
         <v>222</v>
       </c>
-      <c r="H4" s="73" t="s">
+      <c r="H4" s="69" t="s">
         <v>223</v>
       </c>
-      <c r="I4" s="74" t="s">
+      <c r="I4" s="70" t="s">
         <v>254</v>
       </c>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22580,156 +23578,156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="62" t="s">
         <v>201</v>
       </c>
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="62" t="s">
         <v>202</v>
       </c>
-      <c r="C1" s="66" t="s">
+      <c r="C1" s="62" t="s">
         <v>203</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="D1" s="62" t="s">
         <v>204</v>
       </c>
-      <c r="E1" s="66" t="s">
+      <c r="E1" s="62" t="s">
         <v>205</v>
       </c>
-      <c r="F1" s="66" t="s">
+      <c r="F1" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="G1" s="66" t="s">
+      <c r="G1" s="62" t="s">
         <v>207</v>
       </c>
-      <c r="H1" s="66" t="s">
+      <c r="H1" s="62" t="s">
         <v>208</v>
       </c>
-      <c r="I1" s="66" t="s">
+      <c r="I1" s="62" t="s">
         <v>209</v>
       </c>
-      <c r="J1" s="66" t="s">
+      <c r="J1" s="62" t="s">
         <v>239</v>
       </c>
-      <c r="K1" s="66" t="s">
+      <c r="K1" s="62" t="s">
         <v>210</v>
       </c>
-      <c r="L1" s="66" t="s">
+      <c r="L1" s="62" t="s">
         <v>211</v>
       </c>
-      <c r="M1" s="66" t="s">
+      <c r="M1" s="62" t="s">
         <v>245</v>
       </c>
-      <c r="N1" s="66" t="s">
+      <c r="N1" s="62" t="s">
         <v>246</v>
       </c>
-      <c r="O1" s="66" t="s">
+      <c r="O1" s="62" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="67">
+      <c r="A2" s="63">
         <v>2025</v>
       </c>
-      <c r="B2" s="67">
+      <c r="B2" s="63">
         <v>8</v>
       </c>
-      <c r="C2" s="67">
-        <v>1</v>
-      </c>
-      <c r="D2" s="67">
-        <v>0</v>
-      </c>
-      <c r="E2" s="67">
-        <v>1</v>
-      </c>
-      <c r="F2" s="67">
+      <c r="C2" s="63">
+        <v>1</v>
+      </c>
+      <c r="D2" s="63">
+        <v>0</v>
+      </c>
+      <c r="E2" s="63">
+        <v>1</v>
+      </c>
+      <c r="F2" s="63">
         <v>2</v>
       </c>
-      <c r="G2" s="67" t="s">
+      <c r="G2" s="63" t="s">
         <v>224</v>
       </c>
-      <c r="H2" s="67" t="s">
+      <c r="H2" s="63" t="s">
         <v>223</v>
       </c>
-      <c r="I2" s="69" t="s">
+      <c r="I2" s="65" t="s">
         <v>254</v>
       </c>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="68">
+      <c r="A3" s="64">
         <v>2024</v>
       </c>
-      <c r="B3" s="68">
+      <c r="B3" s="64">
         <v>2</v>
       </c>
-      <c r="C3" s="68">
-        <v>1</v>
-      </c>
-      <c r="D3" s="68">
-        <v>0</v>
-      </c>
-      <c r="E3" s="68">
-        <v>1</v>
-      </c>
-      <c r="F3" s="68">
+      <c r="C3" s="64">
+        <v>1</v>
+      </c>
+      <c r="D3" s="64">
+        <v>0</v>
+      </c>
+      <c r="E3" s="64">
+        <v>1</v>
+      </c>
+      <c r="F3" s="64">
         <v>2</v>
       </c>
-      <c r="G3" s="68" t="s">
+      <c r="G3" s="64" t="s">
         <v>224</v>
       </c>
-      <c r="H3" s="68" t="s">
+      <c r="H3" s="64" t="s">
         <v>223</v>
       </c>
-      <c r="I3" s="70" t="s">
+      <c r="I3" s="66" t="s">
         <v>254</v>
       </c>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="73">
+      <c r="A4" s="69">
         <v>2024</v>
       </c>
-      <c r="B4" s="73">
+      <c r="B4" s="69">
         <v>8</v>
       </c>
-      <c r="C4" s="73">
-        <v>1</v>
-      </c>
-      <c r="D4" s="73">
-        <v>0</v>
-      </c>
-      <c r="E4" s="73">
-        <v>1</v>
-      </c>
-      <c r="F4" s="73">
+      <c r="C4" s="69">
+        <v>1</v>
+      </c>
+      <c r="D4" s="69">
+        <v>0</v>
+      </c>
+      <c r="E4" s="69">
+        <v>1</v>
+      </c>
+      <c r="F4" s="69">
         <v>2</v>
       </c>
-      <c r="G4" s="73" t="s">
+      <c r="G4" s="69" t="s">
         <v>224</v>
       </c>
-      <c r="H4" s="73" t="s">
+      <c r="H4" s="69" t="s">
         <v>223</v>
       </c>
-      <c r="I4" s="74" t="s">
+      <c r="I4" s="70" t="s">
         <v>254</v>
       </c>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/STW programs/STW_sitefile_and_mapping.xlsx
+++ b/STW programs/STW_sitefile_and_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\finnf\Desktop\LEI-SRML-Intern-Project\STW programs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/finnfujimura/Desktop/LEI-SRML-Intern-Project/STW programs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8290B3-06D5-444F-A12F-B9162221781A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9144FD34-92E7-E647-BA79-D60AC4971DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="STW site" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2667" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2613" uniqueCount="273">
   <si>
     <t>M = 1000/R</t>
   </si>
@@ -836,9 +836,6 @@
     <t>01/01/2020 00:01</t>
   </si>
   <si>
-    <t>08/01/2020 00:01</t>
-  </si>
-  <si>
     <t>01/01/2021 00:01</t>
   </si>
   <si>
@@ -858,6 +855,12 @@
   </si>
   <si>
     <t>151960</t>
+  </si>
+  <si>
+    <t>08/12/2020 11:35</t>
+  </si>
+  <si>
+    <t>mv</t>
   </si>
 </sst>
 </file>
@@ -1032,12 +1035,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1318,7 +1323,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -1610,19 +1615,6 @@
       <top style="thin">
         <color rgb="FF95B3D7"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF95B3D7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF95B3D7"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF95B3D7"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -1696,7 +1688,7 @@
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1794,6 +1786,11 @@
     <xf numFmtId="49" fontId="22" fillId="48" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="47" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="22" fillId="47" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="48" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="48" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="47" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="47" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1806,13 +1803,7 @@
     <xf numFmtId="0" fontId="16" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="48" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="47" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="48" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="47" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="47" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="47" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -4676,10 +4667,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E2971E8D-EC9F-4E58-B2D2-0AE0519F728F}" name="Table2" displayName="Table2" ref="A1:O19" totalsRowShown="0" headerRowDxfId="96" headerRowBorderDxfId="95" tableBorderDxfId="94" totalsRowBorderDxfId="93">
-  <autoFilter ref="A1:O19" xr:uid="{E2971E8D-EC9F-4E58-B2D2-0AE0519F728F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O19">
-    <sortCondition ref="A1:A19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E2971E8D-EC9F-4E58-B2D2-0AE0519F728F}" name="Table2" displayName="Table2" ref="A1:O14" totalsRowShown="0" headerRowDxfId="96" headerRowBorderDxfId="95" tableBorderDxfId="94" totalsRowBorderDxfId="93">
+  <autoFilter ref="A1:O14" xr:uid="{E2971E8D-EC9F-4E58-B2D2-0AE0519F728F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O14">
+    <sortCondition ref="A1:A14"/>
   </sortState>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{9EF617D4-F72F-428C-8C02-BFC8CEB705E4}" name="Year" dataDxfId="92"/>
@@ -4703,8 +4694,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9FE5D8B3-8BD3-4ECC-BD36-0871F9AB381A}" name="Table4" displayName="Table4" ref="A1:O20" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86" tableBorderDxfId="84" totalsRowBorderDxfId="83">
-  <autoFilter ref="A1:O20" xr:uid="{9FE5D8B3-8BD3-4ECC-BD36-0871F9AB381A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9FE5D8B3-8BD3-4ECC-BD36-0871F9AB381A}" name="Table4" displayName="Table4" ref="A1:O15" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86" tableBorderDxfId="84" totalsRowBorderDxfId="83">
+  <autoFilter ref="A1:O15" xr:uid="{9FE5D8B3-8BD3-4ECC-BD36-0871F9AB381A}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O15">
+    <sortCondition ref="A2:A15"/>
+    <sortCondition ref="B2:B15"/>
+  </sortState>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{C5318B82-0C9B-4280-8F18-2386624D75D4}" name="Year" dataDxfId="82"/>
     <tableColumn id="2" xr3:uid="{AB7BB480-881B-4705-BBE6-30CA6A8F0319}" name="Month" dataDxfId="81"/>
@@ -4727,8 +4722,11 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4CE50CCA-E98C-47E5-9B6A-5036206E6077}" name="Table5" displayName="Table5" ref="A1:O14" totalsRowShown="0" headerRowDxfId="67" dataDxfId="65" headerRowBorderDxfId="66" tableBorderDxfId="64" totalsRowBorderDxfId="63">
-  <autoFilter ref="A1:O14" xr:uid="{4CE50CCA-E98C-47E5-9B6A-5036206E6077}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4CE50CCA-E98C-47E5-9B6A-5036206E6077}" name="Table5" displayName="Table5" ref="A1:O8" totalsRowShown="0" headerRowDxfId="67" dataDxfId="65" headerRowBorderDxfId="66" tableBorderDxfId="64" totalsRowBorderDxfId="63">
+  <autoFilter ref="A1:O8" xr:uid="{4CE50CCA-E98C-47E5-9B6A-5036206E6077}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O8">
+    <sortCondition ref="A1:A8"/>
+  </sortState>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{40739C4F-7926-4D30-85E5-B1C70F07CC58}" name="Year" dataDxfId="62"/>
     <tableColumn id="2" xr3:uid="{B9C436A4-C86A-4176-A748-A2EB263F2366}" name="Month" dataDxfId="61"/>
@@ -5156,42 +5154,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V185"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="4.85546875" style="17" customWidth="1"/>
-    <col min="8" max="9" width="18.7109375" style="43" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="43" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="4.83203125" style="17" customWidth="1"/>
+    <col min="8" max="9" width="18.6640625" style="43" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" style="43" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="3" style="15" customWidth="1"/>
-    <col min="12" max="12" width="23.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="4.28515625" style="17" customWidth="1"/>
-    <col min="16" max="16" width="22.28515625" style="43" customWidth="1"/>
+    <col min="12" max="12" width="23.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="4.33203125" style="17" customWidth="1"/>
+    <col min="16" max="16" width="22.33203125" style="43" customWidth="1"/>
     <col min="17" max="17" width="33" style="43" customWidth="1"/>
-    <col min="18" max="18" width="47.85546875" style="43" customWidth="1"/>
-    <col min="19" max="19" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="47.83203125" style="43" customWidth="1"/>
+    <col min="19" max="19" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="71" t="s">
+      <c r="D1" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="71"/>
-      <c r="F1" s="73" t="s">
+      <c r="E1" s="76"/>
+      <c r="F1" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="74"/>
-      <c r="H1" s="72" t="s">
+      <c r="G1" s="79"/>
+      <c r="H1" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="72"/>
+      <c r="I1" s="77"/>
       <c r="J1" s="46"/>
       <c r="K1" s="13"/>
       <c r="L1" s="5" t="s">
@@ -5216,7 +5214,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -5240,7 +5238,7 @@
       <c r="U2"/>
       <c r="V2"/>
     </row>
-    <row r="3" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" ht="48" x14ac:dyDescent="0.2">
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
@@ -5264,7 +5262,7 @@
       </c>
       <c r="K3" s="14"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D4" s="4" t="s">
         <v>114</v>
       </c>
@@ -5292,7 +5290,7 @@
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" ht="96" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -5333,7 +5331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
@@ -5347,7 +5345,7 @@
       <c r="I6" s="42"/>
       <c r="J6" s="42"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -5361,7 +5359,7 @@
       <c r="I7" s="42"/>
       <c r="J7" s="42"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -5375,7 +5373,7 @@
       <c r="I8" s="42"/>
       <c r="J8" s="42"/>
     </row>
-    <row r="9" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
@@ -5399,7 +5397,7 @@
       <c r="Q9" s="43"/>
       <c r="R9" s="42"/>
     </row>
-    <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
@@ -5441,7 +5439,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
@@ -5450,7 +5448,7 @@
       </c>
       <c r="C11" s="9"/>
     </row>
-    <row r="12" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
@@ -5459,12 +5457,12 @@
       </c>
       <c r="C12" s="9"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
         <f>IF(LEN(C14)=17,LEFT(C14,4)+(B14-1)/(DATE(LEFT(C14,4)+1,1,1)-DATE(LEFT(C14,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2015.7478310502283</v>
@@ -5483,7 +5481,7 @@
       <c r="P14" s="48"/>
       <c r="Q14" s="48"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A15" s="16">
         <v>1000</v>
       </c>
@@ -5538,7 +5536,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2010</v>
       </c>
@@ -5593,7 +5591,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>9300</v>
       </c>
@@ -5647,12 +5645,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="21">
         <f>IF(LEN(C19)=17,LEFT(C19,4)+(B19-1)/(DATE(LEFT(C19,4)+1,1,1)-DATE(LEFT(C19,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2016.0000018973892</v>
@@ -5671,7 +5669,7 @@
       <c r="P19" s="48"/>
       <c r="Q19" s="48"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="16">
         <v>1000</v>
       </c>
@@ -5726,7 +5724,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>2010</v>
       </c>
@@ -5781,7 +5779,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>9300</v>
       </c>
@@ -5835,12 +5833,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="20">
         <f>IF(LEN(C24)=17,LEFT(C24,4)+(B24-1)/(DATE(LEFT(C24,4)+1,1,1)-DATE(LEFT(C24,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2017.0000019025874</v>
@@ -5859,7 +5857,7 @@
       <c r="P24" s="48"/>
       <c r="Q24" s="48"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="16">
         <v>1000</v>
       </c>
@@ -5914,7 +5912,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>2010</v>
       </c>
@@ -5969,7 +5967,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>9300</v>
       </c>
@@ -6023,12 +6021,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <f>IF(LEN(C29)=17,LEFT(C29,4)+(B29-1)/(DATE(LEFT(C29,4)+1,1,1)-DATE(LEFT(C29,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2017.5821537290715</v>
@@ -6047,7 +6045,7 @@
       <c r="P29" s="48"/>
       <c r="Q29" s="48"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" s="16">
         <v>1000</v>
       </c>
@@ -6102,7 +6100,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>2010</v>
       </c>
@@ -6157,7 +6155,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>9300</v>
       </c>
@@ -6211,12 +6209,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <f>IF(LEN(C34)=17,LEFT(C34,4)+(B34-1)/(DATE(LEFT(C34,4)+1,1,1)-DATE(LEFT(C34,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2018.0000019025874</v>
@@ -6235,7 +6233,7 @@
       <c r="P34" s="48"/>
       <c r="Q34" s="48"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" s="16">
         <v>1000</v>
       </c>
@@ -6290,7 +6288,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>2010</v>
       </c>
@@ -6345,7 +6343,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>9300</v>
       </c>
@@ -6399,12 +6397,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <f>IF(LEN(C39)=17,LEFT(C39,4)+(B39-1)/(DATE(LEFT(C39,4)+1,1,1)-DATE(LEFT(C39,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2019.0000019025874</v>
@@ -6423,7 +6421,7 @@
       <c r="P39" s="48"/>
       <c r="Q39" s="48"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" s="16">
         <v>1000</v>
       </c>
@@ -6478,7 +6476,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>2010</v>
       </c>
@@ -6533,7 +6531,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>9300</v>
       </c>
@@ -6587,12 +6585,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <f>IF(LEN(C44)=17,LEFT(C44,4)+(B44-1)/(DATE(LEFT(C44,4)+1,1,1)-DATE(LEFT(C44,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2020.0000018973892</v>
@@ -6611,7 +6609,7 @@
       <c r="P44" s="48"/>
       <c r="Q44" s="48"/>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A45" s="16">
         <v>1000</v>
       </c>
@@ -6666,7 +6664,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>2010</v>
       </c>
@@ -6721,7 +6719,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>9300</v>
       </c>
@@ -6775,7 +6773,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>0</v>
       </c>
@@ -6828,12 +6826,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <f>IF(LEN(C50)=17,LEFT(C50,4)+(B50-1)/(DATE(LEFT(C50,4)+1,1,1)-DATE(LEFT(C50,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2020.5819691105039</v>
@@ -6855,7 +6853,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A51" s="16">
         <v>1000</v>
       </c>
@@ -6911,7 +6909,7 @@
       </c>
       <c r="S51" s="28"/>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A52" s="16">
         <v>2010</v>
       </c>
@@ -6967,7 +6965,7 @@
       </c>
       <c r="S52" s="28"/>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A53" s="16">
         <v>3000</v>
       </c>
@@ -7023,7 +7021,7 @@
       </c>
       <c r="S53" s="28"/>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="16">
         <v>0</v>
       </c>
@@ -7079,7 +7077,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="16">
         <v>0</v>
       </c>
@@ -7138,7 +7136,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="16">
         <v>0</v>
       </c>
@@ -7197,7 +7195,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A57" s="10" t="s">
         <v>78</v>
       </c>
@@ -7252,7 +7250,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A58" s="10" t="s">
         <v>79</v>
       </c>
@@ -7307,7 +7305,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A59" s="10" t="s">
         <v>80</v>
       </c>
@@ -7362,7 +7360,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>7009</v>
       </c>
@@ -7418,7 +7416,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>7008</v>
       </c>
@@ -7471,7 +7469,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>9388</v>
       </c>
@@ -7524,7 +7522,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>9389</v>
       </c>
@@ -7577,7 +7575,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>9300</v>
       </c>
@@ -7631,7 +7629,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>0</v>
       </c>
@@ -7684,12 +7682,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A67" s="10">
         <f>IF(LEN(C67)=17,LEFT(C67,4)+(B67-1)/(DATE(LEFT(C67,4)+1,1,1)-DATE(LEFT(C67,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2021.0000019025874</v>
@@ -7711,7 +7709,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A68" s="16">
         <v>1000</v>
       </c>
@@ -7767,7 +7765,7 @@
       </c>
       <c r="S68" s="28"/>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A69" s="16">
         <v>2010</v>
       </c>
@@ -7823,7 +7821,7 @@
       </c>
       <c r="S69" s="28"/>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A70" s="16">
         <v>3000</v>
       </c>
@@ -7879,7 +7877,7 @@
       </c>
       <c r="S70" s="28"/>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="16">
         <v>0</v>
       </c>
@@ -7935,7 +7933,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="16">
         <v>0</v>
       </c>
@@ -7994,7 +7992,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="16">
         <v>0</v>
       </c>
@@ -8053,7 +8051,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A74" s="10" t="s">
         <v>78</v>
       </c>
@@ -8108,7 +8106,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A75" s="10" t="s">
         <v>79</v>
       </c>
@@ -8163,7 +8161,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A76" s="10" t="s">
         <v>80</v>
       </c>
@@ -8218,7 +8216,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>7009</v>
       </c>
@@ -8274,7 +8272,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>7008</v>
       </c>
@@ -8327,7 +8325,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>9388</v>
       </c>
@@ -8380,7 +8378,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>9389</v>
       </c>
@@ -8433,7 +8431,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>9300</v>
       </c>
@@ -8487,7 +8485,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>0</v>
       </c>
@@ -8540,12 +8538,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A84" s="10">
         <f>IF(LEN(C84)=17,LEFT(C84,4)+(B84-1)/(DATE(LEFT(C84,4)+1,1,1)-DATE(LEFT(C84,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2021.4958923135464</v>
@@ -8567,7 +8565,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A85" s="35">
         <v>1000</v>
       </c>
@@ -8625,7 +8623,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A86" s="16">
         <v>2010</v>
       </c>
@@ -8681,7 +8679,7 @@
       </c>
       <c r="S86" s="28"/>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A87" s="35">
         <v>3000</v>
       </c>
@@ -8739,7 +8737,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="35">
         <v>0</v>
       </c>
@@ -8792,7 +8790,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="16">
         <v>0</v>
       </c>
@@ -8845,7 +8843,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="35">
         <v>0</v>
       </c>
@@ -8898,7 +8896,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A91" s="36" t="s">
         <v>78</v>
       </c>
@@ -8954,7 +8952,7 @@
       </c>
       <c r="S91" s="28"/>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A92" s="10" t="s">
         <v>79</v>
       </c>
@@ -9010,7 +9008,7 @@
       </c>
       <c r="S92" s="28"/>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A93" s="36" t="s">
         <v>80</v>
       </c>
@@ -9066,7 +9064,7 @@
       </c>
       <c r="S93" s="28"/>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>9300</v>
       </c>
@@ -9120,7 +9118,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A95" s="25">
         <v>9380</v>
       </c>
@@ -9173,7 +9171,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A96" s="25">
         <v>9381</v>
       </c>
@@ -9226,7 +9224,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>0</v>
       </c>
@@ -9279,12 +9277,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A99" s="10">
         <f>IF(LEN(C99)=17,LEFT(C99,4)+(B99-1)/(DATE(LEFT(C99,4)+1,1,1)-DATE(LEFT(C99,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2022.5466628614915</v>
@@ -9303,7 +9301,7 @@
       <c r="P99" s="48"/>
       <c r="Q99" s="48"/>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A100" s="16">
         <v>1000</v>
       </c>
@@ -9359,7 +9357,7 @@
       </c>
       <c r="S100" s="28"/>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A101" s="16">
         <v>2010</v>
       </c>
@@ -9415,7 +9413,7 @@
       </c>
       <c r="S101" s="28"/>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A102" s="16">
         <v>3000</v>
       </c>
@@ -9471,7 +9469,7 @@
       </c>
       <c r="S102" s="28"/>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="16">
         <v>0</v>
       </c>
@@ -9524,7 +9522,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A104" s="16">
         <v>0</v>
       </c>
@@ -9577,7 +9575,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" s="16">
         <v>0</v>
       </c>
@@ -9630,7 +9628,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A106" s="10" t="s">
         <v>78</v>
       </c>
@@ -9686,7 +9684,7 @@
       </c>
       <c r="S106" s="28"/>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A107" s="10" t="s">
         <v>79</v>
       </c>
@@ -9742,7 +9740,7 @@
       </c>
       <c r="S107" s="28"/>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A108" s="10" t="s">
         <v>80</v>
       </c>
@@ -9798,7 +9796,7 @@
       </c>
       <c r="S108" s="28"/>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>9300</v>
       </c>
@@ -9847,7 +9845,7 @@
       </c>
       <c r="Q109" s="48"/>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>9380</v>
       </c>
@@ -9893,7 +9891,7 @@
       <c r="P110" s="48"/>
       <c r="Q110" s="48"/>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>9381</v>
       </c>
@@ -9939,7 +9937,7 @@
       <c r="P111" s="48"/>
       <c r="Q111" s="48"/>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>0</v>
       </c>
@@ -9992,12 +9990,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A114" s="10">
         <f>IF(LEN(C114)=17,LEFT(C114,4)+(B114-1)/(DATE(LEFT(C114,4)+1,1,1)-DATE(LEFT(C114,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2024.084701350941</v>
@@ -10016,7 +10014,7 @@
       <c r="P114" s="48"/>
       <c r="Q114" s="48"/>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>0</v>
       </c>
@@ -10069,7 +10067,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <v>0</v>
       </c>
@@ -10122,7 +10120,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A117" s="16">
         <v>1000</v>
       </c>
@@ -10178,7 +10176,7 @@
       </c>
       <c r="S117" s="28"/>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A118" s="16">
         <v>0</v>
       </c>
@@ -10232,7 +10230,7 @@
       </c>
       <c r="S118" s="28"/>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A119" s="16">
         <v>0</v>
       </c>
@@ -10290,7 +10288,7 @@
       </c>
       <c r="S119" s="28"/>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A120" s="35">
         <v>0</v>
       </c>
@@ -10344,7 +10342,7 @@
       </c>
       <c r="S120" s="28"/>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A121" s="16">
         <v>2010</v>
       </c>
@@ -10400,7 +10398,7 @@
       </c>
       <c r="S121" s="28"/>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A122" s="16">
         <v>0</v>
       </c>
@@ -10454,7 +10452,7 @@
       </c>
       <c r="S122" s="28"/>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A123" s="16">
         <v>0</v>
       </c>
@@ -10512,7 +10510,7 @@
       </c>
       <c r="S123" s="28"/>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A124" s="35">
         <v>0</v>
       </c>
@@ -10566,7 +10564,7 @@
       </c>
       <c r="S124" s="28"/>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A125" s="16">
         <v>3000</v>
       </c>
@@ -10622,7 +10620,7 @@
       </c>
       <c r="S125" s="28"/>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A126" s="16">
         <v>0</v>
       </c>
@@ -10675,7 +10673,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A127" s="16">
         <v>0</v>
       </c>
@@ -10732,7 +10730,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A128" s="25">
         <v>0</v>
       </c>
@@ -10785,7 +10783,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A129" s="25">
         <v>0</v>
       </c>
@@ -10839,7 +10837,7 @@
       </c>
       <c r="S129" s="28"/>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
         <v>9300</v>
       </c>
@@ -10893,7 +10891,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
         <v>0</v>
       </c>
@@ -10946,7 +10944,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
         <v>0</v>
       </c>
@@ -11000,7 +10998,7 @@
       </c>
       <c r="S132" s="28"/>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
         <v>0</v>
       </c>
@@ -11053,7 +11051,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A134" s="47">
         <v>0</v>
       </c>
@@ -11106,7 +11104,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A135" s="47">
         <v>0</v>
       </c>
@@ -11159,7 +11157,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
         <v>0</v>
       </c>
@@ -11212,7 +11210,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
         <v>0</v>
       </c>
@@ -11265,12 +11263,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A139" s="10">
         <f>IF(LEN(C139)=17,LEFT(C139,4)+(B139-1)/(DATE(LEFT(C139,4)+1,1,1)-DATE(LEFT(C139,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2024.5819691105039</v>
@@ -11289,7 +11287,7 @@
       <c r="P139" s="48"/>
       <c r="Q139" s="48"/>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
         <v>0</v>
       </c>
@@ -11342,7 +11340,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
         <v>0</v>
       </c>
@@ -11395,7 +11393,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
         <v>1000</v>
       </c>
@@ -11452,7 +11450,7 @@
       </c>
       <c r="S142" s="28"/>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
         <v>0</v>
       </c>
@@ -11506,7 +11504,7 @@
       </c>
       <c r="S143" s="28"/>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
         <v>0</v>
       </c>
@@ -11564,7 +11562,7 @@
       </c>
       <c r="S144" s="28"/>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
         <v>0</v>
       </c>
@@ -11618,7 +11616,7 @@
       </c>
       <c r="S145" s="28"/>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
         <v>2010</v>
       </c>
@@ -11675,7 +11673,7 @@
       </c>
       <c r="S146" s="28"/>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
         <v>0</v>
       </c>
@@ -11729,7 +11727,7 @@
       </c>
       <c r="S147" s="28"/>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
         <v>0</v>
       </c>
@@ -11787,7 +11785,7 @@
       </c>
       <c r="S148" s="28"/>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
         <v>0</v>
       </c>
@@ -11841,7 +11839,7 @@
       </c>
       <c r="S149" s="28"/>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
         <v>3000</v>
       </c>
@@ -11898,7 +11896,7 @@
       </c>
       <c r="S150" s="28"/>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
         <v>0</v>
       </c>
@@ -11951,7 +11949,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
         <v>0</v>
       </c>
@@ -12008,7 +12006,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
         <v>0</v>
       </c>
@@ -12061,7 +12059,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A154" s="2">
         <v>0</v>
       </c>
@@ -12115,7 +12113,7 @@
       </c>
       <c r="S154" s="28"/>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A155" s="2">
         <v>9300</v>
       </c>
@@ -12169,7 +12167,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A156" s="2">
         <v>0</v>
       </c>
@@ -12222,7 +12220,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A157" s="2">
         <v>0</v>
       </c>
@@ -12276,7 +12274,7 @@
       </c>
       <c r="S157" s="28"/>
     </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A158" s="2">
         <v>0</v>
       </c>
@@ -12329,7 +12327,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A159" s="2">
         <v>0</v>
       </c>
@@ -12382,7 +12380,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A160" s="2">
         <v>0</v>
       </c>
@@ -12435,12 +12433,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A162" s="10">
         <f>IF(LEN(C162)=17,LEFT(C162,4)+(B162-1)/(DATE(LEFT(C162,4)+1,1,1)-DATE(LEFT(C162,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2025.5808238203958</v>
@@ -12459,7 +12457,7 @@
       <c r="P162" s="48"/>
       <c r="Q162" s="48"/>
     </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A163" s="2">
         <v>0</v>
       </c>
@@ -12516,7 +12514,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A164" s="2">
         <v>0</v>
       </c>
@@ -12574,7 +12572,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A165" s="2">
         <v>0</v>
       </c>
@@ -12635,7 +12633,7 @@
       </c>
       <c r="S165" s="28"/>
     </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A166" s="25">
         <v>1000</v>
       </c>
@@ -12696,7 +12694,7 @@
       </c>
       <c r="S166" s="28"/>
     </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A167" s="2">
         <v>0</v>
       </c>
@@ -12757,7 +12755,7 @@
       </c>
       <c r="S167" s="28"/>
     </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A168" s="2">
         <v>0</v>
       </c>
@@ -12818,7 +12816,7 @@
       </c>
       <c r="S168" s="28"/>
     </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A169" s="2">
         <v>0</v>
       </c>
@@ -12879,7 +12877,7 @@
       </c>
       <c r="S169" s="28"/>
     </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A170" s="25">
         <v>2010</v>
       </c>
@@ -12940,7 +12938,7 @@
       </c>
       <c r="S170" s="28"/>
     </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A171" s="2">
         <v>0</v>
       </c>
@@ -13001,7 +12999,7 @@
       </c>
       <c r="S171" s="28"/>
     </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A172" s="2">
         <v>0</v>
       </c>
@@ -13062,7 +13060,7 @@
       </c>
       <c r="S172" s="28"/>
     </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A173" s="2">
         <v>0</v>
       </c>
@@ -13123,7 +13121,7 @@
       </c>
       <c r="S173" s="28"/>
     </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A174" s="25">
         <v>3000</v>
       </c>
@@ -13183,7 +13181,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A175" s="2">
         <v>0</v>
       </c>
@@ -13243,7 +13241,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A176" s="2">
         <v>0</v>
       </c>
@@ -13303,7 +13301,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="177" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A177" s="2">
         <v>0</v>
       </c>
@@ -13362,7 +13360,7 @@
       </c>
       <c r="S177" s="28"/>
     </row>
-    <row r="178" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A178" s="2">
         <v>9300</v>
       </c>
@@ -13421,7 +13419,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="179" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A179" s="2">
         <v>0</v>
       </c>
@@ -13479,7 +13477,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="180" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A180" s="2">
         <v>0</v>
       </c>
@@ -13538,7 +13536,7 @@
       </c>
       <c r="S180" s="28"/>
     </row>
-    <row r="181" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A181" s="2">
         <v>0</v>
       </c>
@@ -13596,7 +13594,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="182" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A182" s="2">
         <v>0</v>
       </c>
@@ -13654,7 +13652,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="183" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A183" s="2">
         <v>0</v>
       </c>
@@ -13712,7 +13710,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A184" s="25">
         <v>0</v>
       </c>
@@ -13768,7 +13766,7 @@
         <v>R = 1000/M</v>
       </c>
     </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A185" s="25">
         <v>0</v>
       </c>
@@ -13839,38 +13837,38 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA7BD733-D02F-4818-9D6A-E6E21FE780ED}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" customWidth="1"/>
+    <col min="1" max="1" width="26.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="71" t="s">
         <v>256</v>
       </c>
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="71" t="s">
         <v>213</v>
       </c>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="71" t="s">
         <v>225</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="71" t="s">
         <v>226</v>
       </c>
-      <c r="E1" s="75" t="s">
+      <c r="E1" s="71" t="s">
         <v>228</v>
       </c>
-      <c r="F1" s="75" t="s">
+      <c r="F1" s="71" t="s">
         <v>230</v>
       </c>
-      <c r="G1" s="75" t="s">
+      <c r="G1" s="71" t="s">
         <v>222</v>
       </c>
-      <c r="H1" s="75" t="s">
+      <c r="H1" s="71" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="54" t="s">
         <v>257</v>
       </c>
@@ -13881,7 +13879,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="54" t="s">
         <v>258</v>
       </c>
@@ -13892,7 +13890,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="54" t="s">
         <v>259</v>
       </c>
@@ -13903,7 +13901,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="54" t="s">
         <v>260</v>
       </c>
@@ -13914,7 +13912,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="54" t="s">
         <v>261</v>
       </c>
@@ -13925,7 +13923,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="54" t="s">
         <v>262</v>
       </c>
@@ -13936,7 +13934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="54" t="s">
         <v>263</v>
       </c>
@@ -13947,9 +13945,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="54" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -13964,9 +13962,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="54" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -13984,9 +13982,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="54" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -14001,9 +13999,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="54" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -14018,9 +14016,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="54" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -14041,9 +14039,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="54" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -14064,9 +14062,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="54" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -14095,22 +14093,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B5CE66C-33D7-49A1-8DF7-7981795B80E7}">
   <dimension ref="A1:P147"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="8" max="8" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>200</v>
       </c>
@@ -14160,7 +14158,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>122</v>
       </c>
@@ -14189,7 +14187,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>123</v>
       </c>
@@ -14218,7 +14216,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>124</v>
       </c>
@@ -14253,7 +14251,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>125</v>
       </c>
@@ -14300,7 +14298,7 @@
         <v>1.7168308506891199</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>126</v>
       </c>
@@ -14335,7 +14333,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>127</v>
       </c>
@@ -14370,7 +14368,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>128</v>
       </c>
@@ -14405,7 +14403,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>129</v>
       </c>
@@ -14452,7 +14450,7 @@
         <v>1.0501569268589599</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>130</v>
       </c>
@@ -14487,7 +14485,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>131</v>
       </c>
@@ -14522,7 +14520,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>132</v>
       </c>
@@ -14557,7 +14555,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>133</v>
       </c>
@@ -14604,7 +14602,7 @@
         <v>0.94600494833357596</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>134</v>
       </c>
@@ -14639,7 +14637,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>135</v>
       </c>
@@ -14674,7 +14672,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>136</v>
       </c>
@@ -14703,7 +14701,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>137</v>
       </c>
@@ -14750,7 +14748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>138</v>
       </c>
@@ -14776,7 +14774,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>139</v>
       </c>
@@ -14802,7 +14800,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>140</v>
       </c>
@@ -14828,7 +14826,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>141</v>
       </c>
@@ -14857,7 +14855,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>142</v>
       </c>
@@ -14886,7 +14884,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>143</v>
       </c>
@@ -14927,7 +14925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>144</v>
       </c>
@@ -14968,7 +14966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>78</v>
       </c>
@@ -14997,7 +14995,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>79</v>
       </c>
@@ -15026,7 +15024,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>80</v>
       </c>
@@ -15073,7 +15071,7 @@
         <v>1.2587336487582701</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>81</v>
       </c>
@@ -15108,7 +15106,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>82</v>
       </c>
@@ -15158,7 +15156,7 @@
         <v>1.2587336487582701</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>83</v>
       </c>
@@ -15193,7 +15191,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>84</v>
       </c>
@@ -15240,7 +15238,7 @@
         <v>1.8811551773110999</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>85</v>
       </c>
@@ -15275,7 +15273,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>86</v>
       </c>
@@ -15325,7 +15323,7 @@
         <v>1.8811551773110999</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>87</v>
       </c>
@@ -15360,7 +15358,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>88</v>
       </c>
@@ -15407,7 +15405,7 @@
         <v>1.2914628942617901</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>89</v>
       </c>
@@ -15442,7 +15440,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>90</v>
       </c>
@@ -15492,7 +15490,7 @@
         <v>1.2914628942617901</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>91</v>
       </c>
@@ -15527,7 +15525,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>92</v>
       </c>
@@ -15556,7 +15554,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>93</v>
       </c>
@@ -15603,7 +15601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>94</v>
       </c>
@@ -15629,7 +15627,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>95</v>
       </c>
@@ -15655,7 +15653,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>96</v>
       </c>
@@ -15681,7 +15679,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>97</v>
       </c>
@@ -15716,7 +15714,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>98</v>
       </c>
@@ -15751,7 +15749,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>99</v>
       </c>
@@ -15786,7 +15784,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>100</v>
       </c>
@@ -15821,7 +15819,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>101</v>
       </c>
@@ -15850,7 +15848,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>102</v>
       </c>
@@ -15879,7 +15877,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>103</v>
       </c>
@@ -15923,7 +15921,7 @@
         <v>2.52101822944072</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>104</v>
       </c>
@@ -15955,7 +15953,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>105</v>
       </c>
@@ -16002,7 +16000,7 @@
         <v>2.52101822944072</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>106</v>
       </c>
@@ -16034,7 +16032,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>107</v>
       </c>
@@ -16081,7 +16079,7 @@
         <v>0.929754688179387</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>108</v>
       </c>
@@ -16116,7 +16114,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>109</v>
       </c>
@@ -16166,7 +16164,7 @@
         <v>0.929754688179387</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>110</v>
       </c>
@@ -16201,7 +16199,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>111</v>
       </c>
@@ -16248,7 +16246,7 @@
         <v>2.4150196263511101</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>112</v>
       </c>
@@ -16283,7 +16281,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>113</v>
       </c>
@@ -16333,7 +16331,7 @@
         <v>2.4150196263511101</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>114</v>
       </c>
@@ -16368,7 +16366,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>115</v>
       </c>
@@ -16397,7 +16395,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>116</v>
       </c>
@@ -16444,7 +16442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>117</v>
       </c>
@@ -16470,7 +16468,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>118</v>
       </c>
@@ -16496,7 +16494,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>119</v>
       </c>
@@ -16522,7 +16520,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>120</v>
       </c>
@@ -16551,7 +16549,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>121</v>
       </c>
@@ -16580,7 +16578,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>65</v>
       </c>
@@ -16627,7 +16625,7 @@
         <v>1.16405016530411</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>66</v>
       </c>
@@ -16674,7 +16672,7 @@
         <v>1.8352099609999999</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>67</v>
       </c>
@@ -16721,7 +16719,7 @@
         <v>1.2169603471391199</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>68</v>
       </c>
@@ -16756,7 +16754,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>69</v>
       </c>
@@ -16791,7 +16789,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>70</v>
       </c>
@@ -16826,7 +16824,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>71</v>
       </c>
@@ -16876,7 +16874,7 @@
         <v>1.16405016530411</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>72</v>
       </c>
@@ -16926,7 +16924,7 @@
         <v>1.8352099609999999</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>73</v>
       </c>
@@ -16976,7 +16974,7 @@
         <v>1.2169603471391199</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>74</v>
       </c>
@@ -17023,7 +17021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>75</v>
       </c>
@@ -17073,7 +17071,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>76</v>
       </c>
@@ -17123,7 +17121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>77</v>
       </c>
@@ -17149,7 +17147,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>37</v>
       </c>
@@ -17196,7 +17194,7 @@
         <v>1.80205774681044</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>38</v>
       </c>
@@ -17243,7 +17241,7 @@
         <v>2.03531169831321</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>39</v>
       </c>
@@ -17290,7 +17288,7 @@
         <v>2.20773173146471</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>40</v>
       </c>
@@ -17322,7 +17320,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>41</v>
       </c>
@@ -17354,7 +17352,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>42</v>
       </c>
@@ -17386,7 +17384,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>43</v>
       </c>
@@ -17436,7 +17434,7 @@
         <v>1.80205774681044</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>44</v>
       </c>
@@ -17486,7 +17484,7 @@
         <v>2.03531169831321</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>45</v>
       </c>
@@ -17536,7 +17534,7 @@
         <v>2.20773173146471</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>46</v>
       </c>
@@ -17583,7 +17581,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>47</v>
       </c>
@@ -17630,7 +17628,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>48</v>
       </c>
@@ -17677,7 +17675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>49</v>
       </c>
@@ -17724,7 +17722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>50</v>
       </c>
@@ -17771,7 +17769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>51</v>
       </c>
@@ -17797,7 +17795,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>52</v>
       </c>
@@ -17844,7 +17842,7 @@
         <v>0.76827735566056199</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>53</v>
       </c>
@@ -17891,7 +17889,7 @@
         <v>2.03531169831321</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>54</v>
       </c>
@@ -17938,7 +17936,7 @@
         <v>0.83122061412608705</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>55</v>
       </c>
@@ -17973,7 +17971,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>56</v>
       </c>
@@ -18008,7 +18006,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>57</v>
       </c>
@@ -18043,7 +18041,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>58</v>
       </c>
@@ -18093,7 +18091,7 @@
         <v>0.76827735566056199</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>59</v>
       </c>
@@ -18143,7 +18141,7 @@
         <v>2.03531169831321</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>60</v>
       </c>
@@ -18193,7 +18191,7 @@
         <v>0.83122061412608705</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>61</v>
       </c>
@@ -18240,7 +18238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>62</v>
       </c>
@@ -18290,7 +18288,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>63</v>
       </c>
@@ -18340,7 +18338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>64</v>
       </c>
@@ -18366,7 +18364,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>18</v>
       </c>
@@ -18413,7 +18411,7 @@
         <v>1.67449813656697</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>19</v>
       </c>
@@ -18460,7 +18458,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>20</v>
       </c>
@@ -18504,7 +18502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>21</v>
       </c>
@@ -18530,7 +18528,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>22</v>
       </c>
@@ -18577,7 +18575,7 @@
         <v>1.67449813656697</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>23</v>
       </c>
@@ -18624,7 +18622,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>24</v>
       </c>
@@ -18671,7 +18669,7 @@
         <v>2.2908047722416698</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>25</v>
       </c>
@@ -18703,7 +18701,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>26</v>
       </c>
@@ -18735,7 +18733,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>27</v>
       </c>
@@ -18767,7 +18765,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>28</v>
       </c>
@@ -18814,7 +18812,7 @@
         <v>1.67449813656697</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>28.5</v>
       </c>
@@ -18861,7 +18859,7 @@
         <v>2.2908047722416698</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>29</v>
       </c>
@@ -18908,7 +18906,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>30</v>
       </c>
@@ -18955,7 +18953,7 @@
         <v>2.2908047722416698</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>31</v>
       </c>
@@ -19002,7 +19000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>32</v>
       </c>
@@ -19049,7 +19047,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>33</v>
       </c>
@@ -19096,7 +19094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>34</v>
       </c>
@@ -19143,7 +19141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>35</v>
       </c>
@@ -19187,7 +19185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>36</v>
       </c>
@@ -19213,7 +19211,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>15</v>
       </c>
@@ -19260,7 +19258,7 @@
         <v>1.67262493287749</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>16</v>
       </c>
@@ -19307,7 +19305,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>17</v>
       </c>
@@ -19351,7 +19349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>12</v>
       </c>
@@ -19398,7 +19396,7 @@
         <v>1.67075591548251</v>
       </c>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>13</v>
       </c>
@@ -19445,7 +19443,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>14</v>
       </c>
@@ -19489,7 +19487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>6</v>
       </c>
@@ -19536,7 +19534,7 @@
         <v>1.6226717989921</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>7</v>
       </c>
@@ -19583,7 +19581,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>8</v>
       </c>
@@ -19627,7 +19625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>9</v>
       </c>
@@ -19674,7 +19672,7 @@
         <v>1.66982297226244</v>
       </c>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>10</v>
       </c>
@@ -19721,7 +19719,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>11</v>
       </c>
@@ -19765,7 +19763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>3</v>
       </c>
@@ -19812,7 +19810,7 @@
         <v>1.6188010157323101</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>4</v>
       </c>
@@ -19859,7 +19857,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>5</v>
       </c>
@@ -19903,7 +19901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>0</v>
       </c>
@@ -19951,7 +19949,7 @@
         <v>1.6168725409881399</v>
       </c>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>1</v>
       </c>
@@ -19998,7 +19996,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>2</v>
       </c>
@@ -20052,21 +20050,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C2AC3CD-B28B-4E07-84D1-63F10D71EFF6}">
-  <dimension ref="A1:O19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="9.7109375" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" customWidth="1"/>
-    <col min="14" max="14" width="15.28515625" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.5" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="12" max="12" width="14.5" customWidth="1"/>
+    <col min="13" max="13" width="13.5" customWidth="1"/>
+    <col min="14" max="14" width="15.33203125" customWidth="1"/>
+    <col min="15" max="15" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="60" t="s">
         <v>201</v>
       </c>
@@ -20113,7 +20111,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="57">
         <v>2015</v>
       </c>
@@ -20160,7 +20158,7 @@
         <v>1.6168725409881399</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="56">
         <v>2016</v>
       </c>
@@ -20207,7 +20205,7 @@
         <v>1.6188010157323101</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="56">
         <v>2017</v>
       </c>
@@ -20254,7 +20252,7 @@
         <v>1.6226717989921</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="57">
         <v>2017</v>
       </c>
@@ -20301,7 +20299,7 @@
         <v>1.66982297226244</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="57">
         <v>2018</v>
       </c>
@@ -20348,7 +20346,7 @@
         <v>1.67075591548251</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="56">
         <v>2019</v>
       </c>
@@ -20395,7 +20393,7 @@
         <v>1.67262493287749</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="56">
         <v>2020</v>
       </c>
@@ -20442,7 +20440,7 @@
         <v>1.67449813656697</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="57">
         <v>2020</v>
       </c>
@@ -20471,7 +20469,7 @@
         <v>217</v>
       </c>
       <c r="J9" s="59" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="K9" s="57">
         <v>1000</v>
@@ -20489,7 +20487,7 @@
         <v>1.67449813656697</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="56">
         <v>2021</v>
       </c>
@@ -20518,7 +20516,7 @@
         <v>217</v>
       </c>
       <c r="J10" s="59" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="K10" s="56">
         <v>1000</v>
@@ -20536,7 +20534,7 @@
         <v>1.80205774681044</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="56">
         <v>2021</v>
       </c>
@@ -20564,7 +20562,9 @@
       <c r="I11" s="56">
         <v>4764</v>
       </c>
-      <c r="J11" s="56"/>
+      <c r="J11" s="56" t="s">
+        <v>272</v>
+      </c>
       <c r="K11" s="56">
         <v>1000</v>
       </c>
@@ -20581,323 +20581,145 @@
         <v>0.76827735566056199</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="57">
-        <v>2021</v>
-      </c>
-      <c r="B12" s="57">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" s="56">
+        <v>2022</v>
+      </c>
+      <c r="B12" s="56">
         <v>7</v>
       </c>
-      <c r="C12" s="57">
-        <v>1</v>
-      </c>
-      <c r="D12" s="57">
-        <v>0</v>
-      </c>
-      <c r="E12" s="57">
-        <v>1</v>
-      </c>
-      <c r="F12" s="57">
-        <v>4</v>
-      </c>
-      <c r="G12" s="57" t="s">
+      <c r="C12" s="56">
+        <v>19</v>
+      </c>
+      <c r="D12" s="56">
+        <v>12</v>
+      </c>
+      <c r="E12" s="56">
+        <v>46</v>
+      </c>
+      <c r="F12" s="56">
+        <v>1</v>
+      </c>
+      <c r="G12" s="56" t="s">
         <v>213</v>
       </c>
-      <c r="H12" s="57" t="s">
+      <c r="H12" s="56" t="s">
         <v>248</v>
       </c>
-      <c r="I12" s="57">
+      <c r="I12" s="56">
         <v>4764</v>
       </c>
-      <c r="J12" s="57" t="s">
-        <v>242</v>
-      </c>
-      <c r="K12" s="57"/>
-      <c r="L12" s="57"/>
-      <c r="M12" s="57"/>
-      <c r="N12" s="57"/>
-      <c r="O12" s="57"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="56">
-        <v>2022</v>
-      </c>
-      <c r="B13" s="56">
-        <v>7</v>
-      </c>
-      <c r="C13" s="56">
-        <v>19</v>
-      </c>
-      <c r="D13" s="56">
-        <v>12</v>
-      </c>
-      <c r="E13" s="56">
-        <v>46</v>
-      </c>
-      <c r="F13" s="56">
-        <v>1</v>
-      </c>
-      <c r="G13" s="56" t="s">
+      <c r="J12" s="56" t="s">
+        <v>272</v>
+      </c>
+      <c r="K12" s="56">
+        <v>1000</v>
+      </c>
+      <c r="L12" s="56">
+        <v>16.624700000000001</v>
+      </c>
+      <c r="M12" s="56">
+        <v>1</v>
+      </c>
+      <c r="N12" s="56">
+        <v>60.151461379754203</v>
+      </c>
+      <c r="O12" s="56">
+        <v>1.16405016530411</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A13" s="57">
+        <v>2024</v>
+      </c>
+      <c r="B13" s="57">
+        <v>2</v>
+      </c>
+      <c r="C13" s="57">
+        <v>1</v>
+      </c>
+      <c r="D13" s="57">
+        <v>0</v>
+      </c>
+      <c r="E13" s="57">
+        <v>1</v>
+      </c>
+      <c r="F13" s="57">
+        <v>3</v>
+      </c>
+      <c r="G13" s="57" t="s">
         <v>213</v>
       </c>
-      <c r="H13" s="56" t="s">
+      <c r="H13" s="57" t="s">
         <v>248</v>
       </c>
-      <c r="I13" s="56">
+      <c r="I13" s="57">
         <v>4764</v>
       </c>
-      <c r="J13" s="56"/>
-      <c r="K13" s="56">
-        <v>1000</v>
-      </c>
-      <c r="L13" s="56">
-        <v>16.624700000000001</v>
-      </c>
-      <c r="M13" s="56">
-        <v>1</v>
-      </c>
-      <c r="N13" s="56">
-        <v>60.151461379754203</v>
-      </c>
-      <c r="O13" s="56">
-        <v>1.16405016530411</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J13" s="57" t="s">
+        <v>272</v>
+      </c>
+      <c r="K13" s="57">
+        <v>1000</v>
+      </c>
+      <c r="L13" s="57">
+        <v>16.613499999999998</v>
+      </c>
+      <c r="M13" s="57">
+        <v>1</v>
+      </c>
+      <c r="N13" s="57">
+        <v>60.192012519938601</v>
+      </c>
+      <c r="O13" s="57">
+        <v>1.2587336487582701</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="57">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="B14" s="57">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" s="57">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D14" s="57">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E14" s="57">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="F14" s="57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14" s="57" t="s">
         <v>213</v>
       </c>
       <c r="H14" s="57" t="s">
-        <v>248</v>
+        <v>214</v>
       </c>
       <c r="I14" s="57">
-        <v>4764</v>
+        <v>128907</v>
       </c>
       <c r="J14" s="57" t="s">
-        <v>242</v>
-      </c>
-      <c r="K14" s="57"/>
-      <c r="L14" s="57"/>
-      <c r="M14" s="57"/>
-      <c r="N14" s="57"/>
-      <c r="O14" s="57"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="57">
-        <v>2024</v>
-      </c>
-      <c r="B15" s="57">
-        <v>2</v>
-      </c>
-      <c r="C15" s="57">
-        <v>1</v>
-      </c>
-      <c r="D15" s="57">
-        <v>0</v>
-      </c>
-      <c r="E15" s="57">
-        <v>1</v>
-      </c>
-      <c r="F15" s="57">
-        <v>3</v>
-      </c>
-      <c r="G15" s="57" t="s">
-        <v>213</v>
-      </c>
-      <c r="H15" s="57" t="s">
-        <v>248</v>
-      </c>
-      <c r="I15" s="57">
-        <v>4764</v>
-      </c>
-      <c r="J15" s="57"/>
-      <c r="K15" s="57">
-        <v>1000</v>
-      </c>
-      <c r="L15" s="57">
-        <v>16.613499999999998</v>
-      </c>
-      <c r="M15" s="57">
-        <v>1</v>
-      </c>
-      <c r="N15" s="57">
-        <v>60.192012519938601</v>
-      </c>
-      <c r="O15" s="57">
-        <v>1.2587336487582701</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="56">
-        <v>2024</v>
-      </c>
-      <c r="B16" s="56">
-        <v>2</v>
-      </c>
-      <c r="C16" s="56">
-        <v>1</v>
-      </c>
-      <c r="D16" s="56">
-        <v>0</v>
-      </c>
-      <c r="E16" s="56">
-        <v>1</v>
-      </c>
-      <c r="F16" s="56">
-        <v>4</v>
-      </c>
-      <c r="G16" s="56" t="s">
-        <v>213</v>
-      </c>
-      <c r="H16" s="56" t="s">
-        <v>248</v>
-      </c>
-      <c r="I16" s="56">
-        <v>4764</v>
-      </c>
-      <c r="J16" s="56" t="s">
-        <v>242</v>
-      </c>
-      <c r="K16" s="56"/>
-      <c r="L16" s="56"/>
-      <c r="M16" s="56"/>
-      <c r="N16" s="56"/>
-      <c r="O16" s="56"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="56">
-        <v>2024</v>
-      </c>
-      <c r="B17" s="56">
-        <v>2</v>
-      </c>
-      <c r="C17" s="56">
-        <v>1</v>
-      </c>
-      <c r="D17" s="56">
-        <v>0</v>
-      </c>
-      <c r="E17" s="56">
-        <v>1</v>
-      </c>
-      <c r="F17" s="56">
-        <v>20</v>
-      </c>
-      <c r="G17" s="56" t="s">
-        <v>213</v>
-      </c>
-      <c r="H17" s="56" t="s">
-        <v>248</v>
-      </c>
-      <c r="I17" s="56">
-        <v>4764</v>
-      </c>
-      <c r="J17" s="56" t="s">
-        <v>243</v>
-      </c>
-      <c r="K17" s="56"/>
-      <c r="L17" s="56"/>
-      <c r="M17" s="56"/>
-      <c r="N17" s="56"/>
-      <c r="O17" s="56"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="57">
-        <v>2025</v>
-      </c>
-      <c r="B18" s="57">
-        <v>8</v>
-      </c>
-      <c r="C18" s="57">
-        <v>1</v>
-      </c>
-      <c r="D18" s="57">
-        <v>0</v>
-      </c>
-      <c r="E18" s="57">
-        <v>1</v>
-      </c>
-      <c r="F18" s="57">
-        <v>3</v>
-      </c>
-      <c r="G18" s="57" t="s">
-        <v>213</v>
-      </c>
-      <c r="H18" s="57" t="s">
-        <v>214</v>
-      </c>
-      <c r="I18" s="57">
-        <v>128907</v>
-      </c>
-      <c r="J18" s="57" t="s">
         <v>215</v>
       </c>
-      <c r="K18" s="57"/>
-      <c r="L18" s="57"/>
-      <c r="M18" s="57"/>
-      <c r="N18" s="57"/>
-      <c r="O18" s="57"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="56">
-        <v>2025</v>
-      </c>
-      <c r="B19" s="56">
-        <v>8</v>
-      </c>
-      <c r="C19" s="56">
-        <v>1</v>
-      </c>
-      <c r="D19" s="56">
-        <v>0</v>
-      </c>
-      <c r="E19" s="56">
-        <v>1</v>
-      </c>
-      <c r="F19" s="56">
-        <v>4</v>
-      </c>
-      <c r="G19" s="56" t="s">
-        <v>213</v>
-      </c>
-      <c r="H19" s="56" t="s">
-        <v>214</v>
-      </c>
-      <c r="I19" s="56">
-        <v>128907</v>
-      </c>
-      <c r="J19" s="56"/>
-      <c r="K19" s="56">
-        <v>8.8010999999999999</v>
-      </c>
-      <c r="L19" s="56">
-        <v>8.8010999999999999</v>
-      </c>
-      <c r="M19" s="56">
+      <c r="K14" s="57">
+        <v>1000</v>
+      </c>
+      <c r="L14" s="57">
+        <f>1000/Table2[[#This Row],[M_should_be]]</f>
+        <v>8.8011000000000266</v>
+      </c>
+      <c r="M14" s="57">
+        <v>1</v>
+      </c>
+      <c r="N14" s="56">
         <v>113.622160866255</v>
       </c>
-      <c r="N19" s="56">
-        <v>113.622160866255</v>
-      </c>
-      <c r="O19" s="56">
+      <c r="O14" s="56">
         <v>1.7168308506891199</v>
       </c>
     </row>
@@ -20911,21 +20733,21 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51D50481-F00D-4F48-81C6-07265F307B30}">
-  <dimension ref="A1:O20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="9.7109375" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" customWidth="1"/>
-    <col min="14" max="14" width="15.28515625" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.5" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="12" max="12" width="14.5" customWidth="1"/>
+    <col min="13" max="13" width="13.5" customWidth="1"/>
+    <col min="14" max="14" width="15.33203125" customWidth="1"/>
+    <col min="15" max="15" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="62" t="s">
         <v>201</v>
       </c>
@@ -20972,49 +20794,57 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="63">
-        <v>2025</v>
+        <v>2015</v>
       </c>
       <c r="B2" s="63">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="63">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D2" s="63">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E2" s="63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="63">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G2" s="63" t="s">
         <v>225</v>
       </c>
       <c r="H2" s="63" t="s">
-        <v>247</v>
+        <v>37</v>
       </c>
       <c r="I2" s="65" t="s">
         <v>220</v>
       </c>
-      <c r="J2" s="63" t="s">
-        <v>215</v>
-      </c>
-      <c r="K2" s="63"/>
-      <c r="L2" s="63"/>
-      <c r="M2" s="63"/>
-      <c r="N2" s="63"/>
-      <c r="O2" s="63"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J2" s="63"/>
+      <c r="K2" s="63">
+        <v>8.4133300801790405</v>
+      </c>
+      <c r="L2" s="63">
+        <v>8.3513999999999999</v>
+      </c>
+      <c r="M2" s="63">
+        <v>118.85899999999999</v>
+      </c>
+      <c r="N2" s="63">
+        <v>119.740402806715</v>
+      </c>
+      <c r="O2" s="63">
+        <v>1.9286659923145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="64">
-        <v>2025</v>
+        <v>2016</v>
       </c>
       <c r="B3" s="64">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C3" s="64">
         <v>1</v>
@@ -21026,52 +20856,52 @@
         <v>1</v>
       </c>
       <c r="F3" s="64">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G3" s="64" t="s">
         <v>225</v>
       </c>
       <c r="H3" s="64" t="s">
-        <v>247</v>
+        <v>37</v>
       </c>
       <c r="I3" s="66" t="s">
         <v>220</v>
       </c>
       <c r="J3" s="64"/>
       <c r="K3" s="64">
-        <v>8.3796999999999997</v>
+        <v>8.4133300801790405</v>
       </c>
       <c r="L3" s="64">
-        <v>8.3796999999999997</v>
+        <v>8.3513999999999999</v>
       </c>
       <c r="M3" s="64">
-        <v>119.336014415791</v>
+        <v>118.85899999999999</v>
       </c>
       <c r="N3" s="64">
-        <v>119.336014415791</v>
+        <v>119.740402806715</v>
       </c>
       <c r="O3" s="64">
-        <v>1.0501569268589599</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1.9286659923145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="63">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="B4" s="63">
+        <v>1</v>
+      </c>
+      <c r="C4" s="63">
+        <v>1</v>
+      </c>
+      <c r="D4" s="63">
+        <v>0</v>
+      </c>
+      <c r="E4" s="63">
+        <v>1</v>
+      </c>
+      <c r="F4" s="63">
         <v>2</v>
-      </c>
-      <c r="C4" s="63">
-        <v>1</v>
-      </c>
-      <c r="D4" s="63">
-        <v>0</v>
-      </c>
-      <c r="E4" s="63">
-        <v>1</v>
-      </c>
-      <c r="F4" s="63">
-        <v>7</v>
       </c>
       <c r="G4" s="63" t="s">
         <v>225</v>
@@ -21084,39 +20914,39 @@
       </c>
       <c r="J4" s="63"/>
       <c r="K4" s="63">
-        <v>1000</v>
+        <v>8.4133300801790405</v>
       </c>
       <c r="L4" s="63">
-        <v>8.3575999999999997</v>
+        <v>8.3513999999999999</v>
       </c>
       <c r="M4" s="63">
-        <v>1</v>
+        <v>118.85899999999999</v>
       </c>
       <c r="N4" s="63">
-        <v>119.65157461472199</v>
+        <v>119.740402806715</v>
       </c>
       <c r="O4" s="63">
-        <v>1.8811551773110999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1.9286659923145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="64">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="B5" s="64">
+        <v>8</v>
+      </c>
+      <c r="C5" s="64">
+        <v>1</v>
+      </c>
+      <c r="D5" s="64">
+        <v>11</v>
+      </c>
+      <c r="E5" s="64">
+        <v>40</v>
+      </c>
+      <c r="F5" s="64">
         <v>2</v>
-      </c>
-      <c r="C5" s="64">
-        <v>1</v>
-      </c>
-      <c r="D5" s="64">
-        <v>0</v>
-      </c>
-      <c r="E5" s="64">
-        <v>1</v>
-      </c>
-      <c r="F5" s="64">
-        <v>8</v>
       </c>
       <c r="G5" s="64" t="s">
         <v>225</v>
@@ -21127,30 +20957,38 @@
       <c r="I5" s="66" t="s">
         <v>220</v>
       </c>
-      <c r="J5" s="64" t="s">
-        <v>242</v>
-      </c>
-      <c r="K5" s="64"/>
-      <c r="L5" s="64"/>
-      <c r="M5" s="64"/>
-      <c r="N5" s="64"/>
-      <c r="O5" s="64"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J5" s="64"/>
+      <c r="K5" s="64">
+        <v>8.4133300801790405</v>
+      </c>
+      <c r="L5" s="64">
+        <v>8.3513999999999999</v>
+      </c>
+      <c r="M5" s="64">
+        <v>118.85899999999999</v>
+      </c>
+      <c r="N5" s="64">
+        <v>119.740402806715</v>
+      </c>
+      <c r="O5" s="64">
+        <v>1.9286659923145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="63">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B6" s="63">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C6" s="63">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D6" s="63">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E6" s="63">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="F6" s="63">
         <v>2</v>
@@ -21166,39 +21004,39 @@
       </c>
       <c r="J6" s="63"/>
       <c r="K6" s="63">
-        <v>1000</v>
+        <v>8.4133300801790405</v>
       </c>
       <c r="L6" s="63">
-        <v>8.3750999999999998</v>
+        <v>8.3513999999999999</v>
       </c>
       <c r="M6" s="63">
-        <v>1</v>
+        <v>118.85899999999999</v>
       </c>
       <c r="N6" s="63">
-        <v>119.401559384366</v>
+        <v>119.740402806715</v>
       </c>
       <c r="O6" s="63">
-        <v>1.8352099609999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1.9286659923145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="64">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="B7" s="64">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C7" s="64">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D7" s="64">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E7" s="64">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="F7" s="64">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G7" s="64" t="s">
         <v>225</v>
@@ -21209,18 +21047,26 @@
       <c r="I7" s="66" t="s">
         <v>220</v>
       </c>
-      <c r="J7" s="64" t="s">
-        <v>242</v>
-      </c>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
-      <c r="M7" s="64"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="64"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J7" s="64"/>
+      <c r="K7" s="64">
+        <v>8.4133300801790405</v>
+      </c>
+      <c r="L7" s="64">
+        <v>8.3513999999999999</v>
+      </c>
+      <c r="M7" s="64">
+        <v>118.85899999999999</v>
+      </c>
+      <c r="N7" s="64">
+        <v>119.740402806715</v>
+      </c>
+      <c r="O7" s="64">
+        <v>1.9286659923145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="63">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B8" s="63">
         <v>1</v>
@@ -21248,27 +21094,27 @@
       </c>
       <c r="J8" s="63"/>
       <c r="K8" s="63">
-        <v>1000</v>
+        <v>8.4133300801790405</v>
       </c>
       <c r="L8" s="63">
-        <v>8.3756000000000004</v>
+        <v>8.3513999999999999</v>
       </c>
       <c r="M8" s="63">
-        <v>1</v>
+        <v>118.85899999999999</v>
       </c>
       <c r="N8" s="63">
-        <v>119.394431443717</v>
+        <v>119.740402806715</v>
       </c>
       <c r="O8" s="63">
-        <v>2.03531169831321</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1.9286659923145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="64">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B9" s="64">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" s="64">
         <v>1</v>
@@ -21296,24 +21142,24 @@
         <v>1000</v>
       </c>
       <c r="L9" s="64">
-        <v>8.3756000000000004</v>
+        <v>8.3513999999999999</v>
       </c>
       <c r="M9" s="64">
         <v>1</v>
       </c>
       <c r="N9" s="64">
-        <v>119.394431443717</v>
+        <v>119.740402806715</v>
       </c>
       <c r="O9" s="64">
-        <v>2.03531169831321</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1.9286659923145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="69">
         <v>2021</v>
       </c>
       <c r="B10" s="69">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C10" s="69">
         <v>1</v>
@@ -21325,7 +21171,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="69">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G10" s="69" t="s">
         <v>225</v>
@@ -21336,21 +21182,29 @@
       <c r="I10" s="70" t="s">
         <v>220</v>
       </c>
-      <c r="J10" s="69" t="s">
-        <v>242</v>
-      </c>
-      <c r="K10" s="69"/>
-      <c r="L10" s="69"/>
-      <c r="M10" s="69"/>
-      <c r="N10" s="69"/>
-      <c r="O10" s="69"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="76">
-        <v>2024</v>
+      <c r="J10" s="69"/>
+      <c r="K10" s="69">
+        <v>1000</v>
+      </c>
+      <c r="L10" s="69">
+        <v>8.3756000000000004</v>
+      </c>
+      <c r="M10" s="69">
+        <v>1</v>
+      </c>
+      <c r="N10" s="69">
+        <v>119.394431443717</v>
+      </c>
+      <c r="O10" s="69">
+        <v>2.03531169831321</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" s="72">
+        <v>2021</v>
       </c>
       <c r="B11" s="67">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="67">
         <v>1</v>
@@ -21362,429 +21216,214 @@
         <v>1</v>
       </c>
       <c r="F11" s="67">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G11" s="67" t="s">
         <v>225</v>
       </c>
       <c r="H11" s="67" t="s">
-        <v>247</v>
+        <v>37</v>
       </c>
       <c r="I11" s="68" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J11" s="67"/>
       <c r="K11" s="67">
         <v>1000</v>
       </c>
       <c r="L11" s="67">
-        <v>7.2114000000000003</v>
+        <v>8.3756000000000004</v>
       </c>
       <c r="M11" s="67">
         <v>1</v>
       </c>
       <c r="N11" s="67">
-        <v>138.66932911778599</v>
-      </c>
-      <c r="O11" s="78">
-        <v>0.929754688179387</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="80">
-        <v>2024</v>
+        <v>119.394431443717</v>
+      </c>
+      <c r="O11" s="73">
+        <v>2.03531169831321</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" s="74">
+        <v>2022</v>
       </c>
       <c r="B12" s="69">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="69">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D12" s="69">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E12" s="69">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="F12" s="69">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G12" s="69" t="s">
         <v>225</v>
       </c>
       <c r="H12" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="70" t="s">
+        <v>220</v>
+      </c>
+      <c r="J12" s="69"/>
+      <c r="K12" s="69">
+        <v>1000</v>
+      </c>
+      <c r="L12" s="69">
+        <v>8.3750999999999998</v>
+      </c>
+      <c r="M12" s="69">
+        <v>1</v>
+      </c>
+      <c r="N12" s="69">
+        <v>119.401559384366</v>
+      </c>
+      <c r="O12" s="75">
+        <v>1.8352099609999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A13" s="74">
+        <v>2024</v>
+      </c>
+      <c r="B13" s="69">
+        <v>2</v>
+      </c>
+      <c r="C13" s="69">
+        <v>1</v>
+      </c>
+      <c r="D13" s="69">
+        <v>0</v>
+      </c>
+      <c r="E13" s="69">
+        <v>1</v>
+      </c>
+      <c r="F13" s="69">
+        <v>7</v>
+      </c>
+      <c r="G13" s="69" t="s">
+        <v>225</v>
+      </c>
+      <c r="H13" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="70" t="s">
+        <v>220</v>
+      </c>
+      <c r="J13" s="69"/>
+      <c r="K13" s="69">
+        <v>1000</v>
+      </c>
+      <c r="L13" s="69">
+        <v>8.3575999999999997</v>
+      </c>
+      <c r="M13" s="69">
+        <v>1</v>
+      </c>
+      <c r="N13" s="69">
+        <v>119.65157461472199</v>
+      </c>
+      <c r="O13" s="75">
+        <v>1.8811551773110999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A14" s="72">
+        <v>2024</v>
+      </c>
+      <c r="B14" s="67">
+        <v>8</v>
+      </c>
+      <c r="C14" s="67">
+        <v>1</v>
+      </c>
+      <c r="D14" s="67">
+        <v>0</v>
+      </c>
+      <c r="E14" s="67">
+        <v>1</v>
+      </c>
+      <c r="F14" s="67">
+        <v>7</v>
+      </c>
+      <c r="G14" s="67" t="s">
+        <v>225</v>
+      </c>
+      <c r="H14" s="67" t="s">
         <v>247</v>
       </c>
-      <c r="I12" s="70" t="s">
+      <c r="I14" s="68" t="s">
         <v>221</v>
       </c>
-      <c r="J12" s="69" t="s">
-        <v>242</v>
-      </c>
-      <c r="K12" s="69"/>
-      <c r="L12" s="69"/>
-      <c r="M12" s="69"/>
-      <c r="N12" s="69"/>
-      <c r="O12" s="81"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="76">
-        <v>2020</v>
-      </c>
-      <c r="B13" s="67">
+      <c r="J14" s="67"/>
+      <c r="K14" s="67">
+        <v>1000</v>
+      </c>
+      <c r="L14" s="67">
+        <v>7.2114000000000003</v>
+      </c>
+      <c r="M14" s="67">
+        <v>1</v>
+      </c>
+      <c r="N14" s="67">
+        <v>138.66932911778599</v>
+      </c>
+      <c r="O14" s="73">
+        <v>0.929754688179387</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A15" s="74">
+        <v>2025</v>
+      </c>
+      <c r="B15" s="69">
         <v>8</v>
       </c>
-      <c r="C13" s="67">
-        <v>1</v>
-      </c>
-      <c r="D13" s="67">
-        <v>0</v>
-      </c>
-      <c r="E13" s="67">
-        <v>1</v>
-      </c>
-      <c r="F13" s="67">
-        <v>2</v>
-      </c>
-      <c r="G13" s="67" t="s">
+      <c r="C15" s="69">
+        <v>1</v>
+      </c>
+      <c r="D15" s="69">
+        <v>0</v>
+      </c>
+      <c r="E15" s="69">
+        <v>1</v>
+      </c>
+      <c r="F15" s="69">
+        <v>7</v>
+      </c>
+      <c r="G15" s="69" t="s">
         <v>225</v>
       </c>
-      <c r="H13" s="67" t="s">
-        <v>37</v>
-      </c>
-      <c r="I13" s="68" t="s">
+      <c r="H15" s="69" t="s">
+        <v>247</v>
+      </c>
+      <c r="I15" s="70" t="s">
         <v>220</v>
       </c>
-      <c r="J13" s="67"/>
-      <c r="K13" s="67">
-        <v>1000</v>
-      </c>
-      <c r="L13" s="67">
-        <v>8.3513999999999999</v>
-      </c>
-      <c r="M13" s="67">
-        <v>1</v>
-      </c>
-      <c r="N13" s="67">
-        <v>119.740402806715</v>
-      </c>
-      <c r="O13" s="78">
-        <v>1.9286659923145</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="80">
-        <v>2020</v>
-      </c>
-      <c r="B14" s="69">
-        <v>1</v>
-      </c>
-      <c r="C14" s="69">
-        <v>1</v>
-      </c>
-      <c r="D14" s="69">
-        <v>0</v>
-      </c>
-      <c r="E14" s="69">
-        <v>1</v>
-      </c>
-      <c r="F14" s="69">
-        <v>2</v>
-      </c>
-      <c r="G14" s="69" t="s">
-        <v>225</v>
-      </c>
-      <c r="H14" s="69" t="s">
-        <v>37</v>
-      </c>
-      <c r="I14" s="70" t="s">
-        <v>220</v>
-      </c>
-      <c r="J14" s="69"/>
-      <c r="K14" s="69">
-        <v>8.4133300801790405</v>
-      </c>
-      <c r="L14" s="69">
-        <v>8.3513999999999999</v>
-      </c>
-      <c r="M14" s="69">
-        <v>118.85899999999999</v>
-      </c>
-      <c r="N14" s="69">
-        <v>119.740402806715</v>
-      </c>
-      <c r="O14" s="81">
-        <v>1.9286659923145</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="76">
-        <v>2019</v>
-      </c>
-      <c r="B15" s="67">
-        <v>1</v>
-      </c>
-      <c r="C15" s="67">
-        <v>1</v>
-      </c>
-      <c r="D15" s="67">
-        <v>0</v>
-      </c>
-      <c r="E15" s="67">
-        <v>1</v>
-      </c>
-      <c r="F15" s="67">
-        <v>2</v>
-      </c>
-      <c r="G15" s="67" t="s">
-        <v>225</v>
-      </c>
-      <c r="H15" s="67" t="s">
-        <v>37</v>
-      </c>
-      <c r="I15" s="68" t="s">
-        <v>220</v>
-      </c>
-      <c r="J15" s="67"/>
-      <c r="K15" s="67">
-        <v>8.4133300801790405</v>
-      </c>
-      <c r="L15" s="67">
-        <v>8.3513999999999999</v>
-      </c>
-      <c r="M15" s="67">
-        <v>118.85899999999999</v>
-      </c>
-      <c r="N15" s="67">
-        <v>119.740402806715</v>
-      </c>
-      <c r="O15" s="78">
-        <v>1.9286659923145</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="80">
-        <v>2018</v>
-      </c>
-      <c r="B16" s="69">
-        <v>1</v>
-      </c>
-      <c r="C16" s="69">
-        <v>1</v>
-      </c>
-      <c r="D16" s="69">
-        <v>0</v>
-      </c>
-      <c r="E16" s="69">
-        <v>1</v>
-      </c>
-      <c r="F16" s="69">
-        <v>2</v>
-      </c>
-      <c r="G16" s="69" t="s">
-        <v>225</v>
-      </c>
-      <c r="H16" s="69" t="s">
-        <v>37</v>
-      </c>
-      <c r="I16" s="70" t="s">
-        <v>220</v>
-      </c>
-      <c r="J16" s="69"/>
-      <c r="K16" s="69">
-        <v>8.4133300801790405</v>
-      </c>
-      <c r="L16" s="69">
-        <v>8.3513999999999999</v>
-      </c>
-      <c r="M16" s="69">
-        <v>118.85899999999999</v>
-      </c>
-      <c r="N16" s="69">
-        <v>119.740402806715</v>
-      </c>
-      <c r="O16" s="81">
-        <v>1.9286659923145</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="76">
-        <v>2017</v>
-      </c>
-      <c r="B17" s="67">
-        <v>8</v>
-      </c>
-      <c r="C17" s="67">
-        <v>1</v>
-      </c>
-      <c r="D17" s="67">
-        <v>11</v>
-      </c>
-      <c r="E17" s="67">
-        <v>40</v>
-      </c>
-      <c r="F17" s="67">
-        <v>2</v>
-      </c>
-      <c r="G17" s="67" t="s">
-        <v>225</v>
-      </c>
-      <c r="H17" s="67" t="s">
-        <v>37</v>
-      </c>
-      <c r="I17" s="68" t="s">
-        <v>220</v>
-      </c>
-      <c r="J17" s="67"/>
-      <c r="K17" s="67">
-        <v>8.4133300801790405</v>
-      </c>
-      <c r="L17" s="67">
-        <v>8.3513999999999999</v>
-      </c>
-      <c r="M17" s="67">
-        <v>118.85899999999999</v>
-      </c>
-      <c r="N17" s="67">
-        <v>119.740402806715</v>
-      </c>
-      <c r="O17" s="78">
-        <v>1.9286659923145</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="80">
-        <v>2017</v>
-      </c>
-      <c r="B18" s="69">
-        <v>1</v>
-      </c>
-      <c r="C18" s="69">
-        <v>1</v>
-      </c>
-      <c r="D18" s="69">
-        <v>0</v>
-      </c>
-      <c r="E18" s="69">
-        <v>1</v>
-      </c>
-      <c r="F18" s="69">
-        <v>2</v>
-      </c>
-      <c r="G18" s="69" t="s">
-        <v>225</v>
-      </c>
-      <c r="H18" s="69" t="s">
-        <v>37</v>
-      </c>
-      <c r="I18" s="70" t="s">
-        <v>220</v>
-      </c>
-      <c r="J18" s="69"/>
-      <c r="K18" s="69">
-        <v>8.4133300801790405</v>
-      </c>
-      <c r="L18" s="69">
-        <v>8.3513999999999999</v>
-      </c>
-      <c r="M18" s="69">
-        <v>118.85899999999999</v>
-      </c>
-      <c r="N18" s="69">
-        <v>119.740402806715</v>
-      </c>
-      <c r="O18" s="81">
-        <v>1.9286659923145</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="76">
-        <v>2016</v>
-      </c>
-      <c r="B19" s="67">
-        <v>1</v>
-      </c>
-      <c r="C19" s="67">
-        <v>1</v>
-      </c>
-      <c r="D19" s="67">
-        <v>0</v>
-      </c>
-      <c r="E19" s="67">
-        <v>1</v>
-      </c>
-      <c r="F19" s="67">
-        <v>2</v>
-      </c>
-      <c r="G19" s="67" t="s">
-        <v>225</v>
-      </c>
-      <c r="H19" s="67" t="s">
-        <v>37</v>
-      </c>
-      <c r="I19" s="68" t="s">
-        <v>220</v>
-      </c>
-      <c r="J19" s="67"/>
-      <c r="K19" s="67">
-        <v>8.4133300801790405</v>
-      </c>
-      <c r="L19" s="67">
-        <v>8.3513999999999999</v>
-      </c>
-      <c r="M19" s="67">
-        <v>118.85899999999999</v>
-      </c>
-      <c r="N19" s="67">
-        <v>119.740402806715</v>
-      </c>
-      <c r="O19" s="78">
-        <v>1.9286659923145</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="77">
-        <v>2015</v>
-      </c>
-      <c r="B20" s="63">
-        <v>9</v>
-      </c>
-      <c r="C20" s="63">
-        <v>30</v>
-      </c>
-      <c r="D20" s="63">
-        <v>23</v>
-      </c>
-      <c r="E20" s="63">
-        <v>0</v>
-      </c>
-      <c r="F20" s="63">
-        <v>2</v>
-      </c>
-      <c r="G20" s="63" t="s">
-        <v>225</v>
-      </c>
-      <c r="H20" s="63" t="s">
-        <v>37</v>
-      </c>
-      <c r="I20" s="65" t="s">
-        <v>220</v>
-      </c>
-      <c r="J20" s="63"/>
-      <c r="K20" s="63">
-        <v>8.4133300801790405</v>
-      </c>
-      <c r="L20" s="63">
-        <v>8.3513999999999999</v>
-      </c>
-      <c r="M20" s="63">
-        <v>118.85899999999999</v>
-      </c>
-      <c r="N20" s="63">
-        <v>119.740402806715</v>
-      </c>
-      <c r="O20" s="79">
-        <v>1.9286659923145</v>
+      <c r="J15" s="69" t="s">
+        <v>215</v>
+      </c>
+      <c r="K15" s="64">
+        <v>8.3796999999999997</v>
+      </c>
+      <c r="L15" s="64">
+        <v>8.3796999999999997</v>
+      </c>
+      <c r="M15" s="64">
+        <v>119.336014415791</v>
+      </c>
+      <c r="N15" s="64">
+        <v>119.336014415791</v>
+      </c>
+      <c r="O15" s="80">
+        <v>1.0501569268589599</v>
       </c>
     </row>
   </sheetData>
@@ -21797,21 +21436,21 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71D78007-B334-4AFA-9368-61BFA621700B}">
-  <dimension ref="A1:O14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="9.7109375" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" customWidth="1"/>
-    <col min="14" max="14" width="15.28515625" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.5" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="12" max="12" width="14.5" customWidth="1"/>
+    <col min="13" max="13" width="13.5" customWidth="1"/>
+    <col min="14" max="14" width="15.33203125" customWidth="1"/>
+    <col min="15" max="15" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="62" t="s">
         <v>201</v>
       </c>
@@ -21858,9 +21497,9 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="63">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="B2" s="63">
         <v>8</v>
@@ -21875,32 +21514,40 @@
         <v>1</v>
       </c>
       <c r="F2" s="63">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G2" s="63" t="s">
         <v>226</v>
       </c>
       <c r="H2" s="63" t="s">
-        <v>214</v>
+        <v>86</v>
       </c>
       <c r="I2" s="65" t="s">
-        <v>253</v>
-      </c>
-      <c r="J2" s="63" t="s">
-        <v>215</v>
-      </c>
-      <c r="K2" s="63"/>
-      <c r="L2" s="63"/>
-      <c r="M2" s="63"/>
-      <c r="N2" s="63"/>
-      <c r="O2" s="63"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63">
+        <v>1000</v>
+      </c>
+      <c r="L2" s="63">
+        <v>8.4176000000000002</v>
+      </c>
+      <c r="M2" s="63">
+        <v>1</v>
+      </c>
+      <c r="N2" s="63">
+        <v>118.79870747006299</v>
+      </c>
+      <c r="O2" s="63">
+        <v>2.2908047722416698</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="64">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B3" s="64">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C3" s="64">
         <v>1</v>
@@ -21912,117 +21559,125 @@
         <v>1</v>
       </c>
       <c r="F3" s="64">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G3" s="64" t="s">
         <v>226</v>
       </c>
       <c r="H3" s="64" t="s">
-        <v>214</v>
+        <v>86</v>
       </c>
       <c r="I3" s="66" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="J3" s="64"/>
       <c r="K3" s="64">
-        <v>8.2452000000000005</v>
+        <v>1000</v>
       </c>
       <c r="L3" s="64">
-        <v>8.2452000000000005</v>
+        <v>8.4390000000000001</v>
       </c>
       <c r="M3" s="64">
-        <v>121.282685683792</v>
+        <v>1</v>
       </c>
       <c r="N3" s="64">
-        <v>121.282685683792</v>
+        <v>118.497452304775</v>
       </c>
       <c r="O3" s="64">
-        <v>0.94600494833357596</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="64">
-        <v>2024</v>
-      </c>
-      <c r="B4" s="64">
-        <v>2</v>
-      </c>
-      <c r="C4" s="64">
-        <v>1</v>
-      </c>
-      <c r="D4" s="64">
-        <v>0</v>
-      </c>
-      <c r="E4" s="64">
-        <v>1</v>
-      </c>
-      <c r="F4" s="64">
-        <v>11</v>
-      </c>
-      <c r="G4" s="64" t="s">
+        <v>2.20773173146471</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A4" s="63">
+        <v>2021</v>
+      </c>
+      <c r="B4" s="63">
+        <v>7</v>
+      </c>
+      <c r="C4" s="63">
+        <v>1</v>
+      </c>
+      <c r="D4" s="63">
+        <v>0</v>
+      </c>
+      <c r="E4" s="63">
+        <v>1</v>
+      </c>
+      <c r="F4" s="63">
+        <v>3</v>
+      </c>
+      <c r="G4" s="63" t="s">
         <v>226</v>
       </c>
-      <c r="H4" s="64" t="s">
+      <c r="H4" s="63" t="s">
         <v>248</v>
       </c>
-      <c r="I4" s="66" t="s">
+      <c r="I4" s="65" t="s">
         <v>255</v>
       </c>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64">
-        <v>1000</v>
-      </c>
-      <c r="L4" s="64">
-        <v>13.308199999999999</v>
-      </c>
-      <c r="M4" s="64">
-        <v>1</v>
-      </c>
-      <c r="N4" s="64">
-        <v>75.141641995160896</v>
-      </c>
-      <c r="O4" s="64">
-        <v>1.2914628942617901</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="63">
-        <v>2024</v>
-      </c>
-      <c r="B5" s="63">
-        <v>2</v>
-      </c>
-      <c r="C5" s="63">
-        <v>1</v>
-      </c>
-      <c r="D5" s="63">
-        <v>0</v>
-      </c>
-      <c r="E5" s="63">
-        <v>1</v>
-      </c>
-      <c r="F5" s="63">
+      <c r="J4" s="63"/>
+      <c r="K4" s="63">
+        <v>1000</v>
+      </c>
+      <c r="L4" s="63">
+        <v>13.3057</v>
+      </c>
+      <c r="M4" s="63">
+        <v>1</v>
+      </c>
+      <c r="N4" s="63">
+        <v>75.155760313249203</v>
+      </c>
+      <c r="O4" s="63">
+        <v>0.83122061412608705</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" s="64">
+        <v>2022</v>
+      </c>
+      <c r="B5" s="64">
+        <v>7</v>
+      </c>
+      <c r="C5" s="64">
+        <v>19</v>
+      </c>
+      <c r="D5" s="64">
         <v>12</v>
       </c>
-      <c r="G5" s="63" t="s">
+      <c r="E5" s="64">
+        <v>46</v>
+      </c>
+      <c r="F5" s="64">
+        <v>3</v>
+      </c>
+      <c r="G5" s="64" t="s">
         <v>226</v>
       </c>
-      <c r="H5" s="63" t="s">
+      <c r="H5" s="64" t="s">
         <v>248</v>
       </c>
-      <c r="I5" s="65" t="s">
+      <c r="I5" s="66" t="s">
         <v>255</v>
       </c>
-      <c r="J5" s="63" t="s">
-        <v>242</v>
-      </c>
-      <c r="K5" s="63"/>
-      <c r="L5" s="63"/>
-      <c r="M5" s="63"/>
-      <c r="N5" s="63"/>
-      <c r="O5" s="63"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J5" s="64"/>
+      <c r="K5" s="64">
+        <v>1000</v>
+      </c>
+      <c r="L5" s="64">
+        <v>13.317600000000001</v>
+      </c>
+      <c r="M5" s="64">
+        <v>1</v>
+      </c>
+      <c r="N5" s="64">
+        <v>75.088604553373003</v>
+      </c>
+      <c r="O5" s="64">
+        <v>1.2169603471391199</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="64">
         <v>2024</v>
       </c>
@@ -22039,7 +21694,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="64">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G6" s="64" t="s">
         <v>226</v>
@@ -22050,349 +21705,111 @@
       <c r="I6" s="66" t="s">
         <v>255</v>
       </c>
-      <c r="J6" s="64" t="s">
-        <v>243</v>
-      </c>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="64"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="64">
-        <v>2022</v>
-      </c>
-      <c r="B7" s="64">
-        <v>7</v>
-      </c>
-      <c r="C7" s="64">
-        <v>19</v>
-      </c>
-      <c r="D7" s="64">
+      <c r="J6" s="64"/>
+      <c r="K6" s="64">
+        <v>1000</v>
+      </c>
+      <c r="L6" s="64">
+        <v>13.308199999999999</v>
+      </c>
+      <c r="M6" s="64">
+        <v>1</v>
+      </c>
+      <c r="N6" s="64">
+        <v>75.141641995160896</v>
+      </c>
+      <c r="O6" s="64">
+        <v>1.2914628942617901</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="69">
+        <v>2024</v>
+      </c>
+      <c r="B7" s="69">
+        <v>8</v>
+      </c>
+      <c r="C7" s="69">
+        <v>1</v>
+      </c>
+      <c r="D7" s="69">
+        <v>0</v>
+      </c>
+      <c r="E7" s="69">
+        <v>1</v>
+      </c>
+      <c r="F7" s="69">
+        <v>11</v>
+      </c>
+      <c r="G7" s="69" t="s">
+        <v>226</v>
+      </c>
+      <c r="H7" s="69" t="s">
+        <v>214</v>
+      </c>
+      <c r="I7" s="70" t="s">
+        <v>270</v>
+      </c>
+      <c r="J7" s="69"/>
+      <c r="K7" s="69">
+        <v>1000</v>
+      </c>
+      <c r="L7" s="69">
+        <v>8.6873000000000005</v>
+      </c>
+      <c r="M7" s="69">
+        <v>1</v>
+      </c>
+      <c r="N7" s="69">
+        <v>115.11056369643001</v>
+      </c>
+      <c r="O7" s="69">
+        <v>2.4150196263511101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" s="67">
+        <v>2025</v>
+      </c>
+      <c r="B8" s="67">
+        <v>8</v>
+      </c>
+      <c r="C8" s="67">
+        <v>1</v>
+      </c>
+      <c r="D8" s="67">
+        <v>0</v>
+      </c>
+      <c r="E8" s="67">
+        <v>1</v>
+      </c>
+      <c r="F8" s="67">
         <v>12</v>
       </c>
-      <c r="E7" s="64">
-        <v>46</v>
-      </c>
-      <c r="F7" s="64">
-        <v>3</v>
-      </c>
-      <c r="G7" s="64" t="s">
+      <c r="G8" s="67" t="s">
         <v>226</v>
       </c>
-      <c r="H7" s="64" t="s">
-        <v>248</v>
-      </c>
-      <c r="I7" s="66" t="s">
-        <v>255</v>
-      </c>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64">
-        <v>1000</v>
-      </c>
-      <c r="L7" s="64">
-        <v>13.317600000000001</v>
-      </c>
-      <c r="M7" s="64">
-        <v>1</v>
-      </c>
-      <c r="N7" s="64">
-        <v>75.088604553373003</v>
-      </c>
-      <c r="O7" s="64">
-        <v>1.2169603471391199</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="63">
-        <v>2022</v>
-      </c>
-      <c r="B8" s="63">
-        <v>7</v>
-      </c>
-      <c r="C8" s="63">
-        <v>19</v>
-      </c>
-      <c r="D8" s="63">
-        <v>12</v>
-      </c>
-      <c r="E8" s="63">
-        <v>46</v>
-      </c>
-      <c r="F8" s="63">
-        <v>6</v>
-      </c>
-      <c r="G8" s="63" t="s">
-        <v>226</v>
-      </c>
-      <c r="H8" s="63" t="s">
-        <v>248</v>
-      </c>
-      <c r="I8" s="65" t="s">
-        <v>255</v>
-      </c>
-      <c r="J8" s="63" t="s">
-        <v>242</v>
-      </c>
-      <c r="K8" s="63"/>
-      <c r="L8" s="63"/>
-      <c r="M8" s="63"/>
-      <c r="N8" s="63"/>
-      <c r="O8" s="63"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="64">
-        <v>2021</v>
-      </c>
-      <c r="B9" s="64">
-        <v>1</v>
-      </c>
-      <c r="C9" s="64">
-        <v>1</v>
-      </c>
-      <c r="D9" s="64">
-        <v>0</v>
-      </c>
-      <c r="E9" s="64">
-        <v>1</v>
-      </c>
-      <c r="F9" s="64">
-        <v>3</v>
-      </c>
-      <c r="G9" s="64" t="s">
-        <v>226</v>
-      </c>
-      <c r="H9" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="I9" s="66" t="s">
-        <v>218</v>
-      </c>
-      <c r="J9" s="64"/>
-      <c r="K9" s="64">
-        <v>1000</v>
-      </c>
-      <c r="L9" s="64">
-        <v>8.4390000000000001</v>
-      </c>
-      <c r="M9" s="64">
-        <v>1</v>
-      </c>
-      <c r="N9" s="64">
-        <v>118.497452304775</v>
-      </c>
-      <c r="O9" s="64">
-        <v>2.20773173146471</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="63">
-        <v>2021</v>
-      </c>
-      <c r="B10" s="63">
-        <v>7</v>
-      </c>
-      <c r="C10" s="63">
-        <v>1</v>
-      </c>
-      <c r="D10" s="63">
-        <v>0</v>
-      </c>
-      <c r="E10" s="63">
-        <v>1</v>
-      </c>
-      <c r="F10" s="63">
-        <v>3</v>
-      </c>
-      <c r="G10" s="63" t="s">
-        <v>226</v>
-      </c>
-      <c r="H10" s="63" t="s">
-        <v>248</v>
-      </c>
-      <c r="I10" s="65" t="s">
-        <v>255</v>
-      </c>
-      <c r="J10" s="63"/>
-      <c r="K10" s="63">
-        <v>1000</v>
-      </c>
-      <c r="L10" s="63">
-        <v>13.3057</v>
-      </c>
-      <c r="M10" s="63">
-        <v>1</v>
-      </c>
-      <c r="N10" s="63">
-        <v>75.155760313249203</v>
-      </c>
-      <c r="O10" s="63">
-        <v>0.83122061412608705</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="64">
-        <v>2021</v>
-      </c>
-      <c r="B11" s="64">
-        <v>7</v>
-      </c>
-      <c r="C11" s="64">
-        <v>1</v>
-      </c>
-      <c r="D11" s="64">
-        <v>0</v>
-      </c>
-      <c r="E11" s="64">
-        <v>1</v>
-      </c>
-      <c r="F11" s="64">
-        <v>6</v>
-      </c>
-      <c r="G11" s="64" t="s">
-        <v>226</v>
-      </c>
-      <c r="H11" s="64" t="s">
-        <v>248</v>
-      </c>
-      <c r="I11" s="66" t="s">
-        <v>255</v>
-      </c>
-      <c r="J11" s="64" t="s">
-        <v>242</v>
-      </c>
-      <c r="K11" s="64"/>
-      <c r="L11" s="64"/>
-      <c r="M11" s="64"/>
-      <c r="N11" s="64"/>
-      <c r="O11" s="64"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="69">
-        <v>2024</v>
-      </c>
-      <c r="B12" s="69">
-        <v>8</v>
-      </c>
-      <c r="C12" s="69">
-        <v>1</v>
-      </c>
-      <c r="D12" s="69">
-        <v>0</v>
-      </c>
-      <c r="E12" s="69">
-        <v>1</v>
-      </c>
-      <c r="F12" s="69">
-        <v>11</v>
-      </c>
-      <c r="G12" s="69" t="s">
-        <v>226</v>
-      </c>
-      <c r="H12" s="69" t="s">
+      <c r="H8" s="67" t="s">
         <v>214</v>
       </c>
-      <c r="I12" s="70" t="s">
-        <v>271</v>
-      </c>
-      <c r="J12" s="69"/>
-      <c r="K12" s="69">
-        <v>1000</v>
-      </c>
-      <c r="L12" s="69">
-        <v>8.6873000000000005</v>
-      </c>
-      <c r="M12" s="69">
-        <v>1</v>
-      </c>
-      <c r="N12" s="69">
-        <v>115.11056369643001</v>
-      </c>
-      <c r="O12" s="69">
-        <v>2.4150196263511101</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="67">
-        <v>2024</v>
-      </c>
-      <c r="B13" s="67">
-        <v>8</v>
-      </c>
-      <c r="C13" s="67">
-        <v>1</v>
-      </c>
-      <c r="D13" s="67">
-        <v>0</v>
-      </c>
-      <c r="E13" s="67">
-        <v>1</v>
-      </c>
-      <c r="F13" s="67">
-        <v>12</v>
-      </c>
-      <c r="G13" s="67" t="s">
-        <v>226</v>
-      </c>
-      <c r="H13" s="67" t="s">
-        <v>214</v>
-      </c>
-      <c r="I13" s="68" t="s">
-        <v>271</v>
-      </c>
-      <c r="J13" s="67" t="s">
-        <v>242</v>
-      </c>
-      <c r="K13" s="67"/>
-      <c r="L13" s="67"/>
-      <c r="M13" s="67"/>
-      <c r="N13" s="67"/>
-      <c r="O13" s="67"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="69">
-        <v>2020</v>
-      </c>
-      <c r="B14" s="69">
-        <v>8</v>
-      </c>
-      <c r="C14" s="69">
-        <v>1</v>
-      </c>
-      <c r="D14" s="69">
-        <v>0</v>
-      </c>
-      <c r="E14" s="69">
-        <v>1</v>
-      </c>
-      <c r="F14" s="69">
-        <v>3</v>
-      </c>
-      <c r="G14" s="69" t="s">
-        <v>226</v>
-      </c>
-      <c r="H14" s="69" t="s">
-        <v>86</v>
-      </c>
-      <c r="I14" s="70" t="s">
-        <v>218</v>
-      </c>
-      <c r="J14" s="69"/>
-      <c r="K14" s="69">
-        <v>1000</v>
-      </c>
-      <c r="L14" s="69">
-        <v>8.4176000000000002</v>
-      </c>
-      <c r="M14" s="69">
-        <v>1</v>
-      </c>
-      <c r="N14" s="69">
-        <v>118.79870747006299</v>
-      </c>
-      <c r="O14" s="69">
-        <v>2.2908047722416698</v>
+      <c r="I8" s="68" t="s">
+        <v>253</v>
+      </c>
+      <c r="J8" s="67"/>
+      <c r="K8" s="67">
+        <v>8.2452000000000005</v>
+      </c>
+      <c r="L8" s="67">
+        <v>8.2452000000000005</v>
+      </c>
+      <c r="M8" s="67">
+        <v>121.282685683792</v>
+      </c>
+      <c r="N8" s="67">
+        <v>121.282685683792</v>
+      </c>
+      <c r="O8" s="67">
+        <v>0.94600494833357596</v>
       </c>
     </row>
   </sheetData>
@@ -22406,20 +21823,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EB1D8E7-B939-4F56-8304-C86C81BE8A5F}">
   <dimension ref="A1:O7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="9.7109375" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" customWidth="1"/>
-    <col min="14" max="14" width="15.28515625" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.5" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="12" max="12" width="14.5" customWidth="1"/>
+    <col min="13" max="13" width="13.5" customWidth="1"/>
+    <col min="14" max="14" width="15.33203125" customWidth="1"/>
+    <col min="15" max="15" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="62" t="s">
         <v>201</v>
       </c>
@@ -22466,7 +21883,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="63">
         <v>2025</v>
       </c>
@@ -22511,7 +21928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="64">
         <v>2024</v>
       </c>
@@ -22556,7 +21973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="63">
         <v>2024</v>
       </c>
@@ -22601,7 +22018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="64">
         <v>2022</v>
       </c>
@@ -22646,7 +22063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="63">
         <v>2021</v>
       </c>
@@ -22691,7 +22108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="67">
         <v>2021</v>
       </c>
@@ -22747,20 +22164,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1159179F-CF4E-4E88-AA90-1605119874FB}">
   <dimension ref="A1:O15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="9.7109375" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" customWidth="1"/>
-    <col min="14" max="14" width="15.28515625" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.5" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="12" max="12" width="14.5" customWidth="1"/>
+    <col min="13" max="13" width="13.5" customWidth="1"/>
+    <col min="14" max="14" width="15.33203125" customWidth="1"/>
+    <col min="15" max="15" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="62" t="s">
         <v>201</v>
       </c>
@@ -22807,7 +22224,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="63">
         <v>2021</v>
       </c>
@@ -22842,7 +22259,7 @@
       <c r="N2" s="63"/>
       <c r="O2" s="63"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="64">
         <v>2021</v>
       </c>
@@ -22877,7 +22294,7 @@
       <c r="N3" s="64"/>
       <c r="O3" s="64"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="63">
         <v>2021</v>
       </c>
@@ -22912,7 +22329,7 @@
       <c r="N4" s="63"/>
       <c r="O4" s="63"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="64">
         <v>2021</v>
       </c>
@@ -22957,7 +22374,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="63">
         <v>2021</v>
       </c>
@@ -23002,7 +22419,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="64">
         <v>2021</v>
       </c>
@@ -23047,7 +22464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="63">
         <v>2021</v>
       </c>
@@ -23092,7 +22509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="64">
         <v>2020</v>
       </c>
@@ -23127,7 +22544,7 @@
       <c r="N9" s="64"/>
       <c r="O9" s="64"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="63">
         <v>2020</v>
       </c>
@@ -23162,7 +22579,7 @@
       <c r="N10" s="63"/>
       <c r="O10" s="63"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="64">
         <v>2020</v>
       </c>
@@ -23197,7 +22614,7 @@
       <c r="N11" s="64"/>
       <c r="O11" s="64"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="63">
         <v>2020</v>
       </c>
@@ -23242,7 +22659,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="64">
         <v>2020</v>
       </c>
@@ -23287,7 +22704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="63">
         <v>2020</v>
       </c>
@@ -23332,7 +22749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="67">
         <v>2020</v>
       </c>
@@ -23388,20 +22805,20 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7847FC27-2935-424C-A158-6B9B5A8DB710}">
   <dimension ref="A1:O4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="9.7109375" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" customWidth="1"/>
-    <col min="14" max="14" width="15.28515625" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.5" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="12" max="12" width="14.5" customWidth="1"/>
+    <col min="13" max="13" width="13.5" customWidth="1"/>
+    <col min="14" max="14" width="15.33203125" customWidth="1"/>
+    <col min="15" max="15" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="62" t="s">
         <v>201</v>
       </c>
@@ -23448,7 +22865,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="63">
         <v>2025</v>
       </c>
@@ -23483,7 +22900,7 @@
       <c r="N2" s="63"/>
       <c r="O2" s="63"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="64">
         <v>2024</v>
       </c>
@@ -23518,7 +22935,7 @@
       <c r="N3" s="64"/>
       <c r="O3" s="64"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="69">
         <v>2024</v>
       </c>
@@ -23564,20 +22981,20 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7BE515-81CD-497C-A39A-B15BC3D309FD}">
   <dimension ref="A1:O4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="9.7109375" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" customWidth="1"/>
-    <col min="14" max="14" width="15.28515625" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.5" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="12" max="12" width="14.5" customWidth="1"/>
+    <col min="13" max="13" width="13.5" customWidth="1"/>
+    <col min="14" max="14" width="15.33203125" customWidth="1"/>
+    <col min="15" max="15" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="62" t="s">
         <v>201</v>
       </c>
@@ -23624,7 +23041,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="63">
         <v>2025</v>
       </c>
@@ -23659,7 +23076,7 @@
       <c r="N2" s="63"/>
       <c r="O2" s="63"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="64">
         <v>2024</v>
       </c>
@@ -23694,7 +23111,7 @@
       <c r="N3" s="64"/>
       <c r="O3" s="64"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="69">
         <v>2024</v>
       </c>

--- a/STW programs/STW_sitefile_and_mapping.xlsx
+++ b/STW programs/STW_sitefile_and_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/finnfujimura/Desktop/LEI-SRML-Intern-Project/STW programs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\finnf\Desktop\LEI-SRML-Intern-Project\STW programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9144FD34-92E7-E647-BA79-D60AC4971DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76A56CF-80F2-4854-A879-D9BD9079E865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31230" yWindow="1740" windowWidth="22230" windowHeight="12930" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="STW site" sheetId="2" r:id="rId1"/>
@@ -1791,6 +1791,7 @@
     <xf numFmtId="0" fontId="22" fillId="48" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="47" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="47" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="48" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1803,7 +1804,6 @@
     <xf numFmtId="0" fontId="16" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="48" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -5154,42 +5154,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V185"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="4.83203125" style="17" customWidth="1"/>
-    <col min="8" max="9" width="18.6640625" style="43" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" style="43" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="4.85546875" style="17" customWidth="1"/>
+    <col min="8" max="9" width="18.7109375" style="43" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="43" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="3" style="15" customWidth="1"/>
-    <col min="12" max="12" width="23.1640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.83203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="4.33203125" style="17" customWidth="1"/>
-    <col min="16" max="16" width="22.33203125" style="43" customWidth="1"/>
+    <col min="12" max="12" width="23.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="4.28515625" style="17" customWidth="1"/>
+    <col min="16" max="16" width="22.28515625" style="43" customWidth="1"/>
     <col min="17" max="17" width="33" style="43" customWidth="1"/>
-    <col min="18" max="18" width="47.83203125" style="43" customWidth="1"/>
-    <col min="19" max="19" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="47.85546875" style="43" customWidth="1"/>
+    <col min="19" max="19" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="76" t="s">
+      <c r="D1" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="76"/>
-      <c r="F1" s="78" t="s">
+      <c r="E1" s="77"/>
+      <c r="F1" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="79"/>
-      <c r="H1" s="77" t="s">
+      <c r="G1" s="80"/>
+      <c r="H1" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="77"/>
+      <c r="I1" s="78"/>
       <c r="J1" s="46"/>
       <c r="K1" s="13"/>
       <c r="L1" s="5" t="s">
@@ -5214,7 +5214,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -5238,7 +5238,7 @@
       <c r="U2"/>
       <c r="V2"/>
     </row>
-    <row r="3" spans="1:22" ht="48" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="K3" s="14"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="D4" s="4" t="s">
         <v>114</v>
       </c>
@@ -5290,7 +5290,7 @@
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:22" ht="96" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -5331,7 +5331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
@@ -5345,7 +5345,7 @@
       <c r="I6" s="42"/>
       <c r="J6" s="42"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -5359,7 +5359,7 @@
       <c r="I7" s="42"/>
       <c r="J7" s="42"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -5373,7 +5373,7 @@
       <c r="I8" s="42"/>
       <c r="J8" s="42"/>
     </row>
-    <row r="9" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
@@ -5397,7 +5397,7 @@
       <c r="Q9" s="43"/>
       <c r="R9" s="42"/>
     </row>
-    <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
@@ -5439,7 +5439,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C11" s="9"/>
     </row>
-    <row r="12" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
@@ -5457,12 +5457,12 @@
       </c>
       <c r="C12" s="9"/>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <f>IF(LEN(C14)=17,LEFT(C14,4)+(B14-1)/(DATE(LEFT(C14,4)+1,1,1)-DATE(LEFT(C14,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2015.7478310502283</v>
@@ -5481,7 +5481,7 @@
       <c r="P14" s="48"/>
       <c r="Q14" s="48"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
         <v>1000</v>
       </c>
@@ -5536,7 +5536,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>2010</v>
       </c>
@@ -5591,7 +5591,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>9300</v>
       </c>
@@ -5645,12 +5645,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="21">
         <f>IF(LEN(C19)=17,LEFT(C19,4)+(B19-1)/(DATE(LEFT(C19,4)+1,1,1)-DATE(LEFT(C19,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2016.0000018973892</v>
@@ -5669,7 +5669,7 @@
       <c r="P19" s="48"/>
       <c r="Q19" s="48"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="16">
         <v>1000</v>
       </c>
@@ -5724,7 +5724,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>2010</v>
       </c>
@@ -5779,7 +5779,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>9300</v>
       </c>
@@ -5833,12 +5833,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="20">
         <f>IF(LEN(C24)=17,LEFT(C24,4)+(B24-1)/(DATE(LEFT(C24,4)+1,1,1)-DATE(LEFT(C24,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2017.0000019025874</v>
@@ -5857,7 +5857,7 @@
       <c r="P24" s="48"/>
       <c r="Q24" s="48"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="16">
         <v>1000</v>
       </c>
@@ -5912,7 +5912,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>2010</v>
       </c>
@@ -5967,7 +5967,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>9300</v>
       </c>
@@ -6021,12 +6021,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <f>IF(LEN(C29)=17,LEFT(C29,4)+(B29-1)/(DATE(LEFT(C29,4)+1,1,1)-DATE(LEFT(C29,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2017.5821537290715</v>
@@ -6045,7 +6045,7 @@
       <c r="P29" s="48"/>
       <c r="Q29" s="48"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="16">
         <v>1000</v>
       </c>
@@ -6100,7 +6100,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>2010</v>
       </c>
@@ -6155,7 +6155,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>9300</v>
       </c>
@@ -6209,12 +6209,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
         <f>IF(LEN(C34)=17,LEFT(C34,4)+(B34-1)/(DATE(LEFT(C34,4)+1,1,1)-DATE(LEFT(C34,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2018.0000019025874</v>
@@ -6233,7 +6233,7 @@
       <c r="P34" s="48"/>
       <c r="Q34" s="48"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
         <v>1000</v>
       </c>
@@ -6288,7 +6288,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>2010</v>
       </c>
@@ -6343,7 +6343,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>9300</v>
       </c>
@@ -6397,12 +6397,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="10">
         <f>IF(LEN(C39)=17,LEFT(C39,4)+(B39-1)/(DATE(LEFT(C39,4)+1,1,1)-DATE(LEFT(C39,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2019.0000019025874</v>
@@ -6421,7 +6421,7 @@
       <c r="P39" s="48"/>
       <c r="Q39" s="48"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="16">
         <v>1000</v>
       </c>
@@ -6476,7 +6476,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>2010</v>
       </c>
@@ -6531,7 +6531,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>9300</v>
       </c>
@@ -6585,12 +6585,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="10">
         <f>IF(LEN(C44)=17,LEFT(C44,4)+(B44-1)/(DATE(LEFT(C44,4)+1,1,1)-DATE(LEFT(C44,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2020.0000018973892</v>
@@ -6609,7 +6609,7 @@
       <c r="P44" s="48"/>
       <c r="Q44" s="48"/>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="16">
         <v>1000</v>
       </c>
@@ -6664,7 +6664,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>2010</v>
       </c>
@@ -6719,7 +6719,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>9300</v>
       </c>
@@ -6773,7 +6773,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>0</v>
       </c>
@@ -6826,12 +6826,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="10">
         <f>IF(LEN(C50)=17,LEFT(C50,4)+(B50-1)/(DATE(LEFT(C50,4)+1,1,1)-DATE(LEFT(C50,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2020.5819691105039</v>
@@ -6853,7 +6853,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="16">
         <v>1000</v>
       </c>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="S51" s="28"/>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="16">
         <v>2010</v>
       </c>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="S52" s="28"/>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="16">
         <v>3000</v>
       </c>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="S53" s="28"/>
     </row>
-    <row r="54" spans="1:20" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="16">
         <v>0</v>
       </c>
@@ -7077,7 +7077,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="16">
         <v>0</v>
       </c>
@@ -7136,7 +7136,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="16" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="16">
         <v>0</v>
       </c>
@@ -7195,7 +7195,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
         <v>78</v>
       </c>
@@ -7250,7 +7250,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
         <v>79</v>
       </c>
@@ -7305,7 +7305,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
         <v>80</v>
       </c>
@@ -7360,7 +7360,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>7009</v>
       </c>
@@ -7416,7 +7416,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>7008</v>
       </c>
@@ -7469,7 +7469,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>9388</v>
       </c>
@@ -7522,7 +7522,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>9389</v>
       </c>
@@ -7575,7 +7575,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>9300</v>
       </c>
@@ -7629,7 +7629,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>0</v>
       </c>
@@ -7682,12 +7682,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <f>IF(LEN(C67)=17,LEFT(C67,4)+(B67-1)/(DATE(LEFT(C67,4)+1,1,1)-DATE(LEFT(C67,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2021.0000019025874</v>
@@ -7709,7 +7709,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" s="16">
         <v>1000</v>
       </c>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="S68" s="28"/>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" s="16">
         <v>2010</v>
       </c>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="S69" s="28"/>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="16">
         <v>3000</v>
       </c>
@@ -7877,7 +7877,7 @@
       </c>
       <c r="S70" s="28"/>
     </row>
-    <row r="71" spans="1:20" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" s="16">
         <v>0</v>
       </c>
@@ -7933,7 +7933,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="72" spans="1:20" ht="16" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" s="16">
         <v>0</v>
       </c>
@@ -7992,7 +7992,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="73" spans="1:20" ht="16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="16">
         <v>0</v>
       </c>
@@ -8051,7 +8051,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
         <v>78</v>
       </c>
@@ -8106,7 +8106,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="10" t="s">
         <v>79</v>
       </c>
@@ -8161,7 +8161,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
         <v>80</v>
       </c>
@@ -8216,7 +8216,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>7009</v>
       </c>
@@ -8272,7 +8272,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>7008</v>
       </c>
@@ -8325,7 +8325,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>9388</v>
       </c>
@@ -8378,7 +8378,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>9389</v>
       </c>
@@ -8431,7 +8431,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>9300</v>
       </c>
@@ -8485,7 +8485,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>0</v>
       </c>
@@ -8538,12 +8538,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <f>IF(LEN(C84)=17,LEFT(C84,4)+(B84-1)/(DATE(LEFT(C84,4)+1,1,1)-DATE(LEFT(C84,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2021.4958923135464</v>
@@ -8565,7 +8565,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" s="35">
         <v>1000</v>
       </c>
@@ -8623,7 +8623,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" s="16">
         <v>2010</v>
       </c>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="S86" s="28"/>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" s="35">
         <v>3000</v>
       </c>
@@ -8737,7 +8737,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="88" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88" s="35">
         <v>0</v>
       </c>
@@ -8790,7 +8790,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="89" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" s="16">
         <v>0</v>
       </c>
@@ -8843,7 +8843,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="90" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" s="35">
         <v>0</v>
       </c>
@@ -8896,7 +8896,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" s="36" t="s">
         <v>78</v>
       </c>
@@ -8952,7 +8952,7 @@
       </c>
       <c r="S91" s="28"/>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
         <v>79</v>
       </c>
@@ -9008,7 +9008,7 @@
       </c>
       <c r="S92" s="28"/>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93" s="36" t="s">
         <v>80</v>
       </c>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="S93" s="28"/>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>9300</v>
       </c>
@@ -9118,7 +9118,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" s="25">
         <v>9380</v>
       </c>
@@ -9171,7 +9171,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96" s="25">
         <v>9381</v>
       </c>
@@ -9224,7 +9224,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>0</v>
       </c>
@@ -9277,12 +9277,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <f>IF(LEN(C99)=17,LEFT(C99,4)+(B99-1)/(DATE(LEFT(C99,4)+1,1,1)-DATE(LEFT(C99,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2022.5466628614915</v>
@@ -9301,7 +9301,7 @@
       <c r="P99" s="48"/>
       <c r="Q99" s="48"/>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A100" s="16">
         <v>1000</v>
       </c>
@@ -9357,7 +9357,7 @@
       </c>
       <c r="S100" s="28"/>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101" s="16">
         <v>2010</v>
       </c>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="S101" s="28"/>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" s="16">
         <v>3000</v>
       </c>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="S102" s="28"/>
     </row>
-    <row r="103" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A103" s="16">
         <v>0</v>
       </c>
@@ -9522,7 +9522,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="104" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A104" s="16">
         <v>0</v>
       </c>
@@ -9575,7 +9575,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="105" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A105" s="16">
         <v>0</v>
       </c>
@@ -9628,7 +9628,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A106" s="10" t="s">
         <v>78</v>
       </c>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="S106" s="28"/>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A107" s="10" t="s">
         <v>79</v>
       </c>
@@ -9740,7 +9740,7 @@
       </c>
       <c r="S107" s="28"/>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="s">
         <v>80</v>
       </c>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="S108" s="28"/>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>9300</v>
       </c>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="Q109" s="48"/>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>9380</v>
       </c>
@@ -9891,7 +9891,7 @@
       <c r="P110" s="48"/>
       <c r="Q110" s="48"/>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>9381</v>
       </c>
@@ -9937,7 +9937,7 @@
       <c r="P111" s="48"/>
       <c r="Q111" s="48"/>
     </row>
-    <row r="112" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>0</v>
       </c>
@@ -9990,12 +9990,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A114" s="10">
         <f>IF(LEN(C114)=17,LEFT(C114,4)+(B114-1)/(DATE(LEFT(C114,4)+1,1,1)-DATE(LEFT(C114,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2024.084701350941</v>
@@ -10014,7 +10014,7 @@
       <c r="P114" s="48"/>
       <c r="Q114" s="48"/>
     </row>
-    <row r="115" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>0</v>
       </c>
@@ -10067,7 +10067,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="116" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>0</v>
       </c>
@@ -10120,7 +10120,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A117" s="16">
         <v>1000</v>
       </c>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="S117" s="28"/>
     </row>
-    <row r="118" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A118" s="16">
         <v>0</v>
       </c>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="S118" s="28"/>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A119" s="16">
         <v>0</v>
       </c>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="S119" s="28"/>
     </row>
-    <row r="120" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A120" s="35">
         <v>0</v>
       </c>
@@ -10342,7 +10342,7 @@
       </c>
       <c r="S120" s="28"/>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A121" s="16">
         <v>2010</v>
       </c>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="S121" s="28"/>
     </row>
-    <row r="122" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A122" s="16">
         <v>0</v>
       </c>
@@ -10452,7 +10452,7 @@
       </c>
       <c r="S122" s="28"/>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A123" s="16">
         <v>0</v>
       </c>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="S123" s="28"/>
     </row>
-    <row r="124" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A124" s="35">
         <v>0</v>
       </c>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="S124" s="28"/>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A125" s="16">
         <v>3000</v>
       </c>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="S125" s="28"/>
     </row>
-    <row r="126" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A126" s="16">
         <v>0</v>
       </c>
@@ -10673,7 +10673,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A127" s="16">
         <v>0</v>
       </c>
@@ -10730,7 +10730,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="128" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A128" s="25">
         <v>0</v>
       </c>
@@ -10783,7 +10783,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="129" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A129" s="25">
         <v>0</v>
       </c>
@@ -10837,7 +10837,7 @@
       </c>
       <c r="S129" s="28"/>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>9300</v>
       </c>
@@ -10891,7 +10891,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="131" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>0</v>
       </c>
@@ -10944,7 +10944,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="132" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>0</v>
       </c>
@@ -10998,7 +10998,7 @@
       </c>
       <c r="S132" s="28"/>
     </row>
-    <row r="133" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>0</v>
       </c>
@@ -11051,7 +11051,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="134" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A134" s="47">
         <v>0</v>
       </c>
@@ -11104,7 +11104,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="135" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A135" s="47">
         <v>0</v>
       </c>
@@ -11157,7 +11157,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="136" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>0</v>
       </c>
@@ -11210,7 +11210,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="137" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>0</v>
       </c>
@@ -11263,12 +11263,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A139" s="10">
         <f>IF(LEN(C139)=17,LEFT(C139,4)+(B139-1)/(DATE(LEFT(C139,4)+1,1,1)-DATE(LEFT(C139,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2024.5819691105039</v>
@@ -11287,7 +11287,7 @@
       <c r="P139" s="48"/>
       <c r="Q139" s="48"/>
     </row>
-    <row r="140" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>0</v>
       </c>
@@ -11340,7 +11340,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="141" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>0</v>
       </c>
@@ -11393,7 +11393,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>1000</v>
       </c>
@@ -11450,7 +11450,7 @@
       </c>
       <c r="S142" s="28"/>
     </row>
-    <row r="143" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>0</v>
       </c>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="S143" s="28"/>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>0</v>
       </c>
@@ -11562,7 +11562,7 @@
       </c>
       <c r="S144" s="28"/>
     </row>
-    <row r="145" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>0</v>
       </c>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="S145" s="28"/>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>2010</v>
       </c>
@@ -11673,7 +11673,7 @@
       </c>
       <c r="S146" s="28"/>
     </row>
-    <row r="147" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>0</v>
       </c>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="S147" s="28"/>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>0</v>
       </c>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="S148" s="28"/>
     </row>
-    <row r="149" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>0</v>
       </c>
@@ -11839,7 +11839,7 @@
       </c>
       <c r="S149" s="28"/>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>3000</v>
       </c>
@@ -11896,7 +11896,7 @@
       </c>
       <c r="S150" s="28"/>
     </row>
-    <row r="151" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>0</v>
       </c>
@@ -11949,7 +11949,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>0</v>
       </c>
@@ -12006,7 +12006,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="153" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>0</v>
       </c>
@@ -12059,7 +12059,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="154" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>0</v>
       </c>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="S154" s="28"/>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>9300</v>
       </c>
@@ -12167,7 +12167,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="156" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>0</v>
       </c>
@@ -12220,7 +12220,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="157" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>0</v>
       </c>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="S157" s="28"/>
     </row>
-    <row r="158" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>0</v>
       </c>
@@ -12327,7 +12327,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="159" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>0</v>
       </c>
@@ -12380,7 +12380,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="160" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>0</v>
       </c>
@@ -12433,12 +12433,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A162" s="10">
         <f>IF(LEN(C162)=17,LEFT(C162,4)+(B162-1)/(DATE(LEFT(C162,4)+1,1,1)-DATE(LEFT(C162,4),1,1)),"BAD DATE FORMAT")</f>
         <v>2025.5808238203958</v>
@@ -12457,7 +12457,7 @@
       <c r="P162" s="48"/>
       <c r="Q162" s="48"/>
     </row>
-    <row r="163" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>0</v>
       </c>
@@ -12514,7 +12514,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="164" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <v>0</v>
       </c>
@@ -12572,7 +12572,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="165" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <v>0</v>
       </c>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="S165" s="28"/>
     </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A166" s="25">
         <v>1000</v>
       </c>
@@ -12694,7 +12694,7 @@
       </c>
       <c r="S166" s="28"/>
     </row>
-    <row r="167" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <v>0</v>
       </c>
@@ -12755,7 +12755,7 @@
       </c>
       <c r="S167" s="28"/>
     </row>
-    <row r="168" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
         <v>0</v>
       </c>
@@ -12816,7 +12816,7 @@
       </c>
       <c r="S168" s="28"/>
     </row>
-    <row r="169" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
         <v>0</v>
       </c>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="S169" s="28"/>
     </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A170" s="25">
         <v>2010</v>
       </c>
@@ -12938,7 +12938,7 @@
       </c>
       <c r="S170" s="28"/>
     </row>
-    <row r="171" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
         <v>0</v>
       </c>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="S171" s="28"/>
     </row>
-    <row r="172" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
         <v>0</v>
       </c>
@@ -13060,7 +13060,7 @@
       </c>
       <c r="S172" s="28"/>
     </row>
-    <row r="173" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
         <v>0</v>
       </c>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="S173" s="28"/>
     </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A174" s="25">
         <v>3000</v>
       </c>
@@ -13181,7 +13181,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="175" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
         <v>0</v>
       </c>
@@ -13241,7 +13241,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="176" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
         <v>0</v>
       </c>
@@ -13301,7 +13301,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="177" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
         <v>0</v>
       </c>
@@ -13360,7 +13360,7 @@
       </c>
       <c r="S177" s="28"/>
     </row>
-    <row r="178" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <v>9300</v>
       </c>
@@ -13419,7 +13419,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="179" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
         <v>0</v>
       </c>
@@ -13477,7 +13477,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="180" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
         <v>0</v>
       </c>
@@ -13536,7 +13536,7 @@
       </c>
       <c r="S180" s="28"/>
     </row>
-    <row r="181" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
         <v>0</v>
       </c>
@@ -13594,7 +13594,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="182" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>0</v>
       </c>
@@ -13652,7 +13652,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="183" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
         <v>0</v>
       </c>
@@ -13710,7 +13710,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A184" s="25">
         <v>0</v>
       </c>
@@ -13766,7 +13766,7 @@
         <v>R = 1000/M</v>
       </c>
     </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A185" s="25">
         <v>0</v>
       </c>
@@ -13837,12 +13837,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA7BD733-D02F-4818-9D6A-E6E21FE780ED}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.6640625" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="71" t="s">
         <v>256</v>
       </c>
@@ -13868,7 +13868,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="54" t="s">
         <v>257</v>
       </c>
@@ -13878,8 +13878,11 @@
       <c r="C2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="54" t="s">
         <v>258</v>
       </c>
@@ -13889,8 +13892,11 @@
       <c r="C3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="54" t="s">
         <v>259</v>
       </c>
@@ -13900,8 +13906,11 @@
       <c r="C4">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="54" t="s">
         <v>260</v>
       </c>
@@ -13911,8 +13920,11 @@
       <c r="C5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="54" t="s">
         <v>261</v>
       </c>
@@ -13922,8 +13934,11 @@
       <c r="C6">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="54" t="s">
         <v>262</v>
       </c>
@@ -13933,8 +13948,11 @@
       <c r="C7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="54" t="s">
         <v>263</v>
       </c>
@@ -13944,8 +13962,11 @@
       <c r="C8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="54" t="s">
         <v>271</v>
       </c>
@@ -13958,11 +13979,14 @@
       <c r="D9">
         <v>3</v>
       </c>
+      <c r="E9">
+        <v>14</v>
+      </c>
       <c r="F9">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="54" t="s">
         <v>264</v>
       </c>
@@ -13982,7 +14006,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="54" t="s">
         <v>265</v>
       </c>
@@ -13999,7 +14023,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="54" t="s">
         <v>266</v>
       </c>
@@ -14016,7 +14040,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="54" t="s">
         <v>267</v>
       </c>
@@ -14039,7 +14063,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="54" t="s">
         <v>268</v>
       </c>
@@ -14062,7 +14086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="54" t="s">
         <v>269</v>
       </c>
@@ -14093,22 +14117,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B5CE66C-33D7-49A1-8DF7-7981795B80E7}">
   <dimension ref="A1:P147"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="29.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>200</v>
       </c>
@@ -14158,7 +14182,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>122</v>
       </c>
@@ -14187,7 +14211,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>123</v>
       </c>
@@ -14216,7 +14240,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>124</v>
       </c>
@@ -14251,7 +14275,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>125</v>
       </c>
@@ -14298,7 +14322,7 @@
         <v>1.7168308506891199</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>126</v>
       </c>
@@ -14333,7 +14357,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>127</v>
       </c>
@@ -14368,7 +14392,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>128</v>
       </c>
@@ -14403,7 +14427,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>129</v>
       </c>
@@ -14450,7 +14474,7 @@
         <v>1.0501569268589599</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>130</v>
       </c>
@@ -14485,7 +14509,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>131</v>
       </c>
@@ -14520,7 +14544,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>132</v>
       </c>
@@ -14555,7 +14579,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>133</v>
       </c>
@@ -14602,7 +14626,7 @@
         <v>0.94600494833357596</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>134</v>
       </c>
@@ -14637,7 +14661,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>135</v>
       </c>
@@ -14672,7 +14696,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>136</v>
       </c>
@@ -14701,7 +14725,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>137</v>
       </c>
@@ -14748,7 +14772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>138</v>
       </c>
@@ -14774,7 +14798,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>139</v>
       </c>
@@ -14800,7 +14824,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>140</v>
       </c>
@@ -14826,7 +14850,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>141</v>
       </c>
@@ -14855,7 +14879,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>142</v>
       </c>
@@ -14884,7 +14908,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>143</v>
       </c>
@@ -14925,7 +14949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>144</v>
       </c>
@@ -14966,7 +14990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>78</v>
       </c>
@@ -14995,7 +15019,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>79</v>
       </c>
@@ -15024,7 +15048,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>80</v>
       </c>
@@ -15071,7 +15095,7 @@
         <v>1.2587336487582701</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>81</v>
       </c>
@@ -15106,7 +15130,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>82</v>
       </c>
@@ -15156,7 +15180,7 @@
         <v>1.2587336487582701</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>83</v>
       </c>
@@ -15191,7 +15215,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>84</v>
       </c>
@@ -15238,7 +15262,7 @@
         <v>1.8811551773110999</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>85</v>
       </c>
@@ -15273,7 +15297,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>86</v>
       </c>
@@ -15323,7 +15347,7 @@
         <v>1.8811551773110999</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>87</v>
       </c>
@@ -15358,7 +15382,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>88</v>
       </c>
@@ -15405,7 +15429,7 @@
         <v>1.2914628942617901</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>89</v>
       </c>
@@ -15440,7 +15464,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>90</v>
       </c>
@@ -15490,7 +15514,7 @@
         <v>1.2914628942617901</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>91</v>
       </c>
@@ -15525,7 +15549,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>92</v>
       </c>
@@ -15554,7 +15578,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>93</v>
       </c>
@@ -15601,7 +15625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>94</v>
       </c>
@@ -15627,7 +15651,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>95</v>
       </c>
@@ -15653,7 +15677,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>96</v>
       </c>
@@ -15679,7 +15703,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>97</v>
       </c>
@@ -15714,7 +15738,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>98</v>
       </c>
@@ -15749,7 +15773,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>99</v>
       </c>
@@ -15784,7 +15808,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>100</v>
       </c>
@@ -15819,7 +15843,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>101</v>
       </c>
@@ -15848,7 +15872,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>102</v>
       </c>
@@ -15877,7 +15901,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>103</v>
       </c>
@@ -15921,7 +15945,7 @@
         <v>2.52101822944072</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>104</v>
       </c>
@@ -15953,7 +15977,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>105</v>
       </c>
@@ -16000,7 +16024,7 @@
         <v>2.52101822944072</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>106</v>
       </c>
@@ -16032,7 +16056,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>107</v>
       </c>
@@ -16079,7 +16103,7 @@
         <v>0.929754688179387</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>108</v>
       </c>
@@ -16114,7 +16138,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>109</v>
       </c>
@@ -16164,7 +16188,7 @@
         <v>0.929754688179387</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>110</v>
       </c>
@@ -16199,7 +16223,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>111</v>
       </c>
@@ -16246,7 +16270,7 @@
         <v>2.4150196263511101</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>112</v>
       </c>
@@ -16281,7 +16305,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>113</v>
       </c>
@@ -16331,7 +16355,7 @@
         <v>2.4150196263511101</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>114</v>
       </c>
@@ -16366,7 +16390,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>115</v>
       </c>
@@ -16395,7 +16419,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>116</v>
       </c>
@@ -16442,7 +16466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>117</v>
       </c>
@@ -16468,7 +16492,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>118</v>
       </c>
@@ -16494,7 +16518,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>119</v>
       </c>
@@ -16520,7 +16544,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>120</v>
       </c>
@@ -16549,7 +16573,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>121</v>
       </c>
@@ -16578,7 +16602,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>65</v>
       </c>
@@ -16625,7 +16649,7 @@
         <v>1.16405016530411</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>66</v>
       </c>
@@ -16672,7 +16696,7 @@
         <v>1.8352099609999999</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>67</v>
       </c>
@@ -16719,7 +16743,7 @@
         <v>1.2169603471391199</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>68</v>
       </c>
@@ -16754,7 +16778,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>69</v>
       </c>
@@ -16789,7 +16813,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>70</v>
       </c>
@@ -16824,7 +16848,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>71</v>
       </c>
@@ -16874,7 +16898,7 @@
         <v>1.16405016530411</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>72</v>
       </c>
@@ -16924,7 +16948,7 @@
         <v>1.8352099609999999</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>73</v>
       </c>
@@ -16974,7 +16998,7 @@
         <v>1.2169603471391199</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>74</v>
       </c>
@@ -17021,7 +17045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>75</v>
       </c>
@@ -17071,7 +17095,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>76</v>
       </c>
@@ -17121,7 +17145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>77</v>
       </c>
@@ -17147,7 +17171,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>37</v>
       </c>
@@ -17194,7 +17218,7 @@
         <v>1.80205774681044</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>38</v>
       </c>
@@ -17241,7 +17265,7 @@
         <v>2.03531169831321</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>39</v>
       </c>
@@ -17288,7 +17312,7 @@
         <v>2.20773173146471</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>40</v>
       </c>
@@ -17320,7 +17344,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>41</v>
       </c>
@@ -17352,7 +17376,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>42</v>
       </c>
@@ -17384,7 +17408,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>43</v>
       </c>
@@ -17434,7 +17458,7 @@
         <v>1.80205774681044</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>44</v>
       </c>
@@ -17484,7 +17508,7 @@
         <v>2.03531169831321</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>45</v>
       </c>
@@ -17534,7 +17558,7 @@
         <v>2.20773173146471</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>46</v>
       </c>
@@ -17581,7 +17605,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>47</v>
       </c>
@@ -17628,7 +17652,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>48</v>
       </c>
@@ -17675,7 +17699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>49</v>
       </c>
@@ -17722,7 +17746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>50</v>
       </c>
@@ -17769,7 +17793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>51</v>
       </c>
@@ -17795,7 +17819,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>52</v>
       </c>
@@ -17842,7 +17866,7 @@
         <v>0.76827735566056199</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>53</v>
       </c>
@@ -17889,7 +17913,7 @@
         <v>2.03531169831321</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>54</v>
       </c>
@@ -17936,7 +17960,7 @@
         <v>0.83122061412608705</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>55</v>
       </c>
@@ -17971,7 +17995,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>56</v>
       </c>
@@ -18006,7 +18030,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>57</v>
       </c>
@@ -18041,7 +18065,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>58</v>
       </c>
@@ -18091,7 +18115,7 @@
         <v>0.76827735566056199</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>59</v>
       </c>
@@ -18141,7 +18165,7 @@
         <v>2.03531169831321</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>60</v>
       </c>
@@ -18191,7 +18215,7 @@
         <v>0.83122061412608705</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>61</v>
       </c>
@@ -18238,7 +18262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>62</v>
       </c>
@@ -18288,7 +18312,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>63</v>
       </c>
@@ -18338,7 +18362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>64</v>
       </c>
@@ -18364,7 +18388,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>18</v>
       </c>
@@ -18411,7 +18435,7 @@
         <v>1.67449813656697</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>19</v>
       </c>
@@ -18458,7 +18482,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>20</v>
       </c>
@@ -18502,7 +18526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>21</v>
       </c>
@@ -18528,7 +18552,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>22</v>
       </c>
@@ -18575,7 +18599,7 @@
         <v>1.67449813656697</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>23</v>
       </c>
@@ -18622,7 +18646,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>24</v>
       </c>
@@ -18669,7 +18693,7 @@
         <v>2.2908047722416698</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>25</v>
       </c>
@@ -18701,7 +18725,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>26</v>
       </c>
@@ -18733,7 +18757,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>27</v>
       </c>
@@ -18765,7 +18789,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>28</v>
       </c>
@@ -18812,7 +18836,7 @@
         <v>1.67449813656697</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>28.5</v>
       </c>
@@ -18859,7 +18883,7 @@
         <v>2.2908047722416698</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>29</v>
       </c>
@@ -18906,7 +18930,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>30</v>
       </c>
@@ -18953,7 +18977,7 @@
         <v>2.2908047722416698</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>31</v>
       </c>
@@ -19000,7 +19024,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>32</v>
       </c>
@@ -19047,7 +19071,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>33</v>
       </c>
@@ -19094,7 +19118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>34</v>
       </c>
@@ -19141,7 +19165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>35</v>
       </c>
@@ -19185,7 +19209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>36</v>
       </c>
@@ -19211,7 +19235,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>15</v>
       </c>
@@ -19258,7 +19282,7 @@
         <v>1.67262493287749</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>16</v>
       </c>
@@ -19305,7 +19329,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>17</v>
       </c>
@@ -19349,7 +19373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>12</v>
       </c>
@@ -19396,7 +19420,7 @@
         <v>1.67075591548251</v>
       </c>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>13</v>
       </c>
@@ -19443,7 +19467,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>14</v>
       </c>
@@ -19487,7 +19511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>6</v>
       </c>
@@ -19534,7 +19558,7 @@
         <v>1.6226717989921</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>7</v>
       </c>
@@ -19581,7 +19605,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>8</v>
       </c>
@@ -19625,7 +19649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>9</v>
       </c>
@@ -19672,7 +19696,7 @@
         <v>1.66982297226244</v>
       </c>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>10</v>
       </c>
@@ -19719,7 +19743,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>11</v>
       </c>
@@ -19763,7 +19787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>3</v>
       </c>
@@ -19810,7 +19834,7 @@
         <v>1.6188010157323101</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>4</v>
       </c>
@@ -19857,7 +19881,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>5</v>
       </c>
@@ -19901,7 +19925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>0</v>
       </c>
@@ -19949,7 +19973,7 @@
         <v>1.6168725409881399</v>
       </c>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>1</v>
       </c>
@@ -19996,7 +20020,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2</v>
       </c>
@@ -20051,20 +20075,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C2AC3CD-B28B-4E07-84D1-63F10D71EFF6}">
   <dimension ref="A1:O14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="9.6640625" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="14.5" customWidth="1"/>
-    <col min="9" max="9" width="15.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
-    <col min="12" max="12" width="14.5" customWidth="1"/>
-    <col min="13" max="13" width="13.5" customWidth="1"/>
-    <col min="14" max="14" width="15.33203125" customWidth="1"/>
-    <col min="15" max="15" width="13.5" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="15.28515625" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="60" t="s">
         <v>201</v>
       </c>
@@ -20111,7 +20135,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="57">
         <v>2015</v>
       </c>
@@ -20158,7 +20182,7 @@
         <v>1.6168725409881399</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="56">
         <v>2016</v>
       </c>
@@ -20205,7 +20229,7 @@
         <v>1.6188010157323101</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="56">
         <v>2017</v>
       </c>
@@ -20252,7 +20276,7 @@
         <v>1.6226717989921</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="57">
         <v>2017</v>
       </c>
@@ -20299,7 +20323,7 @@
         <v>1.66982297226244</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="57">
         <v>2018</v>
       </c>
@@ -20346,7 +20370,7 @@
         <v>1.67075591548251</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="56">
         <v>2019</v>
       </c>
@@ -20393,7 +20417,7 @@
         <v>1.67262493287749</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="56">
         <v>2020</v>
       </c>
@@ -20440,7 +20464,7 @@
         <v>1.67449813656697</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="57">
         <v>2020</v>
       </c>
@@ -20487,7 +20511,7 @@
         <v>1.67449813656697</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="56">
         <v>2021</v>
       </c>
@@ -20534,7 +20558,7 @@
         <v>1.80205774681044</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="56">
         <v>2021</v>
       </c>
@@ -20581,7 +20605,7 @@
         <v>0.76827735566056199</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="56">
         <v>2022</v>
       </c>
@@ -20628,7 +20652,7 @@
         <v>1.16405016530411</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="57">
         <v>2024</v>
       </c>
@@ -20675,7 +20699,7 @@
         <v>1.2587336487582701</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="57">
         <v>2025</v>
       </c>
@@ -20734,20 +20758,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51D50481-F00D-4F48-81C6-07265F307B30}">
   <dimension ref="A1:O15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="9.6640625" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="14.5" customWidth="1"/>
-    <col min="9" max="9" width="15.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
-    <col min="12" max="12" width="14.5" customWidth="1"/>
-    <col min="13" max="13" width="13.5" customWidth="1"/>
-    <col min="14" max="14" width="15.33203125" customWidth="1"/>
-    <col min="15" max="15" width="13.5" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="15.28515625" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="62" t="s">
         <v>201</v>
       </c>
@@ -20794,7 +20818,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="63">
         <v>2015</v>
       </c>
@@ -20839,7 +20863,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="64">
         <v>2016</v>
       </c>
@@ -20884,7 +20908,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="63">
         <v>2017</v>
       </c>
@@ -20929,7 +20953,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="64">
         <v>2017</v>
       </c>
@@ -20974,7 +20998,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="63">
         <v>2018</v>
       </c>
@@ -21019,7 +21043,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="64">
         <v>2019</v>
       </c>
@@ -21064,7 +21088,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="63">
         <v>2020</v>
       </c>
@@ -21109,7 +21133,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="64">
         <v>2020</v>
       </c>
@@ -21154,7 +21178,7 @@
         <v>1.9286659923145</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="69">
         <v>2021</v>
       </c>
@@ -21199,7 +21223,7 @@
         <v>2.03531169831321</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="72">
         <v>2021</v>
       </c>
@@ -21244,7 +21268,7 @@
         <v>2.03531169831321</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="74">
         <v>2022</v>
       </c>
@@ -21289,7 +21313,7 @@
         <v>1.8352099609999999</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="74">
         <v>2024</v>
       </c>
@@ -21334,7 +21358,7 @@
         <v>1.8811551773110999</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="72">
         <v>2024</v>
       </c>
@@ -21379,7 +21403,7 @@
         <v>0.929754688179387</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="74">
         <v>2025</v>
       </c>
@@ -21422,7 +21446,7 @@
       <c r="N15" s="64">
         <v>119.336014415791</v>
       </c>
-      <c r="O15" s="80">
+      <c r="O15" s="76">
         <v>1.0501569268589599</v>
       </c>
     </row>
@@ -21437,20 +21461,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71D78007-B334-4AFA-9368-61BFA621700B}">
   <dimension ref="A1:O8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="9.6640625" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="14.5" customWidth="1"/>
-    <col min="9" max="9" width="15.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
-    <col min="12" max="12" width="14.5" customWidth="1"/>
-    <col min="13" max="13" width="13.5" customWidth="1"/>
-    <col min="14" max="14" width="15.33203125" customWidth="1"/>
-    <col min="15" max="15" width="13.5" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="15.28515625" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="62" t="s">
         <v>201</v>
       </c>
@@ -21497,7 +21521,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="63">
         <v>2020</v>
       </c>
@@ -21542,7 +21566,7 @@
         <v>2.2908047722416698</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="64">
         <v>2021</v>
       </c>
@@ -21587,7 +21611,7 @@
         <v>2.20773173146471</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="63">
         <v>2021</v>
       </c>
@@ -21632,7 +21656,7 @@
         <v>0.83122061412608705</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="64">
         <v>2022</v>
       </c>
@@ -21677,7 +21701,7 @@
         <v>1.2169603471391199</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="64">
         <v>2024</v>
       </c>
@@ -21722,7 +21746,7 @@
         <v>1.2914628942617901</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="69">
         <v>2024</v>
       </c>
@@ -21767,7 +21791,7 @@
         <v>2.4150196263511101</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="67">
         <v>2025</v>
       </c>
@@ -21823,20 +21847,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EB1D8E7-B939-4F56-8304-C86C81BE8A5F}">
   <dimension ref="A1:O7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="9.6640625" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="14.5" customWidth="1"/>
-    <col min="9" max="9" width="15.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
-    <col min="12" max="12" width="14.5" customWidth="1"/>
-    <col min="13" max="13" width="13.5" customWidth="1"/>
-    <col min="14" max="14" width="15.33203125" customWidth="1"/>
-    <col min="15" max="15" width="13.5" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="15.28515625" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="62" t="s">
         <v>201</v>
       </c>
@@ -21883,7 +21907,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="63">
         <v>2025</v>
       </c>
@@ -21928,7 +21952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="64">
         <v>2024</v>
       </c>
@@ -21973,7 +21997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="63">
         <v>2024</v>
       </c>
@@ -22018,7 +22042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="64">
         <v>2022</v>
       </c>
@@ -22063,7 +22087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="63">
         <v>2021</v>
       </c>
@@ -22108,7 +22132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="67">
         <v>2021</v>
       </c>
@@ -22164,20 +22188,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1159179F-CF4E-4E88-AA90-1605119874FB}">
   <dimension ref="A1:O15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="9.6640625" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="14.5" customWidth="1"/>
-    <col min="9" max="9" width="15.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
-    <col min="12" max="12" width="14.5" customWidth="1"/>
-    <col min="13" max="13" width="13.5" customWidth="1"/>
-    <col min="14" max="14" width="15.33203125" customWidth="1"/>
-    <col min="15" max="15" width="13.5" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="15.28515625" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="62" t="s">
         <v>201</v>
       </c>
@@ -22224,7 +22248,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="63">
         <v>2021</v>
       </c>
@@ -22259,7 +22283,7 @@
       <c r="N2" s="63"/>
       <c r="O2" s="63"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="64">
         <v>2021</v>
       </c>
@@ -22294,7 +22318,7 @@
       <c r="N3" s="64"/>
       <c r="O3" s="64"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="63">
         <v>2021</v>
       </c>
@@ -22329,7 +22353,7 @@
       <c r="N4" s="63"/>
       <c r="O4" s="63"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="64">
         <v>2021</v>
       </c>
@@ -22374,7 +22398,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="63">
         <v>2021</v>
       </c>
@@ -22419,7 +22443,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="64">
         <v>2021</v>
       </c>
@@ -22464,7 +22488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="63">
         <v>2021</v>
       </c>
@@ -22509,7 +22533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="64">
         <v>2020</v>
       </c>
@@ -22544,7 +22568,7 @@
       <c r="N9" s="64"/>
       <c r="O9" s="64"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="63">
         <v>2020</v>
       </c>
@@ -22579,7 +22603,7 @@
       <c r="N10" s="63"/>
       <c r="O10" s="63"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="64">
         <v>2020</v>
       </c>
@@ -22614,7 +22638,7 @@
       <c r="N11" s="64"/>
       <c r="O11" s="64"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="63">
         <v>2020</v>
       </c>
@@ -22659,7 +22683,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="64">
         <v>2020</v>
       </c>
@@ -22704,7 +22728,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="63">
         <v>2020</v>
       </c>
@@ -22749,7 +22773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="67">
         <v>2020</v>
       </c>
@@ -22805,20 +22829,20 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7847FC27-2935-424C-A158-6B9B5A8DB710}">
   <dimension ref="A1:O4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="9.6640625" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="14.5" customWidth="1"/>
-    <col min="9" max="9" width="15.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
-    <col min="12" max="12" width="14.5" customWidth="1"/>
-    <col min="13" max="13" width="13.5" customWidth="1"/>
-    <col min="14" max="14" width="15.33203125" customWidth="1"/>
-    <col min="15" max="15" width="13.5" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="15.28515625" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="62" t="s">
         <v>201</v>
       </c>
@@ -22865,7 +22889,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="63">
         <v>2025</v>
       </c>
@@ -22900,7 +22924,7 @@
       <c r="N2" s="63"/>
       <c r="O2" s="63"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="64">
         <v>2024</v>
       </c>
@@ -22935,7 +22959,7 @@
       <c r="N3" s="64"/>
       <c r="O3" s="64"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="69">
         <v>2024</v>
       </c>
@@ -22981,20 +23005,20 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7BE515-81CD-497C-A39A-B15BC3D309FD}">
   <dimension ref="A1:O4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="9.6640625" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="14.5" customWidth="1"/>
-    <col min="9" max="9" width="15.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
-    <col min="12" max="12" width="14.5" customWidth="1"/>
-    <col min="13" max="13" width="13.5" customWidth="1"/>
-    <col min="14" max="14" width="15.33203125" customWidth="1"/>
-    <col min="15" max="15" width="13.5" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="15.28515625" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="62" t="s">
         <v>201</v>
       </c>
@@ -23041,7 +23065,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="63">
         <v>2025</v>
       </c>
@@ -23076,7 +23100,7 @@
       <c r="N2" s="63"/>
       <c r="O2" s="63"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="64">
         <v>2024</v>
       </c>
@@ -23111,7 +23135,7 @@
       <c r="N3" s="64"/>
       <c r="O3" s="64"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="69">
         <v>2024</v>
       </c>
